--- a/daftar_istilah.xlsx
+++ b/daftar_istilah.xlsx
@@ -1640,7 +1640,28 @@
     <font>
       <b/>
       <i val="0"/>
+      <sz val="16"/>
+      <color rgb="FF1F3864"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b val="0"/>
+      <i val="0"/>
       <sz val="11"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <i val="0"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <i val="0"/>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
@@ -1668,36 +1689,15 @@
     <font>
       <b/>
       <i val="0"/>
-      <sz val="11"/>
-      <color auto="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <i val="0"/>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <sz val="11"/>
-      <color rgb="FF666666"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <i val="0"/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color rgb="FF1F3864"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <i val="0"/>
-      <sz val="14"/>
-      <color rgb="FF1F3864"/>
+      <sz val="11"/>
+      <color auto="1"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1722,17 +1722,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF2F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD9E2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2F5496"/>
       </patternFill>
     </fill>
   </fills>
@@ -1776,59 +1776,59 @@
   </cellStyleXfs>
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -2144,7 +2144,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{D211C496-09A5-4FD4-AC5F-3E96BA746EB5}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{9162F4F5-3EBA-492A-8063-4130DE83CE9E}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:E215"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -5058,7 +5058,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{FD32EE32-9DC4-40FD-ABD1-58B6F2E0A3F5}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{83F6191D-0A84-4788-8934-BCF8FA41E61A}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -5145,7 +5145,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{37864AC0-CEF5-4A78-952D-24CC0D2FCDF1}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{3261D3A7-5333-4698-B79E-B2FF47D1BE41}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -5210,7 +5210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{B4F93749-1198-4F72-835F-287DDE4099D0}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{96500025-C12B-403A-915B-2533F0D9335E}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -5275,7 +5275,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{64CEDD02-912F-44A8-9D9E-8DE8BBE10506}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{51AFB0C7-D394-4835-839D-3B1604679F99}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -5450,7 +5450,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{F83D31D7-AE93-4169-8A58-E13B541BE2E1}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{12E90631-3612-4161-9BDB-14860BC150AA}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -5592,7 +5592,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{D27A72C7-BC0A-460E-BD96-5D7F23845E1F}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{71F4A608-23BE-4FF6-862A-A2488346237C}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -5646,7 +5646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{22A7F680-84FD-41A3-A714-AC3C693E6F8C}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{A4E32BBB-4EE7-41A0-A40C-2F90A397FA77}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -5744,7 +5744,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{063007CC-9DC3-4BAD-B614-C4EB866DA199}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{79A6C2D1-30D4-4C2F-8531-46C7CE2722C2}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -5996,7 +5996,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{D4B1CDAF-7172-4BAB-B892-9492997BA7B1}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{C52E0939-A406-43DF-B283-45EBC6067EF2}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -6160,7 +6160,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{5D224BC9-3C59-4E2D-BBF7-1C0E925A7D20}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{9FA269F0-FA1A-4A77-B527-387691A03797}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -6434,7 +6434,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{6CE6DC1A-4264-49B0-9FC5-096E57651D39}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{2355A2B2-0787-4A91-A1B7-539A535656B3}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -6587,7 +6587,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{4A6E96DD-13A4-4D6F-AEF2-75550BA039AA}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{96D0D6F8-EAC0-40F4-8616-C83E0247AC81}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -6762,7 +6762,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{9AF6B2CD-8FF2-4677-90A3-E312C1B9D97A}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{7A9B0B45-21B8-4EC6-85EE-007885B50BDA}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -6838,7 +6838,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{8C718090-1F5B-43C6-AA5F-7CA016EEFCF5}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{7CE0D676-73CB-41E2-9A7D-4A847FEE63EE}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -6903,7 +6903,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{884C9617-CB4F-4919-B8AC-DA6402BEC790}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{9B22F7A3-276A-4909-A5F7-40FD86F4F611}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -7001,7 +7001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{96307F96-68CB-41AA-AAC6-869D32F2EF88}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{AC148654-5CF4-4B84-BBB8-3AE17A731E2F}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -7417,7 +7417,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{326B7F1E-D35D-4FEA-A6E3-E5F1D04FF3A1}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{DDB96EDD-CFD7-4F54-93CF-555DECDC64A8}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -7691,7 +7691,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{F2286697-E20A-4DBE-A96D-1CF53BBB61DE}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{D4C7FDBB-5F71-4F96-8ACC-4252FEB9904F}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -7877,7 +7877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{BEE0ACA7-977C-4629-86C2-23C00CE17ABA}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{D37B6C75-7517-47D5-8E1D-6CFE0ED8D393}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -8008,7 +8008,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{260745AA-CFBC-4C6B-9689-75F4361C4E41}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{DC5B46DB-4770-48F2-80F0-196756A93747}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -8139,7 +8139,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{0385159E-FFB1-4D7F-887C-2C0D3E6975BE}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{49B253F6-CAE9-4BFB-9D3D-5E315FD8E052}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -8325,7 +8325,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{DCF49A85-F3B8-4B77-A71F-96840895CA3B}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{21F1DB70-C37D-4A46-A3D7-7E7C7938D9AC}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
@@ -8434,7 +8434,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{FE7DDD31-B85C-4712-807B-9F6B037AEB5E}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{6DEADA0C-6B7B-4850-B3B0-B1D24F5083F9}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>

--- a/daftar_istilah.xlsx
+++ b/daftar_istilah.xlsx
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D300"/>
+  <dimension ref="A1:D301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" style="44" min="1" max="1"/>
@@ -4496,17 +4496,17 @@
       </c>
       <c r="B175" s="108" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C175" s="101" t="inlineStr">
         <is>
-          <t>Negative Skewness</t>
+          <t>Mark-to-Market (MTM)</t>
         </is>
       </c>
       <c r="D175" s="101" t="inlineStr">
         <is>
-          <t>Kemiringan distribusi probabilitas ke arah negatif: ekor panjang di sebelah kiri — terdapat kejadian penurunan tajam yang jarang namun signifikan, sementara fluktuasi positif harian cenderung lebih kecil dan lebih sering. Return harian Bitcoin menunjukkan negative skewness yang konsisten: dalam kondisi normal harga naik sedikit setiap hari, namun sesekali terjadi crash mendadak yang besar (misalnya -20% dalam satu hari). Karakteristik ini berarti distribusi return Bitcoin tidak simetris seperti yang diasumsikan uji t-test konvensional — justifikasi kuat untuk menggunakan uji non-parametrik Mann-Whitney U dalam penelitian ini. Lihat juga: Skewness, Fat Tails, Mann-Whitney U Test.</t>
+          <t>Mekanisme penilaian posisi trading berdasarkan harga pasar saat ini (bukan harga beli awal). Digunakan pada kontrak futures untuk menghitung unrealized profit/loss secara harian atau real-time. Dalam penelitian ini, posisi BTCUSDT perpetual dinilai secara mark-to-market menggunakan close price setiap bar daily untuk menghasilkan kurva ekuitas yang akurat. Berbeda dengan cost-based valuation yang hanya mencatat realized P&amp;L.</t>
         </is>
       </c>
     </row>
@@ -4521,12 +4521,12 @@
       </c>
       <c r="C176" s="101" t="inlineStr">
         <is>
-          <t>Net Profit</t>
+          <t>Negative Skewness</t>
         </is>
       </c>
       <c r="D176" s="101" t="inlineStr">
         <is>
-          <t>Keuntungan bersih total yang dihasilkan strategi sepanjang periode pengujian, setelah dikurangi semua biaya transaksi (komisi 0,05% dan slippage 0,03% per transaksi). Sinonim dari Net P&amp;L. Dalam penelitian ini: strategi Supertrend menghasilkan Net Profit +$32.170 dari modal awal $10.000 selama periode April 2020-April 2026 (backtest penuh). Angka ini setara dengan return kumulatif +321,70% menggunakan metode Fixed Fractional 5% Risk. Berbeda dari Gross Profit yang belum dikurangi biaya, Net Profit adalah angka yang paling relevan untuk mengevaluasi kinerja nyata strategi. Lihat juga: Gross Profit, Net P&amp;L, Commission, Slippage.</t>
+          <t>Kemiringan distribusi probabilitas ke arah negatif: ekor panjang di sebelah kiri — terdapat kejadian penurunan tajam yang jarang namun signifikan, sementara fluktuasi positif harian cenderung lebih kecil dan lebih sering. Return harian Bitcoin menunjukkan negative skewness yang konsisten: dalam kondisi normal harga naik sedikit setiap hari, namun sesekali terjadi crash mendadak yang besar (misalnya -20% dalam satu hari). Karakteristik ini berarti distribusi return Bitcoin tidak simetris seperti yang diasumsikan uji t-test konvensional — justifikasi kuat untuk menggunakan uji non-parametrik Mann-Whitney U dalam penelitian ini. Lihat juga: Skewness, Fat Tails, Mann-Whitney U Test.</t>
         </is>
       </c>
     </row>
@@ -4541,12 +4541,12 @@
       </c>
       <c r="C177" s="101" t="inlineStr">
         <is>
-          <t>NFT (Non-Fungible Token)</t>
+          <t>Net Profit</t>
         </is>
       </c>
       <c r="D177" s="101" t="inlineStr">
         <is>
-          <t>Aset digital unik yang kepemilikannya dicatat di blockchain — berbeda dari mata uang kripto biasa yang saling dapat dipertukarkan (fungible), setiap NFT memiliki identitas unik yang tidak dapat digandakan. NFT digunakan untuk merepresentasikan kepemilikan karya seni digital, item dalam game, koleksi, dan lain-lain. Dalam penelitian ini, NFT disebutkan dalam konteks menjelaskan peran ekosistem Ethereum sebagai platform yang paling aktif digunakan untuk smart contract, DeFi, dan NFT.</t>
+          <t>Keuntungan bersih total yang dihasilkan strategi sepanjang periode pengujian, setelah dikurangi semua biaya transaksi (komisi 0,05% dan slippage 0,03% per transaksi). Sinonim dari Net P&amp;L. Dalam penelitian ini: strategi Supertrend menghasilkan Net Profit +$32.170 dari modal awal $10.000 selama periode April 2020-April 2026 (backtest penuh). Angka ini setara dengan return kumulatif +321,70% menggunakan metode Fixed Fractional 5% Risk. Berbeda dari Gross Profit yang belum dikurangi biaya, Net Profit adalah angka yang paling relevan untuk mengevaluasi kinerja nyata strategi. Lihat juga: Gross Profit, Net P&amp;L, Commission, Slippage.</t>
         </is>
       </c>
     </row>
@@ -4561,12 +4561,12 @@
       </c>
       <c r="C178" s="101" t="inlineStr">
         <is>
-          <t>Noise (Market Noise)</t>
+          <t>NFT (Non-Fungible Token)</t>
         </is>
       </c>
       <c r="D178" s="101" t="inlineStr">
         <is>
-          <t>"Kebisingan" pasar — fluktuasi harga jangka sangat pendek yang tidak bermakna, mencerminkan ketidakseimbangan sementara kecil antara pembeli dan penjual yang tidak mencerminkan tren sesungguhnya. Bayangkan harga Bitcoin seperti seseorang yang berjalan di pantai: selain langkah maju yang konsisten (tren), ada juga gerakan kecil ke kiri dan kanan akibat ombak kecil (noise). Indikator Supertrend dirancang untuk menyaring noise ini melalui dua mekanisme: (1) ATR mengukur seberapa banyak noise yang ada saat ini; dan (2) Multiplier mengkalibrasi seberapa banyak noise yang harus diabaikan sebelum sinyal dianggap valid. Multiplier = 3,0 dalam penelitian ini berarti hanya pergerakan lebih besar dari 3 kali ATR yang dianggap sebagai sinyal tren nyata.</t>
+          <t>Aset digital unik yang kepemilikannya dicatat di blockchain — berbeda dari mata uang kripto biasa yang saling dapat dipertukarkan (fungible), setiap NFT memiliki identitas unik yang tidak dapat digandakan. NFT digunakan untuk merepresentasikan kepemilikan karya seni digital, item dalam game, koleksi, dan lain-lain. Dalam penelitian ini, NFT disebutkan dalam konteks menjelaskan peran ekosistem Ethereum sebagai platform yang paling aktif digunakan untuk smart contract, DeFi, dan NFT.</t>
         </is>
       </c>
     </row>
@@ -4581,12 +4581,12 @@
       </c>
       <c r="C179" s="101" t="inlineStr">
         <is>
-          <t>Normalisasi Min-Max (Min-Max Normalization)</t>
+          <t>Noise (Market Noise)</t>
         </is>
       </c>
       <c r="D179" s="101" t="inlineStr">
         <is>
-          <t>Teknik transformasi data yang mengubah nilai-nilai dari berbagai skala berbeda ke dalam rentang standar [0, 1], dengan rumus: Nilai_ternormalisasi = (Nilai − Batas_Bawah) / (Batas_Atas − Batas_Bawah). Hasil bernilai 0 berarti performa terburuk (menyentuh batas bawah), dan 1 berarti performa terbaik (menyentuh batas atas). Normalisasi diperlukan sebelum menggabungkan beberapa metrik yang memiliki skala sangat berbeda ke dalam satu skor komposit — tanpa normalisasi, metrik dengan nilai absolut lebih besar akan mendominasi skor secara tidak adil. Dalam penelitian ini, normalisasi min-max diterapkan pada lima metrik (Sharpe Ratio, Calmar Ratio, Sortino Ratio, Win Rate, Profit Factor) sebelum dijumlahkan dengan bobot masing-masing menjadi RAO Score. Batas normalisasi bersumber dari distribusi metrik pada studi kripto empiris, misalnya Sharpe dinormalisasi dalam rentang −2 hingga +4. Lihat juga: RAO Score, Sharpe Ratio, Calmar Ratio, Grid Search.</t>
+          <t>"Kebisingan" pasar — fluktuasi harga jangka sangat pendek yang tidak bermakna, mencerminkan ketidakseimbangan sementara kecil antara pembeli dan penjual yang tidak mencerminkan tren sesungguhnya. Bayangkan harga Bitcoin seperti seseorang yang berjalan di pantai: selain langkah maju yang konsisten (tren), ada juga gerakan kecil ke kiri dan kanan akibat ombak kecil (noise). Indikator Supertrend dirancang untuk menyaring noise ini melalui dua mekanisme: (1) ATR mengukur seberapa banyak noise yang ada saat ini; dan (2) Multiplier mengkalibrasi seberapa banyak noise yang harus diabaikan sebelum sinyal dianggap valid. Multiplier = 3,0 dalam penelitian ini berarti hanya pergerakan lebih besar dari 3 kali ATR yang dianggap sebagai sinyal tren nyata.</t>
         </is>
       </c>
     </row>
@@ -4596,17 +4596,17 @@
       </c>
       <c r="B180" s="108" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C180" s="101" t="inlineStr">
         <is>
-          <t>OHLCV</t>
+          <t>Normalisasi Min-Max (Min-Max Normalization)</t>
         </is>
       </c>
       <c r="D180" s="101" t="inlineStr">
         <is>
-          <t>Format standar data harga yang digunakan di seluruh dunia keuangan. Setiap huruf mewakili satu informasi: O = Open (harga saat periode mulai), H = High (harga tertinggi sepanjang periode), L = Low (harga terendah), C = Close (harga saat periode berakhir), V = Volume (berapa banyak Bitcoin yang diperdagangkan). Kelima data ini membentuk satu candle di grafik harga. Dalam penelitian ini, data OHLCV harian Bitcoin diunduh dari Bybit melalui API untuk periode April 2020 hingga April 2026 dan menjadi bahan baku utama seluruh kalkulasi indikator dan simulasi backtesting.</t>
+          <t>Teknik transformasi data yang mengubah nilai-nilai dari berbagai skala berbeda ke dalam rentang standar [0, 1], dengan rumus: Nilai_ternormalisasi = (Nilai − Batas_Bawah) / (Batas_Atas − Batas_Bawah). Hasil bernilai 0 berarti performa terburuk (menyentuh batas bawah), dan 1 berarti performa terbaik (menyentuh batas atas). Normalisasi diperlukan sebelum menggabungkan beberapa metrik yang memiliki skala sangat berbeda ke dalam satu skor komposit — tanpa normalisasi, metrik dengan nilai absolut lebih besar akan mendominasi skor secara tidak adil. Dalam penelitian ini, normalisasi min-max diterapkan pada lima metrik (Sharpe Ratio, Calmar Ratio, Sortino Ratio, Win Rate, Profit Factor) sebelum dijumlahkan dengan bobot masing-masing menjadi RAO Score. Batas normalisasi bersumber dari distribusi metrik pada studi kripto empiris, misalnya Sharpe dinormalisasi dalam rentang −2 hingga +4. Lihat juga: RAO Score, Sharpe Ratio, Calmar Ratio, Grid Search.</t>
         </is>
       </c>
     </row>
@@ -4621,12 +4621,12 @@
       </c>
       <c r="C181" s="101" t="inlineStr">
         <is>
-          <t>OOS (Out-of-Sample)</t>
+          <t>OHLCV</t>
         </is>
       </c>
       <c r="D181" s="101" t="inlineStr">
         <is>
-          <t>Bagian dari data historis yang TIDAK pernah digunakan selama proses optimasi parameter — data "buta" yang digunakan untuk menguji apakah strategi yang dioptimasi benar-benar bekerja di kondisi baru. Analoginya persis seperti soal ujian resmi yang belum pernah dilihat mahasiswa sebelum hari ujian. Jika strategi yang bagus di IS ternyata buruk di OOS, itu bukti overfitting yang serius. Sebaliknya, jika kinerja OOS konsisten dengan IS, strategi memiliki generalisasi yang baik. Dalam penelitian ini, Walk-Forward Analysis menggunakan 4 periode OOS berbeda (masing-masing sekitar 12 bulan) untuk menguji konsistensi kinerja lintas waktu.</t>
+          <t>Format standar data harga yang digunakan di seluruh dunia keuangan. Setiap huruf mewakili satu informasi: O = Open (harga saat periode mulai), H = High (harga tertinggi sepanjang periode), L = Low (harga terendah), C = Close (harga saat periode berakhir), V = Volume (berapa banyak Bitcoin yang diperdagangkan). Kelima data ini membentuk satu candle di grafik harga. Dalam penelitian ini, data OHLCV harian Bitcoin diunduh dari Bybit melalui API untuk periode April 2020 hingga April 2026 dan menjadi bahan baku utama seluruh kalkulasi indikator dan simulasi backtesting.</t>
         </is>
       </c>
     </row>
@@ -4641,12 +4641,12 @@
       </c>
       <c r="C182" s="101" t="inlineStr">
         <is>
-          <t>OOS Profitable (Split Out-of-Sample Profitabel)</t>
+          <t>OOS (Out-of-Sample)</t>
         </is>
       </c>
       <c r="D182" s="101" t="inlineStr">
         <is>
-          <t>Metrik evaluasi dalam Walk-Forward Analysis yang mengukur persentase jumlah sub-periode pengujian Out-of-Sample (OOS) yang menghasilkan keuntungan bersih positif, sebagai indikator ketahanan sistem di berbagai kondisi pasar.</t>
+          <t>Bagian dari data historis yang TIDAK pernah digunakan selama proses optimasi parameter — data "buta" yang digunakan untuk menguji apakah strategi yang dioptimasi benar-benar bekerja di kondisi baru. Analoginya persis seperti soal ujian resmi yang belum pernah dilihat mahasiswa sebelum hari ujian. Jika strategi yang bagus di IS ternyata buruk di OOS, itu bukti overfitting yang serius. Sebaliknya, jika kinerja OOS konsisten dengan IS, strategi memiliki generalisasi yang baik. Dalam penelitian ini, Walk-Forward Analysis menggunakan 4 periode OOS berbeda (masing-masing sekitar 12 bulan) untuk menguji konsistensi kinerja lintas waktu.</t>
         </is>
       </c>
     </row>
@@ -4661,12 +4661,12 @@
       </c>
       <c r="C183" s="101" t="inlineStr">
         <is>
-          <t>Open Price (Harga Pembukaan)</t>
+          <t>OOS Profitable (Split Out-of-Sample Profitabel)</t>
         </is>
       </c>
       <c r="D183" s="101" t="inlineStr">
         <is>
-          <t>Harga awal saat candlestick baru mulai terbentuk pada periode tertentu. Open Price digunakan sebagai acuan awal sebelum terjadinya fluktuasi harga dalam satu periode waktu.</t>
+          <t>Metrik evaluasi dalam Walk-Forward Analysis yang mengukur persentase jumlah sub-periode pengujian Out-of-Sample (OOS) yang menghasilkan keuntungan bersih positif, sebagai indikator ketahanan sistem di berbagai kondisi pasar.</t>
         </is>
       </c>
     </row>
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C184" s="101" t="inlineStr">
         <is>
-          <t>Optimasi Parameter</t>
+          <t>Open Price (Harga Pembukaan)</t>
         </is>
       </c>
       <c r="D184" s="101" t="inlineStr">
         <is>
-          <t>Proses sistematis mencari kombinasi nilai parameter (dalam penelitian ini: ATR Period, Multiplier, dan Risk per Trade) yang menghasilkan kinerja terbaik berdasarkan kriteria evaluasi yang ditetapkan. Dalam penelitian ini dilakukan melalui 3D Grid Search dengan 120 kombinasi, menggunakan RAO Score sebagai kriteria pemilihan. Penting: optimasi parameter harus selalu diikuti oleh validasi OOS untuk memastikan parameter yang ditemukan mencerminkan edge nyata, bukan sekadar overfitting terhadap data historis. Proses optimasi yang tidak divalidasi adalah sumber utama backtest overfitting. Lihat juga: Grid Search, RAO Score, Walk-Forward Analysis, Cherry-Picking.</t>
+          <t>Harga awal saat candlestick baru mulai terbentuk pada periode tertentu. Open Price digunakan sebagai acuan awal sebelum terjadinya fluktuasi harga dalam satu periode waktu.</t>
         </is>
       </c>
     </row>
@@ -4701,12 +4701,12 @@
       </c>
       <c r="C185" s="101" t="inlineStr">
         <is>
-          <t>Over-tuning (Penyetelan Berlebih)</t>
+          <t>Optimasi Parameter</t>
         </is>
       </c>
       <c r="D185" s="101" t="inlineStr">
         <is>
-          <t>Kondisi mirip overfitting namun merujuk lebih spesifik pada proses manual penyetelan parameter yang terlalu intensif terhadap data historis. Jika overfitting sering terjadi secara otomatis pada model kompleks, over-tuning lebih merujuk pada situasi di mana seorang peneliti atau trader secara manual terus-menerus menyesuaikan parameter sampai kinerja historisnya tampak sempurna — namun kenyataannya parameter sudah terlalu terikat pada karakteristik unik data masa lalu tersebut. Dalam penelitian ini, risiko over-tuning dikontrol melalui Robustness Score dan Walk-Forward Analysis.</t>
+          <t>Proses sistematis mencari kombinasi nilai parameter (dalam penelitian ini: ATR Period, Multiplier, dan Risk per Trade) yang menghasilkan kinerja terbaik berdasarkan kriteria evaluasi yang ditetapkan. Dalam penelitian ini dilakukan melalui 3D Grid Search dengan 120 kombinasi, menggunakan RAO Score sebagai kriteria pemilihan. Penting: optimasi parameter harus selalu diikuti oleh validasi OOS untuk memastikan parameter yang ditemukan mencerminkan edge nyata, bukan sekadar overfitting terhadap data historis. Proses optimasi yang tidak divalidasi adalah sumber utama backtest overfitting. Lihat juga: Grid Search, RAO Score, Walk-Forward Analysis, Cherry-Picking.</t>
         </is>
       </c>
     </row>
@@ -4721,12 +4721,12 @@
       </c>
       <c r="C186" s="101" t="inlineStr">
         <is>
-          <t>Overfitting</t>
+          <t>Over-tuning (Penyetelan Berlebih)</t>
         </is>
       </c>
       <c r="D186" s="101" t="inlineStr">
         <is>
-          <t>Kondisi di mana sebuah strategi terlalu sempurna disesuaikan dengan data historis yang digunakan dalam pengembangannya, sehingga "menghafalkan" pola-pola spesifik data tersebut alih-alih mempelajari aturan umum. Hasilnya: kinerja di data historis luar biasa bagus, namun di data baru kinerja jelek. Analogi mudah: mahasiswa yang hanya menghafal soal-soal latihan persis tanpa memahami konsepnya — saat muncul soal baru yang mirip tapi tidak identik, ia gagal. Dalam penelitian ini, overfitting dikontrol melalui: (1) Robustness Score yang memilih parameter dengan kinerja stabil; dan (2) Walk-Forward Analysis yang menguji kinerja di data OOS yang tidak disentuh selama optimasi.</t>
+          <t>Kondisi mirip overfitting namun merujuk lebih spesifik pada proses manual penyetelan parameter yang terlalu intensif terhadap data historis. Jika overfitting sering terjadi secara otomatis pada model kompleks, over-tuning lebih merujuk pada situasi di mana seorang peneliti atau trader secara manual terus-menerus menyesuaikan parameter sampai kinerja historisnya tampak sempurna — namun kenyataannya parameter sudah terlalu terikat pada karakteristik unik data masa lalu tersebut. Dalam penelitian ini, risiko over-tuning dikontrol melalui Robustness Score dan Walk-Forward Analysis.</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="C187" s="101" t="inlineStr">
         <is>
-          <t>Overnight Gap (Celah Harga Antar Sesi)</t>
+          <t>Overfitting</t>
         </is>
       </c>
       <c r="D187" s="101" t="inlineStr">
         <is>
-          <t>Perbedaan antara harga penutupan candle harian sebelumnya dan harga pembukaan candle harian berikutnya. Pada pasar saham konvensional yang tutup setiap malam, overnight gap sangat umum karena berita besar yang keluar saat pasar tutup. Pada pasar kripto yang beroperasi 24/7, gap antar candle harian lebih jarang — meskipun bisa terjadi tepat di pergantian hari UTC (00:00 UTC) akibat lonjakan order yang terjadi di momen tersebut.</t>
+          <t>Kondisi di mana sebuah strategi terlalu sempurna disesuaikan dengan data historis yang digunakan dalam pengembangannya, sehingga "menghafalkan" pola-pola spesifik data tersebut alih-alih mempelajari aturan umum. Hasilnya: kinerja di data historis luar biasa bagus, namun di data baru kinerja jelek. Analogi mudah: mahasiswa yang hanya menghafal soal-soal latihan persis tanpa memahami konsepnya — saat muncul soal baru yang mirip tapi tidak identik, ia gagal. Dalam penelitian ini, overfitting dikontrol melalui: (1) Robustness Score yang memilih parameter dengan kinerja stabil; dan (2) Walk-Forward Analysis yang menguji kinerja di data OOS yang tidak disentuh selama optimasi.</t>
         </is>
       </c>
     </row>
@@ -4756,17 +4756,17 @@
       </c>
       <c r="B188" s="108" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>O</t>
         </is>
       </c>
       <c r="C188" s="101" t="inlineStr">
         <is>
-          <t>p-value (Nilai-p)</t>
+          <t>Overnight Gap (Celah Harga Antar Sesi)</t>
         </is>
       </c>
       <c r="D188" s="101" t="inlineStr">
         <is>
-          <t>Probabilitas mengamati hasil yang sama ekstremnya (atau lebih ekstrem) dari data, dengan asumsi bahwa hipotesis nol (H0) benar — dengan kata lain, dengan asumsi tidak ada efek nyata yang terjadi. p-value kecil (di bawah 0,05) berarti: "Sangat tidak mungkin mendapat data seperti ini secara kebetulan — maka kemungkinan besar ada efek nyata." p-value besar (di atas 0,05) berarti data yang diamati cukup mungkin terjadi secara kebetulan. Perlu diingat: signifikan statistik tidak selalu berarti penting secara praktis. Dalam penelitian ini: penelitian INGIN p-value di atas 0,05 untuk H0.2 (tidak ada perbedaan IS vs OOS) sebagai bukti tidak ada overfitting.</t>
+          <t>Perbedaan antara harga penutupan candle harian sebelumnya dan harga pembukaan candle harian berikutnya. Pada pasar saham konvensional yang tutup setiap malam, overnight gap sangat umum karena berita besar yang keluar saat pasar tutup. Pada pasar kripto yang beroperasi 24/7, gap antar candle harian lebih jarang — meskipun bisa terjadi tepat di pergantian hari UTC (00:00 UTC) akibat lonjakan order yang terjadi di momen tersebut.</t>
         </is>
       </c>
     </row>
@@ -4781,12 +4781,12 @@
       </c>
       <c r="C189" s="101" t="inlineStr">
         <is>
-          <t>Paginasi (API Pagination / Pengambilan Data Berbatch)</t>
+          <t>p-value (Nilai-p)</t>
         </is>
       </c>
       <c r="D189" s="101" t="inlineStr">
         <is>
-          <t>Teknik pengambilan data dari API di mana data dalam jumlah besar dibagi menjadi beberapa "halaman" atau batch yang lebih kecil. Analoginya seperti membaca buku: daripada menelan semua 500 halaman sekaligus, Anda membacanya 50 halaman per sesi. Bybit V5 Public API membatasi maksimal 1.000 candle per pemanggilan. Namun data yang dibutuhkan penelitian ini mencakup lebih dari 2.200 candle harian (April 2020-April 2026). Python Tradingbot mengimplementasikan paginasi otomatis: setelah menerima 1.000 candle pertama, sistem menghitung timestamp selanjutnya dan meminta batch berikutnya, terus berulang sampai seluruh rentang waktu terpenuhi.</t>
+          <t>Probabilitas mengamati hasil yang sama ekstremnya (atau lebih ekstrem) dari data, dengan asumsi bahwa hipotesis nol (H0) benar — dengan kata lain, dengan asumsi tidak ada efek nyata yang terjadi. p-value kecil (di bawah 0,05) berarti: "Sangat tidak mungkin mendapat data seperti ini secara kebetulan — maka kemungkinan besar ada efek nyata." p-value besar (di atas 0,05) berarti data yang diamati cukup mungkin terjadi secara kebetulan. Perlu diingat: signifikan statistik tidak selalu berarti penting secara praktis. Dalam penelitian ini: penelitian INGIN p-value di atas 0,05 untuk H0.2 (tidak ada perbedaan IS vs OOS) sebagai bukti tidak ada overfitting.</t>
         </is>
       </c>
     </row>
@@ -4801,12 +4801,12 @@
       </c>
       <c r="C190" s="101" t="inlineStr">
         <is>
-          <t>Panic Buying / Panic Selling (Pembelian/Penjualan Panik)</t>
+          <t>Paginasi (API Pagination / Pengambilan Data Berbatch)</t>
         </is>
       </c>
       <c r="D190" s="101" t="inlineStr">
         <is>
-          <t>Perilaku perdagangan massal yang sepenuhnya didorong oleh emosi ekstrem, bukan analisis rasional. Panic buying terjadi ketika banyak investor tiba-tiba membeli secara bersamaan karena takut ketinggalan kenaikan. Panic selling terjadi ketika banyak investor menjual secara bersamaan karena panik melihat harga turun, memperburuk penurunan jauh di bawah nilai wajar. Kedua fenomena ini jauh lebih parah di pasar kripto karena tidak ada circuit breaker. Sistem algoritmik dalam penelitian ini kebal terhadap kedua fenomena ini secara total: seluruh keputusan dieksekusi oleh algoritma berdasarkan aturan matematis yang objektif — bot tidak pernah "panik."</t>
+          <t>Teknik pengambilan data dari API di mana data dalam jumlah besar dibagi menjadi beberapa "halaman" atau batch yang lebih kecil. Analoginya seperti membaca buku: daripada menelan semua 500 halaman sekaligus, Anda membacanya 50 halaman per sesi. Bybit V5 Public API membatasi maksimal 1.000 candle per pemanggilan. Namun data yang dibutuhkan penelitian ini mencakup lebih dari 2.200 candle harian (April 2020-April 2026). Python Tradingbot mengimplementasikan paginasi otomatis: setelah menerima 1.000 candle pertama, sistem menghitung timestamp selanjutnya dan meminta batch berikutnya, terus berulang sampai seluruh rentang waktu terpenuhi.</t>
         </is>
       </c>
     </row>
@@ -4821,12 +4821,12 @@
       </c>
       <c r="C191" s="101" t="inlineStr">
         <is>
-          <t>Parabolic SAR</t>
+          <t>Panic Buying / Panic Selling (Pembelian/Penjualan Panik)</t>
         </is>
       </c>
       <c r="D191" s="101" t="inlineStr">
         <is>
-          <t>Indikator teknikal yang dikembangkan oleh Welles Wilder (1978) yang mengidentifikasi arah tren dan titik pembalikan potensial melalui serangkaian titik-titik kecil yang muncul di atas atau di bawah grafik harga. Saat harga naik, titik-titik muncul di bawah harga (sebagai trailing stop); saat harga turun, titik muncul di atas. Indikator Supertrend adalah "evolusi" dari Parabolic SAR: mempertahankan konsep dasar trailing stop dinamis, namun menambahkan dimensi adaptasi volatilitas melalui ATR — membuat band lebih lebar saat pasar volatile dan lebih sempit saat tenang.</t>
+          <t>Perilaku perdagangan massal yang sepenuhnya didorong oleh emosi ekstrem, bukan analisis rasional. Panic buying terjadi ketika banyak investor tiba-tiba membeli secara bersamaan karena takut ketinggalan kenaikan. Panic selling terjadi ketika banyak investor menjual secara bersamaan karena panik melihat harga turun, memperburuk penurunan jauh di bawah nilai wajar. Kedua fenomena ini jauh lebih parah di pasar kripto karena tidak ada circuit breaker. Sistem algoritmik dalam penelitian ini kebal terhadap kedua fenomena ini secara total: seluruh keputusan dieksekusi oleh algoritma berdasarkan aturan matematis yang objektif — bot tidak pernah "panik."</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="C192" s="101" t="inlineStr">
         <is>
-          <t>Parameter Robustness (Ketangguhan Parameter)</t>
+          <t>Parabolic SAR</t>
         </is>
       </c>
       <c r="D192" s="101" t="inlineStr">
         <is>
-          <t>Sifat konfigurasi parameter yang menunjukkan kinerja stabil tidak hanya pada satu titik nilai optimal, tetapi juga pada nilai-nilai di sekitarnya. Strategi yang "robust" bekerja dengan baik meskipun kondisi pasar sedikit berubah atau parameter digeser sedikit — menandakan bahwa kinerja tersebut mencerminkan pola nyata, bukan kecocokan kebetulan. Pada heatmap kinerja, parameter yang robust membentuk "dataran tinggi" yang luas (plateau), bukan "puncak gunung" sempit (fragile peak). Dalam penelitian ini, ATR(7) x Multiplier(3,0) terbukti robust: klaster kinerja optimal mencakup ATR Period 5-9 dan Multiplier 2,5-3,5 — seluruh area ini menghasilkan kinerja kompetitif.</t>
+          <t>Indikator teknikal yang dikembangkan oleh Welles Wilder (1978) yang mengidentifikasi arah tren dan titik pembalikan potensial melalui serangkaian titik-titik kecil yang muncul di atas atau di bawah grafik harga. Saat harga naik, titik-titik muncul di bawah harga (sebagai trailing stop); saat harga turun, titik muncul di atas. Indikator Supertrend adalah "evolusi" dari Parabolic SAR: mempertahankan konsep dasar trailing stop dinamis, namun menambahkan dimensi adaptasi volatilitas melalui ATR — membuat band lebih lebar saat pasar volatile dan lebih sempit saat tenang.</t>
         </is>
       </c>
     </row>
@@ -4861,12 +4861,12 @@
       </c>
       <c r="C193" s="101" t="inlineStr">
         <is>
-          <t>Payoff Ratio</t>
+          <t>Parameter Robustness (Ketangguhan Parameter)</t>
         </is>
       </c>
       <c r="D193" s="101" t="inlineStr">
         <is>
-          <t>Rasio yang membandingkan seberapa besar rata-rata keuntungan yang diperoleh saat transaksi menang, dibanding rata-rata kerugian yang diderita saat transaksi kalah. Payoff Ratio 3,84 dalam penelitian ini berarti: rata-rata setiap transaksi yang berhasil menghasilkan keuntungan 3,84 kali lebih besar dari rata-rata kerugian setiap transaksi yang gagal. Ini adalah ciri khas strategi trend-following yang baik: "loss kecil, win besar." Ketika tren kuat dan panjang tertangkap, keuntungannya besar; ketika sinyal palsu pada kondisi sideways, kerugiannya kecil dan segera di-stop. Kombinasi Payoff Ratio 3,84 dan Win Rate 46,15% menghasilkan ekspektansi positif +$1.228,59 per transaksi.</t>
+          <t>Sifat konfigurasi parameter yang menunjukkan kinerja stabil tidak hanya pada satu titik nilai optimal, tetapi juga pada nilai-nilai di sekitarnya. Strategi yang "robust" bekerja dengan baik meskipun kondisi pasar sedikit berubah atau parameter digeser sedikit — menandakan bahwa kinerja tersebut mencerminkan pola nyata, bukan kecocokan kebetulan. Pada heatmap kinerja, parameter yang robust membentuk "dataran tinggi" yang luas (plateau), bukan "puncak gunung" sempit (fragile peak). Dalam penelitian ini, ATR(7) x Multiplier(3,0) terbukti robust: klaster kinerja optimal mencakup ATR Period 5-9 dan Multiplier 2,5-3,5 — seluruh area ini menghasilkan kinerja kompetitif.</t>
         </is>
       </c>
     </row>
@@ -4881,12 +4881,12 @@
       </c>
       <c r="C194" s="101" t="inlineStr">
         <is>
-          <t>Permutasi (dalam Konteks Monte Carlo)</t>
+          <t>Payoff Ratio</t>
         </is>
       </c>
       <c r="D194" s="101" t="inlineStr">
         <is>
-          <t>Dalam konteks simulasi Monte Carlo Reshuffling, permutasi merujuk pada satu skenario di mana urutan kemunculan 26 transaksi historis diacak secara random — menghasilkan satu equity curve alternatif. Dari 26 transaksi, secara matematis terdapat 26! (sekitar 4 × 10²⁶) kemungkinan urutan yang berbeda. Dalam praktiknya, 2.000 permutasi acak sudah cukup representatif untuk membangun distribusi statistik yang bermakna. Setiap permutasi menjawab pertanyaan: "Bagaimana kinerja sistem jika transaksi-transaksi ini terjadi dalam urutan berbeda?" Jika 90%+ dari 2.000 permutasi tetap menguntungkan (seperti hasil penelitian ini), ini membuktikan bahwa keunggulan strategi berasal dari kualitas transaksi itu sendiri, bukan dari keberuntungan urutan.</t>
+          <t>Rasio yang membandingkan seberapa besar rata-rata keuntungan yang diperoleh saat transaksi menang, dibanding rata-rata kerugian yang diderita saat transaksi kalah. Payoff Ratio 3,84 dalam penelitian ini berarti: rata-rata setiap transaksi yang berhasil menghasilkan keuntungan 3,84 kali lebih besar dari rata-rata kerugian setiap transaksi yang gagal. Ini adalah ciri khas strategi trend-following yang baik: "loss kecil, win besar." Ketika tren kuat dan panjang tertangkap, keuntungannya besar; ketika sinyal palsu pada kondisi sideways, kerugiannya kecil dan segera di-stop. Kombinasi Payoff Ratio 3,84 dan Win Rate 46,15% menghasilkan ekspektansi positif +$1.228,59 per transaksi.</t>
         </is>
       </c>
     </row>
@@ -4901,12 +4901,12 @@
       </c>
       <c r="C195" s="101" t="inlineStr">
         <is>
-          <t>Perpetual Contract (Kontrak Perpetual)</t>
+          <t>Permutasi (dalam Konteks Monte Carlo)</t>
         </is>
       </c>
       <c r="D195" s="101" t="inlineStr">
         <is>
-          <t>Jenis instrumen derivatif futures yang TIDAK memiliki tanggal kadaluwarsa — kontrak dapat dipegang untuk jangka waktu yang tidak terbatas selama ada margin yang cukup dan trader membayar funding rate periodik. Berbeda dari futures konvensional yang harus diselesaikan pada tanggal tertentu. Perpetual contract menjaga harga tetap dekat dengan harga spot melalui mekanisme funding rate — jika harga kontrak lebih tinggi dari spot (banyak yang long), long membayar short; jika lebih rendah (banyak yang short), short membayar long. Mekanisme ini "mendorong" harga kontrak kembali mendekati harga spot secara otomatis.</t>
+          <t>Dalam konteks simulasi Monte Carlo Reshuffling, permutasi merujuk pada satu skenario di mana urutan kemunculan 26 transaksi historis diacak secara random — menghasilkan satu equity curve alternatif. Dari 26 transaksi, secara matematis terdapat 26! (sekitar 4 × 10²⁶) kemungkinan urutan yang berbeda. Dalam praktiknya, 2.000 permutasi acak sudah cukup representatif untuk membangun distribusi statistik yang bermakna. Setiap permutasi menjawab pertanyaan: "Bagaimana kinerja sistem jika transaksi-transaksi ini terjadi dalam urutan berbeda?" Jika 90%+ dari 2.000 permutasi tetap menguntungkan (seperti hasil penelitian ini), ini membuktikan bahwa keunggulan strategi berasal dari kualitas transaksi itu sendiri, bukan dari keberuntungan urutan.</t>
         </is>
       </c>
     </row>
@@ -4921,12 +4921,12 @@
       </c>
       <c r="C196" s="101" t="inlineStr">
         <is>
-          <t>Perpetual Futures</t>
+          <t>Perpetual Contract (Kontrak Perpetual)</t>
         </is>
       </c>
       <c r="D196" s="101" t="inlineStr">
         <is>
-          <t>Lihat: Perpetual Contract (Kontrak Perpetual). Istilah umum untuk kontrak futures tanpa tanggal kadaluwarsa yang dapat dipegang selama trader membayar funding rate periodik. Jenis instrumen derivatif paling populer di pasar kripto karena fleksibilitasnya. Dalam penelitian ini, BTC/USDT Perpetual Futures di Bybit adalah instrumen utama yang digunakan — dipilih karena memungkinkan posisi ditahan selama tren berlangsung tanpa batas waktu, sesuai dengan filosofi trend-following strategi Supertrend. Lihat juga: Perpetual Contract, Funding Rate, BTC/USDT.</t>
+          <t>Jenis instrumen derivatif futures yang TIDAK memiliki tanggal kadaluwarsa — kontrak dapat dipegang untuk jangka waktu yang tidak terbatas selama ada margin yang cukup dan trader membayar funding rate periodik. Berbeda dari futures konvensional yang harus diselesaikan pada tanggal tertentu. Perpetual contract menjaga harga tetap dekat dengan harga spot melalui mekanisme funding rate — jika harga kontrak lebih tinggi dari spot (banyak yang long), long membayar short; jika lebih rendah (banyak yang short), short membayar long. Mekanisme ini "mendorong" harga kontrak kembali mendekati harga spot secara otomatis.</t>
         </is>
       </c>
     </row>
@@ -4941,12 +4941,12 @@
       </c>
       <c r="C197" s="101" t="inlineStr">
         <is>
-          <t>Pine Script</t>
+          <t>Perpetual Futures</t>
         </is>
       </c>
       <c r="D197" s="101" t="inlineStr">
         <is>
-          <t>Bahasa pemrograman yang dikembangkan khusus oleh TradingView untuk membuat indikator teknikal dan strategi perdagangan yang dapat divisualisasikan langsung di grafik harga interaktif. Pine Script dirancang agar mudah dipahami bahkan oleh pengguna yang bukan programmer profesional. Fitur unggulannya: kode langsung berjalan di grafik TradingView secara real-time dan bisa mengirimkan perintah ke bursa melalui webhook. Dalam penelitian ini, Pine Script v5 digunakan sebagai implementasi alternatif sistem Supertrend untuk live trading: kode Pine Script mendeteksi sinyal Supertrend di TradingView dan secara otomatis mengirimkan perintah ke akun Bybit melalui webhook — semua tanpa intervensi manual.</t>
+          <t>Lihat: Perpetual Contract (Kontrak Perpetual). Istilah umum untuk kontrak futures tanpa tanggal kadaluwarsa yang dapat dipegang selama trader membayar funding rate periodik. Jenis instrumen derivatif paling populer di pasar kripto karena fleksibilitasnya. Dalam penelitian ini, BTC/USDT Perpetual Futures di Bybit adalah instrumen utama yang digunakan — dipilih karena memungkinkan posisi ditahan selama tren berlangsung tanpa batas waktu, sesuai dengan filosofi trend-following strategi Supertrend. Lihat juga: Perpetual Contract, Funding Rate, BTC/USDT.</t>
         </is>
       </c>
     </row>
@@ -4961,12 +4961,12 @@
       </c>
       <c r="C198" s="101" t="inlineStr">
         <is>
-          <t>Pipeline (Alur Pemrosesan)</t>
+          <t>Pine Script</t>
         </is>
       </c>
       <c r="D198" s="101" t="inlineStr">
         <is>
-          <t>Serangkaian tahapan pemrosesan yang dieksekusi secara berurutan di mana output setiap tahap menjadi input tahap berikutnya — seperti jalur produksi pabrik. Dalam sistem Supertrend penelitian ini, pipeline terdiri dari: (1) Pengambilan data OHLCV via Bybit API; (2) Kalkulasi ATR menggunakan Wilder Smoothing; (3) Kalkulasi Basic Bands dan penerapan mekanisme Sticky Band untuk menghasilkan band final; (4) Deteksi sinyal beli/jual berdasarkan kondisi penembusan band; (5) Kalkulasi ukuran posisi menggunakan Fixed Fractional; dan (6) Eksekusi order atau pencatatan transaksi dalam log.</t>
+          <t>Bahasa pemrograman yang dikembangkan khusus oleh TradingView untuk membuat indikator teknikal dan strategi perdagangan yang dapat divisualisasikan langsung di grafik harga interaktif. Pine Script dirancang agar mudah dipahami bahkan oleh pengguna yang bukan programmer profesional. Fitur unggulannya: kode langsung berjalan di grafik TradingView secara real-time dan bisa mengirimkan perintah ke bursa melalui webhook. Dalam penelitian ini, Pine Script v5 digunakan sebagai implementasi alternatif sistem Supertrend untuk live trading: kode Pine Script mendeteksi sinyal Supertrend di TradingView dan secara otomatis mengirimkan perintah ke akun Bybit melalui webhook — semua tanpa intervensi manual.</t>
         </is>
       </c>
     </row>
@@ -4981,12 +4981,12 @@
       </c>
       <c r="C199" s="101" t="inlineStr">
         <is>
-          <t>Position Size (Ukuran Posisi)</t>
+          <t>Pipeline (Alur Pemrosesan)</t>
         </is>
       </c>
       <c r="D199" s="101" t="inlineStr">
         <is>
-          <t>Jumlah konkret Bitcoin (dalam satuan BTC) yang dibeli atau dijual dalam satu transaksi — output dari kalkulasi Fixed Fractional Position Sizing. Rumusnya: (Ekuitas x Risk per Trade) dibagi Jarak Stop-Loss. Misalnya: ekuitas $10.000, Risk 5% = $500, jarak stop-loss $2.000 per BTC, maka Position Size = 0,25 BTC. Ukuran ini berbeda-beda setiap transaksi: saat ekuitas besar dan stop-loss dekat, posisi besar; saat ekuitas kecil atau volatilitas tinggi (stop-loss jauh), posisi kecil. Dinamisitas inilah yang membuat Fixed Fractional unggul dibanding Fixed Lot.</t>
+          <t>Serangkaian tahapan pemrosesan yang dieksekusi secara berurutan di mana output setiap tahap menjadi input tahap berikutnya — seperti jalur produksi pabrik. Dalam sistem Supertrend penelitian ini, pipeline terdiri dari: (1) Pengambilan data OHLCV via Bybit API; (2) Kalkulasi ATR menggunakan Wilder Smoothing; (3) Kalkulasi Basic Bands dan penerapan mekanisme Sticky Band untuk menghasilkan band final; (4) Deteksi sinyal beli/jual berdasarkan kondisi penembusan band; (5) Kalkulasi ukuran posisi menggunakan Fixed Fractional; dan (6) Eksekusi order atau pencatatan transaksi dalam log.</t>
         </is>
       </c>
     </row>
@@ -5001,12 +5001,12 @@
       </c>
       <c r="C200" s="101" t="inlineStr">
         <is>
-          <t>Positive Drift (Kecenderungan Naik Jangka Panjang)</t>
+          <t>Position Size (Ukuran Posisi)</t>
         </is>
       </c>
       <c r="D200" s="101" t="inlineStr">
         <is>
-          <t>Kecenderungan intrinsik suatu aset untuk bergerak naik secara sistematis dalam jangka panjang, terlepas dari fluktuasi jangka pendek yang naik-turun. Bitcoin memiliki positive drift yang sangat kuat secara historis: dari sekitar $7.200 di awal 2020 menjadi lebih dari $95.000 di akhir 2025 — kenaikan lebih dari 1.200% dalam 5 tahun, meskipun mengalami banyak penurunan tajam di antaranya. Positive drift menjadi fondasi utama pemilihan strategi long-only dalam penelitian ini: karena Bitcoin cenderung naik jangka panjang, lebih logis untuk "mengikuti arus" naik daripada melawan tren jangka panjang dengan short selling.</t>
+          <t>Jumlah konkret Bitcoin (dalam satuan BTC) yang dibeli atau dijual dalam satu transaksi — output dari kalkulasi Fixed Fractional Position Sizing. Rumusnya: (Ekuitas x Risk per Trade) dibagi Jarak Stop-Loss. Misalnya: ekuitas $10.000, Risk 5% = $500, jarak stop-loss $2.000 per BTC, maka Position Size = 0,25 BTC. Ukuran ini berbeda-beda setiap transaksi: saat ekuitas besar dan stop-loss dekat, posisi besar; saat ekuitas kecil atau volatilitas tinggi (stop-loss jauh), posisi kecil. Dinamisitas inilah yang membuat Fixed Fractional unggul dibanding Fixed Lot.</t>
         </is>
       </c>
     </row>
@@ -5021,12 +5021,12 @@
       </c>
       <c r="C201" s="101" t="inlineStr">
         <is>
-          <t>Positive Long-Term Drift</t>
+          <t>Positive Drift (Kecenderungan Naik Jangka Panjang)</t>
         </is>
       </c>
       <c r="D201" s="101" t="inlineStr">
         <is>
-          <t>Lihat: Positive Drift (Kecenderungan Naik Jangka Panjang) di Huruf P (No. 173). Sinonim yang merujuk pada sifat yang sama: kecenderungan harga Bitcoin untuk naik secara sistematis dalam jangka panjang — dari sekitar $7.200 awal 2020 hingga melampaui $95.000 di akhir 2025 (kenaikan lebih dari 1.200%) — yang menjadi fondasi utama pemilihan strategi long-only dalam penelitian ini.</t>
+          <t>Kecenderungan intrinsik suatu aset untuk bergerak naik secara sistematis dalam jangka panjang, terlepas dari fluktuasi jangka pendek yang naik-turun. Bitcoin memiliki positive drift yang sangat kuat secara historis: dari sekitar $7.200 di awal 2020 menjadi lebih dari $95.000 di akhir 2025 — kenaikan lebih dari 1.200% dalam 5 tahun, meskipun mengalami banyak penurunan tajam di antaranya. Positive drift menjadi fondasi utama pemilihan strategi long-only dalam penelitian ini: karena Bitcoin cenderung naik jangka panjang, lebih logis untuk "mengikuti arus" naik daripada melawan tren jangka panjang dengan short selling.</t>
         </is>
       </c>
     </row>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="C202" s="101" t="inlineStr">
         <is>
-          <t>Probability of Ruin (Probabilitas Kebangkrutan)</t>
+          <t>Positive Long-Term Drift</t>
         </is>
       </c>
       <c r="D202" s="101" t="inlineStr">
         <is>
-          <t>Probabilitas bahwa sebuah strategi perdagangan akan menguras habis modal secara permanen akibat serangkaian kerugian yang tidak terkendali. Ini adalah metrik risiko eksistensial yang paling fundamental: tidak ada gunanya membahas potensi keuntungan apapun jika ada kemungkinan nyata modal habis sebelum strategi bisa membuktikan keunggulannya. Dalam penelitian ini, probability of ruin diuji melalui simulasi Monte Carlo dengan mengacak urutan 26 transaksi historis sebanyak 2.000 kali. Hasilnya: 0 dari 2.000 simulasi menghasilkan kebangkrutan total — probability of ruin = 0%, membuktikan ketahanan fundamental sistem.</t>
+          <t>Lihat: Positive Drift (Kecenderungan Naik Jangka Panjang) di Huruf P (No. 173). Sinonim yang merujuk pada sifat yang sama: kecenderungan harga Bitcoin untuk naik secara sistematis dalam jangka panjang — dari sekitar $7.200 awal 2020 hingga melampaui $95.000 di akhir 2025 (kenaikan lebih dari 1.200%) — yang menjadi fondasi utama pemilihan strategi long-only dalam penelitian ini.</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="C203" s="101" t="inlineStr">
         <is>
-          <t>Production-Ready (Siap Produksi)</t>
+          <t>Probability of Ruin (Probabilitas Kebangkrutan)</t>
         </is>
       </c>
       <c r="D203" s="101" t="inlineStr">
         <is>
-          <t>Status sebuah sistem perangkat lunak yang sudah memenuhi semua standar kualitas, keandalan, keamanan, dan ketahanan untuk beroperasi penuh di lingkungan nyata dengan risiko modal sungguhan — mampu menangani koneksi terputus, API tidak merespons, data hilang, dan kondisi pasar ekstrem dengan penanganan error yang tepat. Dalam penelitian ini, implementasi Python Tradingbot dan Pine Script v5 dikategorikan sebagai proof-of-concept (bukti konsep), BUKAN production-ready — masih memerlukan penambahan penanganan error yang lebih robust dan audit keamanan sebelum digunakan dalam skala komersial.</t>
+          <t>Probabilitas bahwa sebuah strategi perdagangan akan menguras habis modal secara permanen akibat serangkaian kerugian yang tidak terkendali. Ini adalah metrik risiko eksistensial yang paling fundamental: tidak ada gunanya membahas potensi keuntungan apapun jika ada kemungkinan nyata modal habis sebelum strategi bisa membuktikan keunggulannya. Dalam penelitian ini, probability of ruin diuji melalui simulasi Monte Carlo dengan mengacak urutan 26 transaksi historis sebanyak 2.000 kali. Hasilnya: 0 dari 2.000 simulasi menghasilkan kebangkrutan total — probability of ruin = 0%, membuktikan ketahanan fundamental sistem.</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C204" s="101" t="inlineStr">
         <is>
-          <t>Profit Factor</t>
+          <t>Production-Ready (Siap Produksi)</t>
         </is>
       </c>
       <c r="D204" s="101" t="inlineStr">
         <is>
-          <t>Rasio antara total keuntungan kotor (dari semua transaksi yang menang) dan total kerugian kotor (dari semua transaksi yang kalah). Nilai lebih dari 1,0 berarti sistem menguntungkan; lebih dari 2,0 dianggap sistem yang kuat dalam literatur perdagangan. Profit Factor memberikan gambaran "efisiensi gross": untuk setiap $1 yang hilang dari transaksi kalah, berapa $-nya yang diperoleh dari transaksi menang? Dalam penelitian ini, Profit Factor sebesar 3,0 berarti setiap $1 total kerugian diimbangi oleh $3 total keuntungan — margin keamanan yang sangat memadai.</t>
+          <t>Status sebuah sistem perangkat lunak yang sudah memenuhi semua standar kualitas, keandalan, keamanan, dan ketahanan untuk beroperasi penuh di lingkungan nyata dengan risiko modal sungguhan — mampu menangani koneksi terputus, API tidak merespons, data hilang, dan kondisi pasar ekstrem dengan penanganan error yang tepat. Dalam penelitian ini, implementasi Python Tradingbot dan Pine Script v5 dikategorikan sebagai proof-of-concept (bukti konsep), BUKAN production-ready — masih memerlukan penambahan penanganan error yang lebih robust dan audit keamanan sebelum digunakan dalam skala komersial.</t>
         </is>
       </c>
     </row>
@@ -5101,12 +5101,12 @@
       </c>
       <c r="C205" s="101" t="inlineStr">
         <is>
-          <t>Profit Giveback (Pengembalian Keuntungan)</t>
+          <t>Profit Factor</t>
         </is>
       </c>
       <c r="D205" s="101" t="inlineStr">
         <is>
-          <t>Fenomena tak terhindarkan dalam strategi trend-following: karena indikator bersifat lagging (tertinggal), sistem tidak bisa menjual di puncak tertinggi. Saat harga naik lama kemudian mulai berbalik turun, sistem baru mendapat sinyal jual setelah harga sudah turun cukup jauh dari puncak — "mengembalikan" sebagian keuntungan yang sudah terkumpul. Ini seperti investor yang terlambat keluar dari investasi — sudah untung besar, tapi profit berkurang karena terlambat menjual. Multiplier = 3,0 dalam penelitian ini adalah keseimbangan optimal: cukup besar untuk tidak "panik menjual" saat koreksi kecil, namun tidak terlalu besar sehingga "mengembalikan" terlalu banyak keuntungan.</t>
+          <t>Rasio antara total keuntungan kotor (dari semua transaksi yang menang) dan total kerugian kotor (dari semua transaksi yang kalah). Nilai lebih dari 1,0 berarti sistem menguntungkan; lebih dari 2,0 dianggap sistem yang kuat dalam literatur perdagangan. Profit Factor memberikan gambaran "efisiensi gross": untuk setiap $1 yang hilang dari transaksi kalah, berapa $-nya yang diperoleh dari transaksi menang? Dalam penelitian ini, Profit Factor sebesar 3,0 berarti setiap $1 total kerugian diimbangi oleh $3 total keuntungan — margin keamanan yang sangat memadai.</t>
         </is>
       </c>
     </row>
@@ -5121,12 +5121,12 @@
       </c>
       <c r="C206" s="101" t="inlineStr">
         <is>
-          <t>Proof-of-Concept (PoC)</t>
+          <t>Profit Giveback (Pengembalian Keuntungan)</t>
         </is>
       </c>
       <c r="D206" s="101" t="inlineStr">
         <is>
-          <t>Demonstrasi awal yang bertujuan membuktikan bahwa sebuah ide secara teknis dan konseptual dapat bekerja — tanpa harus memenuhi semua standar sistem produksi penuh. PoC menjawab "apakah ini mungkin?" sebelum investasi besar dalam pengembangan penuh. Dalam penelitian ini, seluruh implementasi sistem Supertrend dikategorikan sebagai PoC: membuktikan bahwa sinyal Supertrend bisa (1) dihitung otomatis dari data API, (2) menghasilkan sinyal yang valid, (3) dieksekusi di bursa nyata, dan (4) menghasilkan kinerja yang terukur. Langkah selanjutnya adalah mengembangkan PoC ini menjadi sistem yang lebih matang dan production-ready.</t>
+          <t>Fenomena tak terhindarkan dalam strategi trend-following: karena indikator bersifat lagging (tertinggal), sistem tidak bisa menjual di puncak tertinggi. Saat harga naik lama kemudian mulai berbalik turun, sistem baru mendapat sinyal jual setelah harga sudah turun cukup jauh dari puncak — "mengembalikan" sebagian keuntungan yang sudah terkumpul. Ini seperti investor yang terlambat keluar dari investasi — sudah untung besar, tapi profit berkurang karena terlambat menjual. Multiplier = 3,0 dalam penelitian ini adalah keseimbangan optimal: cukup besar untuk tidak "panik menjual" saat koreksi kecil, namun tidak terlalu besar sehingga "mengembalikan" terlalu banyak keuntungan.</t>
         </is>
       </c>
     </row>
@@ -5141,12 +5141,12 @@
       </c>
       <c r="C207" s="101" t="inlineStr">
         <is>
-          <t>Pure Supertrend</t>
+          <t>Proof-of-Concept (PoC)</t>
         </is>
       </c>
       <c r="D207" s="101" t="inlineStr">
         <is>
-          <t>Implementasi strategi Supertrend tanpa filter indikator teknikal tambahan (RSI, MACD, ADX, Bollinger Bands, atau indikator lainnya) — hanya menggunakan sinyal Supertrend murni yang dikombinasikan dengan manajemen risiko Fixed Fractional. Pilihan metodologis yang disengaja dalam penelitian ini: dengan mengisolasi Supertrend dari filter lain, kontribusi murni indikator Supertrend dapat diukur secara objektif. Hasil penelitian membuktikan bahwa Pure Supertrend + Fixed Fractional sudah cukup robust tanpa filter tambahan. Lihat juga: ADX, RSI, MACD, Algorithmic Trading.</t>
+          <t>Demonstrasi awal yang bertujuan membuktikan bahwa sebuah ide secara teknis dan konseptual dapat bekerja — tanpa harus memenuhi semua standar sistem produksi penuh. PoC menjawab "apakah ini mungkin?" sebelum investasi besar dalam pengembangan penuh. Dalam penelitian ini, seluruh implementasi sistem Supertrend dikategorikan sebagai PoC: membuktikan bahwa sinyal Supertrend bisa (1) dihitung otomatis dari data API, (2) menghasilkan sinyal yang valid, (3) dieksekusi di bursa nyata, dan (4) menghasilkan kinerja yang terukur. Langkah selanjutnya adalah mengembangkan PoC ini menjadi sistem yang lebih matang dan production-ready.</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="C208" s="101" t="inlineStr">
         <is>
-          <t>Python Libraries (Pustaka Python)</t>
+          <t>Pure Supertrend</t>
         </is>
       </c>
       <c r="D208" s="101" t="inlineStr">
         <is>
-          <t>Kumpulan modul pemrograman eksternal (seperti pandas, numpy, matplotlib, seaborn, requests, scipy, statsmodels) yang diimpor ke dalam program untuk memfasilitasi analisis data deret waktu, kalkulasi statistik, dan visualisasi grafik.</t>
+          <t>Implementasi strategi Supertrend tanpa filter indikator teknikal tambahan (RSI, MACD, ADX, Bollinger Bands, atau indikator lainnya) — hanya menggunakan sinyal Supertrend murni yang dikombinasikan dengan manajemen risiko Fixed Fractional. Pilihan metodologis yang disengaja dalam penelitian ini: dengan mengisolasi Supertrend dari filter lain, kontribusi murni indikator Supertrend dapat diukur secara objektif. Hasil penelitian membuktikan bahwa Pure Supertrend + Fixed Fractional sudah cukup robust tanpa filter tambahan. Lihat juga: ADX, RSI, MACD, Algorithmic Trading.</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="C209" s="101" t="inlineStr">
         <is>
-          <t>Python Tradingbot (Bot Perdagangan Python)</t>
+          <t>Python Libraries (Pustaka Python)</t>
         </is>
       </c>
       <c r="D209" s="101" t="inlineStr">
         <is>
-          <t>Komponen inti penelitian ini — program komputer berbentuk Jupyter Notebook (file .ipynb yang bisa dijalankan secara interaktif) yang mengimplementasikan seluruh sistem Supertrend dalam bahasa pemrograman Python. Ditetapkan sebagai SSOT (Single Source of Truth), artinya semua angka, grafik, dan kesimpulan dalam penelitian bersumber dari satu kode yang sama dan dapat direproduksi secara independen. Notebook ini mencakup tujuh modul: pengambilan data dari Bybit API, kalkulasi Supertrend, backtesting bar-by-bar, 3D Grid Search untuk optimasi parameter, Walk-Forward Analysis, simulasi Monte Carlo dan Bootstrap, serta Scorecard kinerja otomatis.</t>
+          <t>Kumpulan modul pemrograman eksternal (seperti pandas, numpy, matplotlib, seaborn, requests, scipy, statsmodels) yang diimpor ke dalam program untuk memfasilitasi analisis data deret waktu, kalkulasi statistik, dan visualisasi grafik.</t>
         </is>
       </c>
     </row>
@@ -5196,17 +5196,17 @@
       </c>
       <c r="B210" s="108" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C210" s="101" t="inlineStr">
         <is>
-          <t>RAO Score (Risk-Adjusted Optimization Score)</t>
+          <t>Python Tradingbot (Bot Perdagangan Python)</t>
         </is>
       </c>
       <c r="D210" s="101" t="inlineStr">
         <is>
-          <t>Metrik komposit yang dikembangkan khusus dalam penelitian ini untuk mengevaluasi kombinasi parameter secara komprehensif — tidak hanya berdasarkan satu metrik tunggal. Formula: 35% Sharpe Ratio + 25% Calmar Ratio + 20% Sortino Ratio + 10% Win Rate + 10% Profit Factor. Mengapa tidak sekadar pilih yang Sharpe Ratio tertinggi? Karena Sharpe Ratio tertinggi bisa berasal dari kombinasi dengan drawdown sangat besar atau win rate sangat rendah. RAO Score memastikan parameter yang dipilih seimbang dan baik di SEMUA dimensi risiko dan return — bukan jagoan di satu aspek namun lemah di aspek lain.</t>
+          <t>Komponen inti penelitian ini — program komputer berbentuk Jupyter Notebook (file .ipynb yang bisa dijalankan secara interaktif) yang mengimplementasikan seluruh sistem Supertrend dalam bahasa pemrograman Python. Ditetapkan sebagai SSOT (Single Source of Truth), artinya semua angka, grafik, dan kesimpulan dalam penelitian bersumber dari satu kode yang sama dan dapat direproduksi secara independen. Notebook ini mencakup tujuh modul: pengambilan data dari Bybit API, kalkulasi Supertrend, backtesting bar-by-bar, 3D Grid Search untuk optimasi parameter, Walk-Forward Analysis, simulasi Monte Carlo dan Bootstrap, serta Scorecard kinerja otomatis.</t>
         </is>
       </c>
     </row>
@@ -5221,12 +5221,12 @@
       </c>
       <c r="C211" s="101" t="inlineStr">
         <is>
-          <t>Real-Time</t>
+          <t>RAO Score (Risk-Adjusted Optimization Score)</t>
         </is>
       </c>
       <c r="D211" s="101" t="inlineStr">
         <is>
-          <t>Pemrosesan atau eksekusi yang terjadi dengan latensi sangat minimal, mendekati waktu kejadian sesungguhnya. Dalam konteks sistem perdagangan algoritmik, real-time berarti sinyal dideteksi dan order dikirim dalam hitungan detik setelah kondisi pasar terpenuhi. Dalam penelitian ini, komponen real-time diimplementasikan oleh Pine Script v5 di TradingView: setiap detik TradingView memperbarui grafik dengan data terbaru dari Bybit, dan ketika candle harian ditutup serta kondisi Supertrend terpenuhi, webhook langsung dikirim ke API Bybit — seluruh proses dari deteksi sinyal ke order terkirim memakan waktu di bawah 5 detik. Lihat juga: Pine Script, Webhook, TradingView, Live Trading.</t>
+          <t>Metrik komposit yang dikembangkan khusus dalam penelitian ini untuk mengevaluasi kombinasi parameter secara komprehensif — tidak hanya berdasarkan satu metrik tunggal. Formula: 35% Sharpe Ratio + 25% Calmar Ratio + 20% Sortino Ratio + 10% Win Rate + 10% Profit Factor. Mengapa tidak sekadar pilih yang Sharpe Ratio tertinggi? Karena Sharpe Ratio tertinggi bisa berasal dari kombinasi dengan drawdown sangat besar atau win rate sangat rendah. RAO Score memastikan parameter yang dipilih seimbang dan baik di SEMUA dimensi risiko dan return — bukan jagoan di satu aspek namun lemah di aspek lain.</t>
         </is>
       </c>
     </row>
@@ -5241,10 +5241,30 @@
       </c>
       <c r="C212" s="101" t="inlineStr">
         <is>
+          <t>Real-Time</t>
+        </is>
+      </c>
+      <c r="D212" s="101" t="inlineStr">
+        <is>
+          <t>Pemrosesan atau eksekusi yang terjadi dengan latensi sangat minimal, mendekati waktu kejadian sesungguhnya. Dalam konteks sistem perdagangan algoritmik, real-time berarti sinyal dideteksi dan order dikirim dalam hitungan detik setelah kondisi pasar terpenuhi. Dalam penelitian ini, komponen real-time diimplementasikan oleh Pine Script v5 di TradingView: setiap detik TradingView memperbarui grafik dengan data terbaru dari Bybit, dan ketika candle harian ditutup serta kondisi Supertrend terpenuhi, webhook langsung dikirim ke API Bybit — seluruh proses dari deteksi sinyal ke order terkirim memakan waktu di bawah 5 detik. Lihat juga: Pine Script, Webhook, TradingView, Live Trading.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="122.5" customHeight="1" s="44">
+      <c r="A213" s="107" t="n">
+        <v>210</v>
+      </c>
+      <c r="B213" s="108" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C213" s="101" t="inlineStr">
+        <is>
           <t>Regime Pasar (Market Regime)</t>
         </is>
       </c>
-      <c r="D212" s="101" t="inlineStr">
+      <c r="D213" s="101" t="inlineStr">
         <is>
           <t>Klasifikasi kondisi pasar ke dalam kategori-kategori berbeda berdasarkan kombinasi arah tren dan tingkat volatilitas. Konsep ini penting karena strategi berbeda bekerja dengan baik pada regime yang berbeda: Supertrend bekerja optimal saat pasar bertren jelas, namun buruk saat pasar mendatar tanpa arah. Dalam penelitian ini, pasar diklasifikasikan ke dalam 8 sub-kategori berdasarkan dua dimensi: (1) arah tren (Bull/Bear/Sideways/Unknown berdasarkan posisi harga relatif terhadap MA50) dan (2) tingkat volatilitas (HighVol/LowVol). Analisis ini memungkinkan pemahaman mendalam tentang dalam kondisi apa strategi Supertrend bekerja terbaik dan terburuk.',
 - 'Bull-LowVol': 'Kondisi pasar tren naik dengan volatilitas rendah — kondisi TERBAIK untuk strategi Supertrend long-only: tren naik yang konsisten dan halus memungkinkan posisi dipertahankan lama dengan stop-loss yang tidak mudah tersentuh.',
@@ -5258,26 +5278,6 @@
         </is>
       </c>
     </row>
-    <row r="213" ht="122.5" customHeight="1" s="44">
-      <c r="A213" s="107" t="n">
-        <v>210</v>
-      </c>
-      <c r="B213" s="108" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="C213" s="101" t="inlineStr">
-        <is>
-          <t>Resampling (Pengambilan Sampel Ulang)</t>
-        </is>
-      </c>
-      <c r="D213" s="101" t="inlineStr">
-        <is>
-          <t>Teknik statistik yang menghasilkan banyak "dataset tiruan" dari data asli yang sama, dengan cara mengambil sampel secara berulang-ulang untuk memperkirakan distribusi metrik statistik tanpa mengasumsikan distribusi tertentu. Bayangkan punya kantong 26 kelereng dan ingin tahu rata-rata ukurannya secara akurat — Anda ambil 26 kelereng acak (dengan mengembalikan setiap kelereng), catat rata-ratanya, ulangi 2.000 kali. Persebaran 2.000 nilai rata-rata memberikan gambaran ketidakpastian estimasi. Dalam penelitian ini, resampling diterapkan melalui Bootstrap (untuk CI metrik kinerja) dan Monte Carlo (untuk probability of ruin).</t>
-        </is>
-      </c>
-    </row>
     <row r="214" ht="122.5" customHeight="1" s="44">
       <c r="A214" s="107" t="n">
         <v>211</v>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="C214" s="101" t="inlineStr">
         <is>
-          <t>Risk per Trade</t>
+          <t>Resampling (Pengambilan Sampel Ulang)</t>
         </is>
       </c>
       <c r="D214" s="101" t="inlineStr">
         <is>
-          <t>Parameter ketiga dari tiga parameter utama sistem, sekaligus parameter manajemen risiko yang paling fundamental: persentase dari total ekuitas yang bersedia dikorbankan jika stop-loss tersentuh dalam satu transaksi. Contoh: Risk per Trade 5% dengan modal $10.000 berarti kerugian maksimal $500 per transaksi. Jika pada transaksi berikutnya modal sudah jadi $9.500, kerugian maksimal berikutnya adalah $475 (5% dari $9.500) — selalu proporsional terhadap modal yang ada. Dalam penelitian ini, setelah menguji nilai 1% hingga 5%, Risk per Trade = 5% ditemukan sebagai nilai optimal yang menghasilkan pertumbuhan modal terbaik sekaligus drawdown yang terkontrol.</t>
+          <t>Teknik statistik yang menghasilkan banyak "dataset tiruan" dari data asli yang sama, dengan cara mengambil sampel secara berulang-ulang untuk memperkirakan distribusi metrik statistik tanpa mengasumsikan distribusi tertentu. Bayangkan punya kantong 26 kelereng dan ingin tahu rata-rata ukurannya secara akurat — Anda ambil 26 kelereng acak (dengan mengembalikan setiap kelereng), catat rata-ratanya, ulangi 2.000 kali. Persebaran 2.000 nilai rata-rata memberikan gambaran ketidakpastian estimasi. Dalam penelitian ini, resampling diterapkan melalui Bootstrap (untuk CI metrik kinerja) dan Monte Carlo (untuk probability of ruin).</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5309,12 @@
       </c>
       <c r="C215" s="101" t="inlineStr">
         <is>
-          <t>Risk-Adjusted Return</t>
+          <t>Risk per Trade</t>
         </is>
       </c>
       <c r="D215" s="101" t="inlineStr">
         <is>
-          <t>Keuntungan yang dinormalisasi terhadap tingkat risiko yang diambil untuk menghasilkannya — memberikan perbandingan yang lebih adil antar strategi daripada membandingkan return mentah saja. Logikanya: strategi yang menghasilkan 30% per tahun dengan drawdown 10% jauh lebih baik dari strategi 35% per tahun dengan drawdown 70%. Berbagai metrik mengukur risk-adjusted return dengan definisi risiko yang berbeda: Sharpe Ratio menggunakan deviasi standar total, Sortino Ratio menggunakan downside deviation, dan Calmar Ratio menggunakan Maximum Drawdown. Dalam penelitian ini, Calmar Ratio menjadi metrik risk-adjusted return yang paling membedakan: Supertrend +0,9533 vs Buy &amp; Hold +0,6481. Lihat juga: Sharpe Ratio, Sortino Ratio, Calmar Ratio.</t>
+          <t>Parameter ketiga dari tiga parameter utama sistem, sekaligus parameter manajemen risiko yang paling fundamental: persentase dari total ekuitas yang bersedia dikorbankan jika stop-loss tersentuh dalam satu transaksi. Contoh: Risk per Trade 5% dengan modal $10.000 berarti kerugian maksimal $500 per transaksi. Jika pada transaksi berikutnya modal sudah jadi $9.500, kerugian maksimal berikutnya adalah $475 (5% dari $9.500) — selalu proporsional terhadap modal yang ada. Dalam penelitian ini, setelah menguji nilai 1% hingga 5%, Risk per Trade = 5% ditemukan sebagai nilai optimal yang menghasilkan pertumbuhan modal terbaik sekaligus drawdown yang terkontrol.</t>
         </is>
       </c>
     </row>
@@ -5329,12 +5329,12 @@
       </c>
       <c r="C216" s="101" t="inlineStr">
         <is>
-          <t>Risk-Free Rate (Tingkat Imbal Hasil Bebas Risiko)</t>
+          <t>Risk-Adjusted Return</t>
         </is>
       </c>
       <c r="D216" s="101" t="inlineStr">
         <is>
-          <t>Tingkat keuntungan teoritis dari investasi yang dianggap sepenuhnya bebas risiko — biasanya imbal hasil obligasi pemerintah jangka pendek. Risk-free rate digunakan sebagai "baseline minimum" dalam perhitungan Sharpe Ratio dan Sortino Ratio: strategi apapun seharusnya menghasilkan lebih dari ini, karena jika tidak, investor lebih baik menyimpan uang di instrumen bebas risiko. Dalam penelitian ini, risk-free rate ditetapkan 0% sesuai konvensi yang umum digunakan dalam literatur aset kripto — karena investasi yang benar-benar bebas risiko di ekosistem kripto dianggap tidak ada yang relevan secara langsung.</t>
+          <t>Keuntungan yang dinormalisasi terhadap tingkat risiko yang diambil untuk menghasilkannya — memberikan perbandingan yang lebih adil antar strategi daripada membandingkan return mentah saja. Logikanya: strategi yang menghasilkan 30% per tahun dengan drawdown 10% jauh lebih baik dari strategi 35% per tahun dengan drawdown 70%. Berbagai metrik mengukur risk-adjusted return dengan definisi risiko yang berbeda: Sharpe Ratio menggunakan deviasi standar total, Sortino Ratio menggunakan downside deviation, dan Calmar Ratio menggunakan Maximum Drawdown. Dalam penelitian ini, Calmar Ratio menjadi metrik risk-adjusted return yang paling membedakan: Supertrend +0,9533 vs Buy &amp; Hold +0,6481. Lihat juga: Sharpe Ratio, Sortino Ratio, Calmar Ratio.</t>
         </is>
       </c>
     </row>
@@ -5349,12 +5349,12 @@
       </c>
       <c r="C217" s="101" t="inlineStr">
         <is>
-          <t>RMA (Running Moving Average)</t>
+          <t>Risk-Free Rate (Tingkat Imbal Hasil Bebas Risiko)</t>
         </is>
       </c>
       <c r="D217" s="101" t="inlineStr">
         <is>
-          <t>Lihat: Wilder Smoothing (RMA) di Huruf W. Singkatan dari Running Moving Average — metode pemulusan rata-rata bergerak yang diperkenalkan oleh Welles Wilder (1978) dan digunakan secara konsisten dalam penelitian ini untuk menghitung ATR pada kedua implementasi: Python Tradingbot (SSOT) maupun Pine Script v5 (melalui fungsi bawaan ta.atr()). Secara matematis identik dengan EMA namun dengan faktor pemulusan α = 1/n (lebih kecil dari EMA konvensional yang menggunakan 2/(n+1)), sehingga menghasilkan estimasi volatilitas yang lebih stabil tanpa efek 'drop-off' saat data lama keluar dari jendela perhitungan. Lihat juga: ATR, Wilder Smoothing (RMA), EMA.</t>
+          <t>Tingkat keuntungan teoritis dari investasi yang dianggap sepenuhnya bebas risiko — biasanya imbal hasil obligasi pemerintah jangka pendek. Risk-free rate digunakan sebagai "baseline minimum" dalam perhitungan Sharpe Ratio dan Sortino Ratio: strategi apapun seharusnya menghasilkan lebih dari ini, karena jika tidak, investor lebih baik menyimpan uang di instrumen bebas risiko. Dalam penelitian ini, risk-free rate ditetapkan 0% sesuai konvensi yang umum digunakan dalam literatur aset kripto — karena investasi yang benar-benar bebas risiko di ekosistem kripto dianggap tidak ada yang relevan secara langsung.</t>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
       </c>
       <c r="C218" s="101" t="inlineStr">
         <is>
-          <t>Robotic Trading</t>
+          <t>RMA (Running Moving Average)</t>
         </is>
       </c>
       <c r="D218" s="101" t="inlineStr">
         <is>
-          <t>Istilah informal untuk algorithmic trading atau autotrade — perdagangan yang dieksekusi sepenuhnya oleh program komputer (robot) tanpa intervensi manusia saat eksekusi berlangsung. Lebih sering digunakan dalam komunitas kripto dan media populer dibanding terminologi akademis algorithmic trading. Keunggulan utama robotic trading: konsistensi tanpa emosi, kecepatan eksekusi, kemampuan memantau pasar 24/7, dan reproduksibilitas keputusan. Dalam penelitian ini, robotic trading diimplementasikan melalui dua sistem paralel: Python Tradingbot (untuk backtesting dan analisis) dan Pine Script v5 + webhook Bybit (untuk live trading). Lihat juga: Algorithmic Trading, Autotrade, Trading Bot.</t>
+          <t>Lihat: Wilder Smoothing (RMA) di Huruf W. Singkatan dari Running Moving Average — metode pemulusan rata-rata bergerak yang diperkenalkan oleh Welles Wilder (1978) dan digunakan secara konsisten dalam penelitian ini untuk menghitung ATR pada kedua implementasi: Python Tradingbot (SSOT) maupun Pine Script v5 (melalui fungsi bawaan ta.atr()). Secara matematis identik dengan EMA namun dengan faktor pemulusan α = 1/n (lebih kecil dari EMA konvensional yang menggunakan 2/(n+1)), sehingga menghasilkan estimasi volatilitas yang lebih stabil tanpa efek 'drop-off' saat data lama keluar dari jendela perhitungan. Lihat juga: ATR, Wilder Smoothing (RMA), EMA.</t>
         </is>
       </c>
     </row>
@@ -5389,12 +5389,12 @@
       </c>
       <c r="C219" s="101" t="inlineStr">
         <is>
-          <t>Robustness Analysis (Analisis Ketahanan)</t>
+          <t>Robotic Trading</t>
         </is>
       </c>
       <c r="D219" s="101" t="inlineStr">
         <is>
-          <t>Prosedur pengujian sistematis (seperti Walk-Forward Analysis dan simulasi Monte Carlo) untuk membuktikan bahwa kinerja strategi perdagangan tetap kokoh, stabil, dan tidak rentan terhadap kegagalan parameter atau variasi data.</t>
+          <t>Istilah informal untuk algorithmic trading atau autotrade — perdagangan yang dieksekusi sepenuhnya oleh program komputer (robot) tanpa intervensi manusia saat eksekusi berlangsung. Lebih sering digunakan dalam komunitas kripto dan media populer dibanding terminologi akademis algorithmic trading. Keunggulan utama robotic trading: konsistensi tanpa emosi, kecepatan eksekusi, kemampuan memantau pasar 24/7, dan reproduksibilitas keputusan. Dalam penelitian ini, robotic trading diimplementasikan melalui dua sistem paralel: Python Tradingbot (untuk backtesting dan analisis) dan Pine Script v5 + webhook Bybit (untuk live trading). Lihat juga: Algorithmic Trading, Autotrade, Trading Bot.</t>
         </is>
       </c>
     </row>
@@ -5409,12 +5409,12 @@
       </c>
       <c r="C220" s="101" t="inlineStr">
         <is>
-          <t>Robustness Score</t>
+          <t>Robustness Analysis (Analisis Ketahanan)</t>
         </is>
       </c>
       <c r="D220" s="101" t="inlineStr">
         <is>
-          <t>Metrik kuantitatif yang mengukur "ketangguhan" sebuah kombinasi parameter. Cara menghitungnya: dari semua sel parameter tetangga (plus/minus 1 langkah di setiap dimensi dalam grid), berapa persen yang memenuhi standar kinerja minimum (Sharpe Ratio dan RAO Score di atas median)? Semakin tinggi nilainya, semakin banyak kombinasi di sekitar parameter tersebut yang juga berkinerja baik — tanda bahwa parameter ini berada di "dataran tinggi" kinerja, bukan "puncak gunung runcing." Dalam penelitian ini, ATR(7) x Multiplier(3,0) memiliki Robustness Score moderat sebesar 58,3% — nilai yang menunjukkan stabilitas yang wajar.</t>
+          <t>Prosedur pengujian sistematis (seperti Walk-Forward Analysis dan simulasi Monte Carlo) untuk membuktikan bahwa kinerja strategi perdagangan tetap kokoh, stabil, dan tidak rentan terhadap kegagalan parameter atau variasi data.</t>
         </is>
       </c>
     </row>
@@ -5429,12 +5429,12 @@
       </c>
       <c r="C221" s="101" t="inlineStr">
         <is>
-          <t>Robustness Sweet-Spot (Zona Parameter Optimal Tangguh)</t>
+          <t>Robustness Score</t>
         </is>
       </c>
       <c r="D221" s="101" t="inlineStr">
         <is>
-          <t>Wilayah dalam ruang parameter grid search di mana kinerja strategi tetap kompetitif dan stabil meskipun parameter digeser ke segala arah. Pada heatmap kinerja, sweet-spot terlihat sebagai "dataran tinggi" yang luas — area dengan warna konsisten, bukan satu titik terang tunggal dikelilingi area gelap. Strategi yang dipilih dari sweet-spot lebih mungkin mempertahankan kinerjanya di masa depan karena tidak bergantung pada kombinasi parameter yang sangat presisi. Dalam penelitian ini, ATR(7) x Multiplier(3,0) berada di sweet-spot yang mencakup ATR Period 5-9 dan Multiplier 2,5-3,5.</t>
+          <t>Metrik kuantitatif yang mengukur "ketangguhan" sebuah kombinasi parameter. Cara menghitungnya: dari semua sel parameter tetangga (plus/minus 1 langkah di setiap dimensi dalam grid), berapa persen yang memenuhi standar kinerja minimum (Sharpe Ratio dan RAO Score di atas median)? Semakin tinggi nilainya, semakin banyak kombinasi di sekitar parameter tersebut yang juga berkinerja baik — tanda bahwa parameter ini berada di "dataran tinggi" kinerja, bukan "puncak gunung runcing." Dalam penelitian ini, ATR(7) x Multiplier(3,0) memiliki Robustness Score moderat sebesar 58,3% — nilai yang menunjukkan stabilitas yang wajar.</t>
         </is>
       </c>
     </row>
@@ -5449,12 +5449,12 @@
       </c>
       <c r="C222" s="101" t="inlineStr">
         <is>
-          <t>Rolling Window (Jendela Bergulir)</t>
+          <t>Robustness Sweet-Spot (Zona Parameter Optimal Tangguh)</t>
         </is>
       </c>
       <c r="D222" s="101" t="inlineStr">
         <is>
-          <t>Metode Walk-Forward Analysis di mana panjang periode pelatihan (IS) selalu TETAP konstan, tetapi seluruh jendela "bergeser" maju seiring waktu. Misalnya: selalu menggunakan 24 bulan data terakhir sebagai IS — bulan ini gunakan Jan 2021-Des 2022; bulan depan gunakan Feb 2021-Jan 2023; dan seterusnya. Ini berarti data lama "dilupakan" seiring munculnya data baru — lebih responsif terhadap perubahan karakteristik pasar terkini. Berbeda dari Growing Window yang "mengingat" semua data dari awal. Dalam penelitian ini, Rolling Window tidak dipilih; Growing Window lebih sesuai untuk Bitcoin yang memiliki tren jangka panjang yang kuat.</t>
+          <t>Wilayah dalam ruang parameter grid search di mana kinerja strategi tetap kompetitif dan stabil meskipun parameter digeser ke segala arah. Pada heatmap kinerja, sweet-spot terlihat sebagai "dataran tinggi" yang luas — area dengan warna konsisten, bukan satu titik terang tunggal dikelilingi area gelap. Strategi yang dipilih dari sweet-spot lebih mungkin mempertahankan kinerjanya di masa depan karena tidak bergantung pada kombinasi parameter yang sangat presisi. Dalam penelitian ini, ATR(7) x Multiplier(3,0) berada di sweet-spot yang mencakup ATR Period 5-9 dan Multiplier 2,5-3,5.</t>
         </is>
       </c>
     </row>
@@ -5469,12 +5469,12 @@
       </c>
       <c r="C223" s="101" t="inlineStr">
         <is>
-          <t>Round-Trip (Siklus Transaksi Lengkap)</t>
+          <t>Rolling Window (Jendela Bergulir)</t>
         </is>
       </c>
       <c r="D223" s="101" t="inlineStr">
         <is>
-          <t>Satu siklus perdagangan lengkap yang terdiri dari pembukaan posisi (entry) diikuti oleh penutupannya (exit). Setiap round-trip menghasilkan satu catatan transaksi dengan semua detailnya: harga masuk, harga keluar, ukuran posisi, durasi, dan profit/loss. Biaya komisi dan slippage dikenakan dua kali per round-trip: sekali saat masuk dan sekali saat keluar. Dalam penelitian ini, terdapat total 26 round-trip dalam 6,1 tahun — rata-rata sekitar 4 transaksi per tahun. Frekuensi rendah yang disengaja: strategi ini mengutamakan kualitas sinyal daripada kuantitas transaksi.</t>
+          <t>Metode Walk-Forward Analysis di mana panjang periode pelatihan (IS) selalu TETAP konstan, tetapi seluruh jendela "bergeser" maju seiring waktu. Misalnya: selalu menggunakan 24 bulan data terakhir sebagai IS — bulan ini gunakan Jan 2021-Des 2022; bulan depan gunakan Feb 2021-Jan 2023; dan seterusnya. Ini berarti data lama "dilupakan" seiring munculnya data baru — lebih responsif terhadap perubahan karakteristik pasar terkini. Berbeda dari Growing Window yang "mengingat" semua data dari awal. Dalam penelitian ini, Rolling Window tidak dipilih; Growing Window lebih sesuai untuk Bitcoin yang memiliki tren jangka panjang yang kuat.</t>
         </is>
       </c>
     </row>
@@ -5489,12 +5489,12 @@
       </c>
       <c r="C224" s="101" t="inlineStr">
         <is>
-          <t>RSI (Relative Strength Index)</t>
+          <t>Round-Trip (Siklus Transaksi Lengkap)</t>
         </is>
       </c>
       <c r="D224" s="101" t="inlineStr">
         <is>
-          <t>Indikator momentum yang bergerak antara 0 dan 100, mengukur kecepatan dan besaran perubahan harga untuk mengidentifikasi kondisi "jenuh beli" (overbought, RSI &gt; 70) atau "jenuh jual" (oversold, RSI &lt; 30). RSI adalah salah satu indikator teknikal paling populer dan sering dikombinasikan dengan indikator lain. Dalam penelitian ini, RSI secara sadar TIDAK digunakan sebagai komponen sistem — keputusan metodologis yang disengaja agar penelitian dapat mengevaluasi Supertrend sebagai sistem mandiri tanpa filter tambahan, sehingga kontribusi Supertrend itu sendiri dapat diukur secara murni.</t>
+          <t>Satu siklus perdagangan lengkap yang terdiri dari pembukaan posisi (entry) diikuti oleh penutupannya (exit). Setiap round-trip menghasilkan satu catatan transaksi dengan semua detailnya: harga masuk, harga keluar, ukuran posisi, durasi, dan profit/loss. Biaya komisi dan slippage dikenakan dua kali per round-trip: sekali saat masuk dan sekali saat keluar. Dalam penelitian ini, terdapat total 26 round-trip dalam 6,1 tahun — rata-rata sekitar 4 transaksi per tahun. Frekuensi rendah yang disengaja: strategi ini mengutamakan kualitas sinyal daripada kuantitas transaksi.</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="C225" s="101" t="inlineStr">
         <is>
-          <t>Ruin</t>
+          <t>RSI (Relative Strength Index)</t>
         </is>
       </c>
       <c r="D225" s="101" t="inlineStr">
         <is>
-          <t>Kehancuran modal secara permanen — kondisi di mana ekuitas turun hingga level di mana perdagangan bermakna tidak lagi bisa dilanjutkan. Berbeda dari drawdown biasa yang bisa dipulihkan, ruin bersifat final. Probability of ruin adalah metrik kritis dalam manajemen risiko: seberapa besar kemungkinan strategi menyebabkan kehancuran modal total? Dalam penelitian ini, probability of ruin diuji melalui 2.000 simulasi Monte Carlo dengan urutan transaksi yang diacak. Hasilnya: 0 dari 2.000 simulasi (0%) menghasilkan kebangkrutan — bukti kuat bahwa Fixed Fractional 5% Risk memberikan perlindungan matematis yang efektif. Lihat juga: Monte Carlo, Geometric Ruin, Fixed Fractional Position Sizing.</t>
+          <t>Indikator momentum yang bergerak antara 0 dan 100, mengukur kecepatan dan besaran perubahan harga untuk mengidentifikasi kondisi "jenuh beli" (overbought, RSI &gt; 70) atau "jenuh jual" (oversold, RSI &lt; 30). RSI adalah salah satu indikator teknikal paling populer dan sering dikombinasikan dengan indikator lain. Dalam penelitian ini, RSI secara sadar TIDAK digunakan sebagai komponen sistem — keputusan metodologis yang disengaja agar penelitian dapat mengevaluasi Supertrend sebagai sistem mandiri tanpa filter tambahan, sehingga kontribusi Supertrend itu sendiri dapat diukur secara murni.</t>
         </is>
       </c>
     </row>
@@ -5524,17 +5524,17 @@
       </c>
       <c r="B226" s="108" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C226" s="101" t="inlineStr">
         <is>
-          <t>Scorecard (Kartu Skor Kinerja)</t>
+          <t>Ruin</t>
         </is>
       </c>
       <c r="D226" s="101" t="inlineStr">
         <is>
-          <t>Format penyajian ringkas yang menampilkan semua metrik kinerja kunci dalam satu tampilan terpadu — seperti rapor lengkap yang memberikan gambaran holistik tanpa perlu membuka banyak tabel terpisah. Dalam penelitian ini, Scorecard digunakan dalam dua konteks: (1) sebagai format visualisasi perbandingan antar strategi (Supertrend vs Buy &amp; Hold vs SMA 20/50 Crossover) untuk semua metrik utama; dan (2) sebagai Modul 7 dalam Python Tradingbot yang secara otomatis menghasilkan ringkasan kinerja terstruktur setelah setiap sesi backtesting atau WFA selesai.</t>
+          <t>Kehancuran modal secara permanen — kondisi di mana ekuitas turun hingga level di mana perdagangan bermakna tidak lagi bisa dilanjutkan. Berbeda dari drawdown biasa yang bisa dipulihkan, ruin bersifat final. Probability of ruin adalah metrik kritis dalam manajemen risiko: seberapa besar kemungkinan strategi menyebabkan kehancuran modal total? Dalam penelitian ini, probability of ruin diuji melalui 2.000 simulasi Monte Carlo dengan urutan transaksi yang diacak. Hasilnya: 0 dari 2.000 simulasi (0%) menghasilkan kebangkrutan — bukti kuat bahwa Fixed Fractional 5% Risk memberikan perlindungan matematis yang efektif. Lihat juga: Monte Carlo, Geometric Ruin, Fixed Fractional Position Sizing.</t>
         </is>
       </c>
     </row>
@@ -5549,12 +5549,12 @@
       </c>
       <c r="C227" s="101" t="inlineStr">
         <is>
-          <t>Sell Signal (Sinyal Jual)</t>
+          <t>Scorecard (Kartu Skor Kinerja)</t>
         </is>
       </c>
       <c r="D227" s="101" t="inlineStr">
         <is>
-          <t>Kondisi spesifik yang memicu sistem untuk menutup posisi long yang sedang aktif — "lampu merah" dari indikator Supertrend. Sinyal jual terjadi tepat saat harga penutupan sebuah candle jatuh ke bawah garis Upper Band untuk pertama kalinya setelah sebelumnya berada di atasnya, menandakan tren naik kemungkinan telah berakhir. Eksekusi penjualan dilakukan pada harga Open candle BERIKUTNYA (keesokan harinya), bukan pada candle sinyal itu sendiri — untuk konsistensi metodologi menghindari look-ahead bias.</t>
+          <t>Format penyajian ringkas yang menampilkan semua metrik kinerja kunci dalam satu tampilan terpadu — seperti rapor lengkap yang memberikan gambaran holistik tanpa perlu membuka banyak tabel terpisah. Dalam penelitian ini, Scorecard digunakan dalam dua konteks: (1) sebagai format visualisasi perbandingan antar strategi (Supertrend vs Buy &amp; Hold vs SMA 20/50 Crossover) untuk semua metrik utama; dan (2) sebagai Modul 7 dalam Python Tradingbot yang secara otomatis menghasilkan ringkasan kinerja terstruktur setelah setiap sesi backtesting atau WFA selesai.</t>
         </is>
       </c>
     </row>
@@ -5569,12 +5569,12 @@
       </c>
       <c r="C228" s="101" t="inlineStr">
         <is>
-          <t>Serial Correlation (Korelasi Serial / Autokorelasi)</t>
+          <t>Sell Signal (Sinyal Jual)</t>
         </is>
       </c>
       <c r="D228" s="101" t="inlineStr">
         <is>
-          <t>Sifat deret waktu di mana nilai pada satu periode berkorelasi dengan nilai pada periode sebelumnya — data "mengingat" masa lalunya. Contoh: setelah hari dengan volatilitas sangat tinggi, hari berikutnya cenderung masih volatil. Data yang murni acak tidak memiliki serial correlation. Keberadaan serial correlation berarti asumsi i.i.d. dalam Bootstrap dan Monte Carlo standar tidak sepenuhnya valid. Dalam penelitian ini, ini diakui sebagai keterbatasan metodologis yang jujur — simulasi dijalankan dengan asumsi i.i.d. untuk kesederhanaan, meskipun data return harian mungkin memiliki sedikit autokorelasi. Keberadaannya dapat dideteksi menggunakan uji Ljung-Box atau uji Breusch-Godfrey.</t>
+          <t>Kondisi spesifik yang memicu sistem untuk menutup posisi long yang sedang aktif — "lampu merah" dari indikator Supertrend. Sinyal jual terjadi tepat saat harga penutupan sebuah candle jatuh ke bawah garis Upper Band untuk pertama kalinya setelah sebelumnya berada di atasnya, menandakan tren naik kemungkinan telah berakhir. Eksekusi penjualan dilakukan pada harga Open candle BERIKUTNYA (keesokan harinya), bukan pada candle sinyal itu sendiri — untuk konsistensi metodologi menghindari look-ahead bias.</t>
         </is>
       </c>
     </row>
@@ -5589,12 +5589,12 @@
       </c>
       <c r="C229" s="101" t="inlineStr">
         <is>
-          <t>Serial Correlation — lihat Huruf R (Korelasi Serial / Autokorelasi)</t>
+          <t>Serial Correlation (Korelasi Serial / Autokorelasi)</t>
         </is>
       </c>
       <c r="D229" s="101" t="inlineStr">
         <is>
-          <t>Lihat entri lengkap: Serial Correlation (Korelasi Serial / Autokorelasi) di Huruf R, No.11. Sifat deret waktu di mana nilai pada satu periode berkorelasi dengan nilai periode sebelumnya — data 'mengingat' masa lalunya. Juga dikenal sebagai Autokorelasi. Dalam penelitian ini, serial correlation diakui sebagai keterbatasan metodologis: simulasi Bootstrap dan Monte Carlo dijalankan dengan asumsi i.i.d. meski return harian Bitcoin mungkin memiliki sedikit autokorelasi. Dapat dideteksi dengan uji Ljung-Box atau Breusch-Godfrey.</t>
+          <t>Sifat deret waktu di mana nilai pada satu periode berkorelasi dengan nilai pada periode sebelumnya — data "mengingat" masa lalunya. Contoh: setelah hari dengan volatilitas sangat tinggi, hari berikutnya cenderung masih volatil. Data yang murni acak tidak memiliki serial correlation. Keberadaan serial correlation berarti asumsi i.i.d. dalam Bootstrap dan Monte Carlo standar tidak sepenuhnya valid. Dalam penelitian ini, ini diakui sebagai keterbatasan metodologis yang jujur — simulasi dijalankan dengan asumsi i.i.d. untuk kesederhanaan, meskipun data return harian mungkin memiliki sedikit autokorelasi. Keberadaannya dapat dideteksi menggunakan uji Ljung-Box atau uji Breusch-Godfrey.</t>
         </is>
       </c>
     </row>
@@ -5609,12 +5609,12 @@
       </c>
       <c r="C230" s="101" t="inlineStr">
         <is>
-          <t>Sharpe Ratio</t>
+          <t>Serial Correlation — lihat Huruf R (Korelasi Serial / Autokorelasi)</t>
         </is>
       </c>
       <c r="D230" s="101" t="inlineStr">
         <is>
-          <t>Metrik kinerja paling populer dalam dunia investasi untuk mengukur efisiensi risiko-return. Cara menghitungnya: (Return rata-rata dikurangi Risk-free rate) dibagi Deviasi standar return. Hasilnya menunjukkan "berapa unit return yang diperoleh per unit risiko yang diambil?" Analoginya: dua pengemudi sama-sama mencapai tujuan dalam waktu sama — satu berkendara mulus dengan kecepatan stabil (Sharpe tinggi), satu lagi dengan kecepatan ekstrem naik-turun berbahaya (Sharpe rendah). Dalam penelitian ini, Sharpe Ratio strategi Supertrend (+0,8334) sedikit lebih tinggi dari Buy &amp; Hold (+0,8208) — keunggulan kecil yang menjadi lebih jelas saat dibandingkan pada Calmar Ratio dan Maximum Drawdown.</t>
+          <t>Lihat entri lengkap: Serial Correlation (Korelasi Serial / Autokorelasi) di Huruf R, No.11. Sifat deret waktu di mana nilai pada satu periode berkorelasi dengan nilai periode sebelumnya — data 'mengingat' masa lalunya. Juga dikenal sebagai Autokorelasi. Dalam penelitian ini, serial correlation diakui sebagai keterbatasan metodologis: simulasi Bootstrap dan Monte Carlo dijalankan dengan asumsi i.i.d. meski return harian Bitcoin mungkin memiliki sedikit autokorelasi. Dapat dideteksi dengan uji Ljung-Box atau Breusch-Godfrey.</t>
         </is>
       </c>
     </row>
@@ -5629,12 +5629,12 @@
       </c>
       <c r="C231" s="101" t="inlineStr">
         <is>
-          <t>Short Selling (Jual Kosong / Posisi Short)</t>
+          <t>Sharpe Ratio</t>
         </is>
       </c>
       <c r="D231" s="101" t="inlineStr">
         <is>
-          <t>Strategi perdagangan di mana trader "meminjam" aset dari broker atau bursa, menjualnya di harga pasar saat ini, kemudian berharap harga turun agar bisa membelinya kembali lebih murah — mengambil selisih harga sebagai keuntungan. Di pasar futures seperti yang digunakan dalam penelitian ini, short selling dilakukan tanpa benar-benar "meminjam" aset: cukup membuka kontrak short. Dalam penelitian ini, pendekatan Short-Only dan Both Sides diuji, namun akhirnya Long-Only dipilih sebagai strategi utama karena Bitcoin memiliki positive drift kuat jangka panjang.</t>
+          <t>Metrik kinerja paling populer dalam dunia investasi untuk mengukur efisiensi risiko-return. Cara menghitungnya: (Return rata-rata dikurangi Risk-free rate) dibagi Deviasi standar return. Hasilnya menunjukkan "berapa unit return yang diperoleh per unit risiko yang diambil?" Analoginya: dua pengemudi sama-sama mencapai tujuan dalam waktu sama — satu berkendara mulus dengan kecepatan stabil (Sharpe tinggi), satu lagi dengan kecepatan ekstrem naik-turun berbahaya (Sharpe rendah). Dalam penelitian ini, Sharpe Ratio strategi Supertrend (+0,8334) sedikit lebih tinggi dari Buy &amp; Hold (+0,8208) — keunggulan kecil yang menjadi lebih jelas saat dibandingkan pada Calmar Ratio dan Maximum Drawdown.</t>
         </is>
       </c>
     </row>
@@ -5649,12 +5649,12 @@
       </c>
       <c r="C232" s="101" t="inlineStr">
         <is>
-          <t>Short Squeeze</t>
+          <t>Short Selling (Jual Kosong / Posisi Short)</t>
         </is>
       </c>
       <c r="D232" s="101" t="inlineStr">
         <is>
-          <t>Fenomena pasar di mana harga naik sangat tajam dan cepat, memaksa banyak trader yang sedang memegang posisi short untuk menutup posisi mereka dengan membeli aset — dan pembelian massal ini justru mendorong harga naik lebih jauh lagi, menciptakan siklus akselerasi. Ini seperti pegas yang terus ditekan: semakin banyak short seller, semakin besar tekanan tersimpan, dan ketika harga mulai naik, pelepasannya sangat eksplosif. Bagi strategi Long-Only seperti dalam penelitian ini, short squeeze justru menguntungkan karena posisi long ikut terdorong naik. Ini juga menjadi salah satu risiko mengapa penelitian menghindari skenario Short-Only.</t>
+          <t>Strategi perdagangan di mana trader "meminjam" aset dari broker atau bursa, menjualnya di harga pasar saat ini, kemudian berharap harga turun agar bisa membelinya kembali lebih murah — mengambil selisih harga sebagai keuntungan. Di pasar futures seperti yang digunakan dalam penelitian ini, short selling dilakukan tanpa benar-benar "meminjam" aset: cukup membuka kontrak short. Dalam penelitian ini, pendekatan Short-Only dan Both Sides diuji, namun akhirnya Long-Only dipilih sebagai strategi utama karena Bitcoin memiliki positive drift kuat jangka panjang.</t>
         </is>
       </c>
     </row>
@@ -5669,12 +5669,12 @@
       </c>
       <c r="C233" s="101" t="inlineStr">
         <is>
-          <t>Short-Only</t>
+          <t>Short Squeeze</t>
         </is>
       </c>
       <c r="D233" s="101" t="inlineStr">
         <is>
-          <t>Skenario pengujian di mana strategi HANYA membuka posisi jual (short) mengikuti sinyal bearish Supertrend — kebalikan dari Long-Only. Posisi short berarti "meminjam" Bitcoin dari bursa, menjualnya sekarang, berharap harganya turun agar bisa dibeli kembali lebih murah dan mengambil selisih sebagai keuntungan. Dalam konteks Bitcoin yang memiliki positive drift kuat, Short-Only cenderung menghasilkan kinerja lebih buruk dari Long-Only dalam jangka panjang — itulah salah satu justifikasi empiris memilih Long-Only sebagai pendekatan utama penelitian ini.</t>
+          <t>Fenomena pasar di mana harga naik sangat tajam dan cepat, memaksa banyak trader yang sedang memegang posisi short untuk menutup posisi mereka dengan membeli aset — dan pembelian massal ini justru mendorong harga naik lebih jauh lagi, menciptakan siklus akselerasi. Ini seperti pegas yang terus ditekan: semakin banyak short seller, semakin besar tekanan tersimpan, dan ketika harga mulai naik, pelepasannya sangat eksplosif. Bagi strategi Long-Only seperti dalam penelitian ini, short squeeze justru menguntungkan karena posisi long ikut terdorong naik. Ini juga menjadi salah satu risiko mengapa penelitian menghindari skenario Short-Only.</t>
         </is>
       </c>
     </row>
@@ -5689,12 +5689,12 @@
       </c>
       <c r="C234" s="101" t="inlineStr">
         <is>
-          <t>Shorting</t>
+          <t>Short-Only</t>
         </is>
       </c>
       <c r="D234" s="101" t="inlineStr">
         <is>
-          <t>Aktivitas membuka posisi short (jual tanpa kepemilikan) — meminjam aset dari bursa, menjualnya di harga saat ini, lalu berharap harga turun agar bisa dibeli kembali lebih murah. Shorting pada Bitcoin sangat berisiko karena: (1) Bitcoin memiliki positive drift jangka panjang yang kuat — shorting melawan tren jangka panjang; (2) potensi short squeeze yang bisa menghasilkan kerugian tak terbatas; dan (3) funding rate yang biasanya negatif bagi posisi short saat pasar bullish. Dalam penelitian ini, shorting tidak dilakukan — strategi long-only dipilih berdasarkan bukti empiris positive drift Bitcoin. Lihat juga: Long-Only, Short-Only, Short Squeeze, Positive Drift.</t>
+          <t>Skenario pengujian di mana strategi HANYA membuka posisi jual (short) mengikuti sinyal bearish Supertrend — kebalikan dari Long-Only. Posisi short berarti "meminjam" Bitcoin dari bursa, menjualnya sekarang, berharap harganya turun agar bisa dibeli kembali lebih murah dan mengambil selisih sebagai keuntungan. Dalam konteks Bitcoin yang memiliki positive drift kuat, Short-Only cenderung menghasilkan kinerja lebih buruk dari Long-Only dalam jangka panjang — itulah salah satu justifikasi empiris memilih Long-Only sebagai pendekatan utama penelitian ini.</t>
         </is>
       </c>
     </row>
@@ -5709,12 +5709,12 @@
       </c>
       <c r="C235" s="101" t="inlineStr">
         <is>
-          <t>Sideways (Pasar Mendatar / Ranging)</t>
+          <t>Shorting</t>
         </is>
       </c>
       <c r="D235" s="101" t="inlineStr">
         <is>
-          <t>Kondisi di mana harga bergerak horizontal dalam rentang yang relatif sempit, tanpa membentuk tren naik maupun turun yang jelas — harga seperti "terjebak" di antara batas atas dan batas bawah, bolak-balik tanpa arah. Ini adalah kondisi paling tidak kondusif bagi strategi trend-following: karena tidak ada tren yang bisa diikuti, sinyal beli dan jual silih berganti dalam waktu singkat, menghasilkan banyak transaksi kecil yang rugi (whipsaw). Dalam penelitian ini, kondisi Sideways-HighVol diidentifikasi sebagai regime paling merugikan bagi strategi Supertrend.</t>
+          <t>Aktivitas membuka posisi short (jual tanpa kepemilikan) — meminjam aset dari bursa, menjualnya di harga saat ini, lalu berharap harga turun agar bisa dibeli kembali lebih murah. Shorting pada Bitcoin sangat berisiko karena: (1) Bitcoin memiliki positive drift jangka panjang yang kuat — shorting melawan tren jangka panjang; (2) potensi short squeeze yang bisa menghasilkan kerugian tak terbatas; dan (3) funding rate yang biasanya negatif bagi posisi short saat pasar bullish. Dalam penelitian ini, shorting tidak dilakukan — strategi long-only dipilih berdasarkan bukti empiris positive drift Bitcoin. Lihat juga: Long-Only, Short-Only, Short Squeeze, Positive Drift.</t>
         </is>
       </c>
     </row>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="C236" s="101" t="inlineStr">
         <is>
-          <t>Sideways-HighVol</t>
+          <t>Sideways (Pasar Mendatar / Ranging)</t>
         </is>
       </c>
       <c r="D236" s="101" t="inlineStr">
         <is>
-          <t>Sub-kategori regime pasar: kondisi pasar mendatar tanpa tren yang jelas dengan volatilitas tinggi — kondisi TERBURUK untuk strategi trend-following seperti Supertrend. Terjadi saat harga dalam rentang 3% di sekitar MA50 sekaligus volatilitas harian di atas median historis. Harga bergerak naik-turun acak dengan amplitudo besar tanpa membentuk tren, menghasilkan banyak sinyal palsu (whipsaw) berturut-turut dengan kerugian kecil yang menumpuk. Dalam analisis regime penelitian ini, Sideways-HighVol diidentifikasi sebagai kondisi di mana Win Rate paling rendah dan drawdown terbesar terjadi. Lihat juga: Regime Pasar, Whipsaw, False Signals, Sideways.</t>
+          <t>Kondisi di mana harga bergerak horizontal dalam rentang yang relatif sempit, tanpa membentuk tren naik maupun turun yang jelas — harga seperti "terjebak" di antara batas atas dan batas bawah, bolak-balik tanpa arah. Ini adalah kondisi paling tidak kondusif bagi strategi trend-following: karena tidak ada tren yang bisa diikuti, sinyal beli dan jual silih berganti dalam waktu singkat, menghasilkan banyak transaksi kecil yang rugi (whipsaw). Dalam penelitian ini, kondisi Sideways-HighVol diidentifikasi sebagai regime paling merugikan bagi strategi Supertrend.</t>
         </is>
       </c>
     </row>
@@ -5749,12 +5749,12 @@
       </c>
       <c r="C237" s="101" t="inlineStr">
         <is>
-          <t>Sideways-LowVol</t>
+          <t>Sideways-HighVol</t>
         </is>
       </c>
       <c r="D237" s="101" t="inlineStr">
         <is>
-          <t>Sub-kategori regime pasar: kondisi mendatar tanpa tren dengan volatilitas rendah. Terjadi saat harga dalam rentang 3% di sekitar MA50 sekaligus volatilitas harian di bawah median historis. Tidak kondusif untuk trend-following karena tidak ada tren yang bisa diikuti, namun lebih jinak dari Sideways-HighVol: volatilitas rendah membatasi kerugian dari false signals. Sistem Supertrend cenderung hanya melakukan sedikit transaksi di kondisi ini. Lihat juga: Regime Pasar, Sideways, Sideways-HighVol.</t>
+          <t>Sub-kategori regime pasar: kondisi pasar mendatar tanpa tren yang jelas dengan volatilitas tinggi — kondisi TERBURUK untuk strategi trend-following seperti Supertrend. Terjadi saat harga dalam rentang 3% di sekitar MA50 sekaligus volatilitas harian di atas median historis. Harga bergerak naik-turun acak dengan amplitudo besar tanpa membentuk tren, menghasilkan banyak sinyal palsu (whipsaw) berturut-turut dengan kerugian kecil yang menumpuk. Dalam analisis regime penelitian ini, Sideways-HighVol diidentifikasi sebagai kondisi di mana Win Rate paling rendah dan drawdown terbesar terjadi. Lihat juga: Regime Pasar, Whipsaw, False Signals, Sideways.</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="C238" s="101" t="inlineStr">
         <is>
-          <t>Single-Asset Scope (Cakupan Aset Tunggal)</t>
+          <t>Sideways-LowVol</t>
         </is>
       </c>
       <c r="D238" s="101" t="inlineStr">
         <is>
-          <t>Batasan penelitian di mana pengujian strategi perdagangan hanya diterapkan pada satu pasangan aset kripto (dalam penelitian ini: BTC/USDT), tanpa melibatkan diversifikasi ke aset kripto lainnya.</t>
+          <t>Sub-kategori regime pasar: kondisi mendatar tanpa tren dengan volatilitas rendah. Terjadi saat harga dalam rentang 3% di sekitar MA50 sekaligus volatilitas harian di bawah median historis. Tidak kondusif untuk trend-following karena tidak ada tren yang bisa diikuti, namun lebih jinak dari Sideways-HighVol: volatilitas rendah membatasi kerugian dari false signals. Sistem Supertrend cenderung hanya melakukan sedikit transaksi di kondisi ini. Lihat juga: Regime Pasar, Sideways, Sideways-HighVol.</t>
         </is>
       </c>
     </row>
@@ -5789,12 +5789,12 @@
       </c>
       <c r="C239" s="101" t="inlineStr">
         <is>
-          <t>Skewness (Kemiringan)</t>
+          <t>Single-Asset Scope (Cakupan Aset Tunggal)</t>
         </is>
       </c>
       <c r="D239" s="101" t="inlineStr">
         <is>
-          <t>Ukuran statistik yang mengkuantifikasi seberapa "miring" atau asimetris distribusi data. Skewness negatif berarti distribusi memiliki "ekor panjang di sebelah kiri" — ada beberapa nilai sangat negatif yang jarang namun terjadi (penurunan tajam sesekali), sementara nilai sehari-hari cenderung sedikit positif. Return harian Bitcoin umumnya menunjukkan negative skewness: fluktuasi positif kecil sering terjadi setiap hari, namun penurunan tajam yang besar terjadi lebih sering dari prediksi distribusi normal — menjadi justifikasi penggunaan uji non-parametrik.</t>
+          <t>Batasan penelitian di mana pengujian strategi perdagangan hanya diterapkan pada satu pasangan aset kripto (dalam penelitian ini: BTC/USDT), tanpa melibatkan diversifikasi ke aset kripto lainnya.</t>
         </is>
       </c>
     </row>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="C240" s="101" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Skewness (Kemiringan)</t>
         </is>
       </c>
       <c r="D240" s="101" t="inlineStr">
         <is>
-          <t>Dalam konteks simulasi Monte Carlo strategi perdagangan, skill merujuk pada keunggulan matematis nyata (edge) yang dimiliki strategi — berlawanan dengan luck (keberuntungan urutan). Strategi yang memiliki skill akan menghasilkan kinerja positif di mayoritas simulasi Monte Carlo meskipun urutan transaksinya diacak secara acak. Dalam penelitian ini, kinerja positif di 2.000 dari 2.000 simulasi Monte Carlo (probability of ruin 0%) adalah bukti bahwa strategi Supertrend memiliki skill yang nyata, bukan sekadar keberuntungan. Lihat juga: Edge, Luck, Monte Carlo.</t>
+          <t>Ukuran statistik yang mengkuantifikasi seberapa "miring" atau asimetris distribusi data. Skewness negatif berarti distribusi memiliki "ekor panjang di sebelah kiri" — ada beberapa nilai sangat negatif yang jarang namun terjadi (penurunan tajam sesekali), sementara nilai sehari-hari cenderung sedikit positif. Return harian Bitcoin umumnya menunjukkan negative skewness: fluktuasi positif kecil sering terjadi setiap hari, namun penurunan tajam yang besar terjadi lebih sering dari prediksi distribusi normal — menjadi justifikasi penggunaan uji non-parametrik.</t>
         </is>
       </c>
     </row>
@@ -5829,12 +5829,12 @@
       </c>
       <c r="C241" s="101" t="inlineStr">
         <is>
-          <t>Slippage</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="D241" s="101" t="inlineStr">
         <is>
-          <t>Perbedaan antara harga yang diharapkan saat order ditempatkan dengan harga aktual saat order benar-benar dieksekusi di bursa. Slippage terjadi karena harga pasar terus bergerak antara momen order ditempatkan dan momen order dieksekusi, atau karena order berukuran besar menggerakkan harga. Di pasar Bitcoin yang sangat likuid, slippage biasanya sangat kecil dalam kondisi normal — namun bisa menjadi sangat besar saat flash crash ketika likuiditas menghilang mendadak. Dalam penelitian ini, slippage diasumsikan 0,03% per transaksi — estimasi konservatif yang mencerminkan kondisi pasar normal.</t>
+          <t>Dalam konteks simulasi Monte Carlo strategi perdagangan, skill merujuk pada keunggulan matematis nyata (edge) yang dimiliki strategi — berlawanan dengan luck (keberuntungan urutan). Strategi yang memiliki skill akan menghasilkan kinerja positif di mayoritas simulasi Monte Carlo meskipun urutan transaksinya diacak secara acak. Dalam penelitian ini, kinerja positif di 2.000 dari 2.000 simulasi Monte Carlo (probability of ruin 0%) adalah bukti bahwa strategi Supertrend memiliki skill yang nyata, bukan sekadar keberuntungan. Lihat juga: Edge, Luck, Monte Carlo.</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="C242" s="101" t="inlineStr">
         <is>
-          <t>SMA (Simple Moving Average)</t>
+          <t>Slippage</t>
         </is>
       </c>
       <c r="D242" s="101" t="inlineStr">
         <is>
-          <t>Rata-rata harga sederhana yang menghitung rata-rata aritmetika dari harga penutupan selama N periode terakhir, memberikan bobot yang sama untuk semua harga dalam jendela waktu tersebut. Saat harga terbaru masuk ke dalam perhitungan, harga tertua keluar — seperti jendela yang bergerak maju. Dalam penelitian ini, SMA digunakan dalam dua konteks: (1) sebagai komponen strategi benchmark aktif SMA 20/50 Crossover; dan (2) sebagai basis klasifikasi Regime Pasar menggunakan MA50.</t>
+          <t>Perbedaan antara harga yang diharapkan saat order ditempatkan dengan harga aktual saat order benar-benar dieksekusi di bursa. Slippage terjadi karena harga pasar terus bergerak antara momen order ditempatkan dan momen order dieksekusi, atau karena order berukuran besar menggerakkan harga. Di pasar Bitcoin yang sangat likuid, slippage biasanya sangat kecil dalam kondisi normal — namun bisa menjadi sangat besar saat flash crash ketika likuiditas menghilang mendadak. Dalam penelitian ini, slippage diasumsikan 0,03% per transaksi — estimasi konservatif yang mencerminkan kondisi pasar normal.</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="C243" s="101" t="inlineStr">
         <is>
-          <t>SMA Crossover (Persilangan SMA)</t>
+          <t>SMA (Simple Moving Average)</t>
         </is>
       </c>
       <c r="D243" s="101" t="inlineStr">
         <is>
-          <t>Strategi trend-following klasik yang menghasilkan sinyal beli atau jual berdasarkan persilangan dua Simple Moving Average dengan periode berbeda. SMA dengan periode pendek (20 hari) mewakili tren jangka pendek; SMA dengan periode panjang (50 hari) mewakili tren jangka menengah. Ketika SMA 20 memotong ke atas SMA 50 (Golden Cross), sinyal beli; ketika SMA 20 memotong ke bawah SMA 50 (Death Cross), sinyal jual. Dalam penelitian ini, SMA 20/50 Crossover digunakan sebagai benchmark aktif: pembanding untuk mengukur apakah Supertrend yang lebih canggih benar-benar lebih baik dari strategi crossover yang lebih sederhana.</t>
+          <t>Rata-rata harga sederhana yang menghitung rata-rata aritmetika dari harga penutupan selama N periode terakhir, memberikan bobot yang sama untuk semua harga dalam jendela waktu tersebut. Saat harga terbaru masuk ke dalam perhitungan, harga tertua keluar — seperti jendela yang bergerak maju. Dalam penelitian ini, SMA digunakan dalam dua konteks: (1) sebagai komponen strategi benchmark aktif SMA 20/50 Crossover; dan (2) sebagai basis klasifikasi Regime Pasar menggunakan MA50.</t>
         </is>
       </c>
     </row>
@@ -5889,12 +5889,12 @@
       </c>
       <c r="C244" s="101" t="inlineStr">
         <is>
-          <t>Smart Contract (Kontrak Pintar)</t>
+          <t>SMA Crossover (Persilangan SMA)</t>
         </is>
       </c>
       <c r="D244" s="101" t="inlineStr">
         <is>
-          <t>Program komputer yang berjalan secara otomatis di atas blockchain, mengeksekusi perjanjian atau transaksi secara mandiri ketika kondisi yang telah ditetapkan sebelumnya terpenuhi — tanpa memerlukan perantara atau kepercayaan pihak ketiga. Smart contract adalah fondasi teknologi dari seluruh ekosistem DeFi dan NFT. Dalam penelitian ini, smart contract disebutkan dalam konteks menjelaskan mengapa Ethereum lebih dari sekadar mata uang digital — ia adalah platform pemrograman blockchain yang memungkinkan aplikasi keuangan terdesentralisasi.</t>
+          <t>Strategi trend-following klasik yang menghasilkan sinyal beli atau jual berdasarkan persilangan dua Simple Moving Average dengan periode berbeda. SMA dengan periode pendek (20 hari) mewakili tren jangka pendek; SMA dengan periode panjang (50 hari) mewakili tren jangka menengah. Ketika SMA 20 memotong ke atas SMA 50 (Golden Cross), sinyal beli; ketika SMA 20 memotong ke bawah SMA 50 (Death Cross), sinyal jual. Dalam penelitian ini, SMA 20/50 Crossover digunakan sebagai benchmark aktif: pembanding untuk mengukur apakah Supertrend yang lebih canggih benar-benar lebih baik dari strategi crossover yang lebih sederhana.</t>
         </is>
       </c>
     </row>
@@ -5909,12 +5909,12 @@
       </c>
       <c r="C245" s="101" t="inlineStr">
         <is>
-          <t>Solana (SOL)</t>
+          <t>Smart Contract (Kontrak Pintar)</t>
         </is>
       </c>
       <c r="D245" s="101" t="inlineStr">
         <is>
-          <t>Aset kripto dan platform blockchain yang dikenal dengan kecepatan transaksi sangat tinggi (hingga 65.000 TPS) dan biaya transaksi yang sangat rendah. Didirikan oleh Anatoly Yakovenko pada 2020, Solana menggunakan mekanisme konsensus unik bernama Proof of History yang memungkinkan pemrosesan transaksi paralel. Dalam penelitian ini, Solana disebutkan dalam saran pengembangan lanjutan sebagai salah satu dari tiga aset kripto berkapitalisasi besar (bersama ETH dan BNB) yang menjadi kandidat target replikasi metodologi Supertrend.</t>
+          <t>Program komputer yang berjalan secara otomatis di atas blockchain, mengeksekusi perjanjian atau transaksi secara mandiri ketika kondisi yang telah ditetapkan sebelumnya terpenuhi — tanpa memerlukan perantara atau kepercayaan pihak ketiga. Smart contract adalah fondasi teknologi dari seluruh ekosistem DeFi dan NFT. Dalam penelitian ini, smart contract disebutkan dalam konteks menjelaskan mengapa Ethereum lebih dari sekadar mata uang digital — ia adalah platform pemrograman blockchain yang memungkinkan aplikasi keuangan terdesentralisasi.</t>
         </is>
       </c>
     </row>
@@ -5929,12 +5929,12 @@
       </c>
       <c r="C246" s="101" t="inlineStr">
         <is>
-          <t>Sortino Ratio</t>
+          <t>Solana (SOL)</t>
         </is>
       </c>
       <c r="D246" s="101" t="inlineStr">
         <is>
-          <t>Versi yang lebih "adil" dari Sharpe Ratio untuk mengevaluasi strategi long-only: perbedaannya adalah Sortino Ratio hanya memperhitungkan volatilitas ke BAWAH (downside deviation) sebagai ukuran risiko, bukan volatilitas total. Logikanya: investor tidak seharusnya "dihukum" karena keuntungan yang lebih besar dari rata-rata — yang dikhawatirkan hanya kerugian. Seseorang senang jika portofolionya naik 30% padahal rata-ratanya 10%; yang tidak menyenangkan adalah jika turun 30%. Sortino Ratio biasanya menghasilkan nilai lebih tinggi dari Sharpe Ratio untuk strategi yang sama, karena penyebutnya lebih kecil.</t>
+          <t>Aset kripto dan platform blockchain yang dikenal dengan kecepatan transaksi sangat tinggi (hingga 65.000 TPS) dan biaya transaksi yang sangat rendah. Didirikan oleh Anatoly Yakovenko pada 2020, Solana menggunakan mekanisme konsensus unik bernama Proof of History yang memungkinkan pemrosesan transaksi paralel. Dalam penelitian ini, Solana disebutkan dalam saran pengembangan lanjutan sebagai salah satu dari tiga aset kripto berkapitalisasi besar (bersama ETH dan BNB) yang menjadi kandidat target replikasi metodologi Supertrend.</t>
         </is>
       </c>
     </row>
@@ -5949,12 +5949,12 @@
       </c>
       <c r="C247" s="101" t="inlineStr">
         <is>
-          <t>Sovereign Risk-Free Asset (Aset Bebas Risiko Berdaulat)</t>
+          <t>Sortino Ratio</t>
         </is>
       </c>
       <c r="D247" s="101" t="inlineStr">
         <is>
-          <t>Instrumen investasi yang diterbitkan oleh pemerintah suatu negara berdaulat dan dianggap bebas dari risiko gagal bayar — contoh utamanya adalah obligasi pemerintah AS (US Treasury Bills/Bonds) atau Surat Utang Negara (SUN) Indonesia. "Sovereign" (berdaulat) menekankan bahwa penerbit adalah pemerintah dengan kapasitas mencetak uang sendiri, berbeda dari obligasi korporasi. Risk-free rate yang digunakan dalam perhitungan Sharpe Ratio dan Sortino Ratio secara konvensional mengacu pada imbal hasil aset jenis ini. Dalam penelitian ini, sovereign risk-free asset disebutkan dalam konteks keterbatasan: ekosistem kripto terdesentralisasi tidak memiliki padanan instrumen bebas risiko berdaulat yang terintegrasi secara langsung — tidak ada "obligasi pemerintah kripto". Akibatnya, risk-free rate ditetapkan 0% sebagai konvensi yang umum digunakan dalam literatur aset kripto. Lihat juga: Risk-Free Rate, Sharpe Ratio, Sortino Ratio.</t>
+          <t>Versi yang lebih "adil" dari Sharpe Ratio untuk mengevaluasi strategi long-only: perbedaannya adalah Sortino Ratio hanya memperhitungkan volatilitas ke BAWAH (downside deviation) sebagai ukuran risiko, bukan volatilitas total. Logikanya: investor tidak seharusnya "dihukum" karena keuntungan yang lebih besar dari rata-rata — yang dikhawatirkan hanya kerugian. Seseorang senang jika portofolionya naik 30% padahal rata-ratanya 10%; yang tidak menyenangkan adalah jika turun 30%. Sortino Ratio biasanya menghasilkan nilai lebih tinggi dari Sharpe Ratio untuk strategi yang sama, karena penyebutnya lebih kecil.</t>
         </is>
       </c>
     </row>
@@ -5969,12 +5969,12 @@
       </c>
       <c r="C248" s="101" t="inlineStr">
         <is>
-          <t>Split (Periode WFA / Fold WFA)</t>
+          <t>Sovereign Risk-Free Asset (Aset Bebas Risiko Berdaulat)</t>
         </is>
       </c>
       <c r="D248" s="101" t="inlineStr">
         <is>
-          <t>Istilah yang digunakan dalam penelitian ini untuk merujuk pada satu pasang periode In-Sample dan Out-of-Sample dalam Walk-Forward Analysis — sinonim dari istilah "fold". Setiap split diberi nama: WF-1, WF-2, WF-3, dan WF-4. Dalam penelitian ini, split WF-1 (OOS 2022) adalah periode paling menantang akibat kolaps Terra/LUNA dan FTX, sedangkan split WF-3 (OOS 2024) adalah periode terbaik berkat bull market pasca-halving. Dalam penelitian ini, empat split diberi label WF-1, WF-2, WF-3, dan WF-4. Lihat juga: WF-1 / WF-2 / WF-3 / WF-4 (Label Split Walk-Forward).</t>
+          <t>Instrumen investasi yang diterbitkan oleh pemerintah suatu negara berdaulat dan dianggap bebas dari risiko gagal bayar — contoh utamanya adalah obligasi pemerintah AS (US Treasury Bills/Bonds) atau Surat Utang Negara (SUN) Indonesia. "Sovereign" (berdaulat) menekankan bahwa penerbit adalah pemerintah dengan kapasitas mencetak uang sendiri, berbeda dari obligasi korporasi. Risk-free rate yang digunakan dalam perhitungan Sharpe Ratio dan Sortino Ratio secara konvensional mengacu pada imbal hasil aset jenis ini. Dalam penelitian ini, sovereign risk-free asset disebutkan dalam konteks keterbatasan: ekosistem kripto terdesentralisasi tidak memiliki padanan instrumen bebas risiko berdaulat yang terintegrasi secara langsung — tidak ada "obligasi pemerintah kripto". Akibatnya, risk-free rate ditetapkan 0% sebagai konvensi yang umum digunakan dalam literatur aset kripto. Lihat juga: Risk-Free Rate, Sharpe Ratio, Sortino Ratio.</t>
         </is>
       </c>
     </row>
@@ -5989,12 +5989,12 @@
       </c>
       <c r="C249" s="101" t="inlineStr">
         <is>
-          <t>Splits</t>
+          <t>Split (Periode WFA / Fold WFA)</t>
         </is>
       </c>
       <c r="D249" s="101" t="inlineStr">
         <is>
-          <t>Pembagian data historis menjadi beberapa pasang periode In-Sample/Out-of-Sample yang berurutan dalam Walk-Forward Analysis. Setiap split atau fold terdiri dari satu periode IS (untuk optimasi) dan satu periode OOS (untuk validasi buta). Penelitian ini menggunakan 4 splits (disebut WF-1, WF-2, WF-3, WF-4), masing-masing dengan periode OOS sekitar 12 bulan, mencakup berbagai kondisi pasar: bull market 2021, bear market 2022, recovery dan halving 2023-2024. Konsistensi kinerja di keempat splits adalah bukti terkuat bahwa strategi tidak overfit ke satu periode pasar tertentu. Lihat juga: Walk-Forward Analysis, In-Sample, Out-of-Sample. Dalam penelitian ini, keempat splits diberi label WF-1, WF-2, WF-3, dan WF-4. Lihat juga: WF-1 / WF-2 / WF-3 / WF-4 (Label Split Walk-Forward).</t>
+          <t>Istilah yang digunakan dalam penelitian ini untuk merujuk pada satu pasang periode In-Sample dan Out-of-Sample dalam Walk-Forward Analysis — sinonim dari istilah "fold". Setiap split diberi nama: WF-1, WF-2, WF-3, dan WF-4. Dalam penelitian ini, split WF-1 (OOS 2022) adalah periode paling menantang akibat kolaps Terra/LUNA dan FTX, sedangkan split WF-3 (OOS 2024) adalah periode terbaik berkat bull market pasca-halving. Dalam penelitian ini, empat split diberi label WF-1, WF-2, WF-3, dan WF-4. Lihat juga: WF-1 / WF-2 / WF-3 / WF-4 (Label Split Walk-Forward).</t>
         </is>
       </c>
     </row>
@@ -6009,12 +6009,12 @@
       </c>
       <c r="C250" s="101" t="inlineStr">
         <is>
-          <t>Spot</t>
+          <t>Splits</t>
         </is>
       </c>
       <c r="D250" s="101" t="inlineStr">
         <is>
-          <t>Lihat: Spot Trading (Perdagangan Spot). Istilah singkat untuk perdagangan aset kripto secara langsung — membeli atau menjual Bitcoin nyata pada harga pasar saat itu, tanpa leverage, tanpa funding rate, tanpa risiko likuidasi paksa. Dalam penelitian ini, Spot merujuk spesifik pada benchmark Buy &amp; Hold yang menggunakan BTC/USDT Spot Market di Bybit — berlawanan dengan instrumen utama penelitian (BTC/USDT Perpetual Futures). Lihat juga: Spot Trading, Perpetual Futures, Buy and Hold.</t>
+          <t>Pembagian data historis menjadi beberapa pasang periode In-Sample/Out-of-Sample yang berurutan dalam Walk-Forward Analysis. Setiap split atau fold terdiri dari satu periode IS (untuk optimasi) dan satu periode OOS (untuk validasi buta). Penelitian ini menggunakan 4 splits (disebut WF-1, WF-2, WF-3, WF-4), masing-masing dengan periode OOS sekitar 12 bulan, mencakup berbagai kondisi pasar: bull market 2021, bear market 2022, recovery dan halving 2023-2024. Konsistensi kinerja di keempat splits adalah bukti terkuat bahwa strategi tidak overfit ke satu periode pasar tertentu. Lihat juga: Walk-Forward Analysis, In-Sample, Out-of-Sample. Dalam penelitian ini, keempat splits diberi label WF-1, WF-2, WF-3, dan WF-4. Lihat juga: WF-1 / WF-2 / WF-3 / WF-4 (Label Split Walk-Forward).</t>
         </is>
       </c>
     </row>
@@ -6029,12 +6029,12 @@
       </c>
       <c r="C251" s="101" t="inlineStr">
         <is>
-          <t>Spot Trading (Perdagangan Spot)</t>
+          <t>Spot</t>
         </is>
       </c>
       <c r="D251" s="101" t="inlineStr">
         <is>
-          <t>Perdagangan aset kripto secara langsung — membeli Bitcoin nyata dan menyimpannya, atau menjual Bitcoin yang dimiliki, pada harga pasar saat itu. Tidak ada leverage, tidak ada tanggal kadaluwarsa, tidak ada funding rate. Lebih sederhana dan tidak ada risiko likuidasi paksa. Namun tidak bisa short (profit dari penurunan harga) dan modal terblokir penuh dalam aset. Dalam penelitian ini, Buy &amp; Hold menggunakan BTC/USDT Spot sebagai benchmark, sementara strategi Supertrend aktif menggunakan BTC/USDT Perpetual Futures — perbedaan instrumen ini perlu diingat saat membandingkan kinerja keduanya.</t>
+          <t>Lihat: Spot Trading (Perdagangan Spot). Istilah singkat untuk perdagangan aset kripto secara langsung — membeli atau menjual Bitcoin nyata pada harga pasar saat itu, tanpa leverage, tanpa funding rate, tanpa risiko likuidasi paksa. Dalam penelitian ini, Spot merujuk spesifik pada benchmark Buy &amp; Hold yang menggunakan BTC/USDT Spot Market di Bybit — berlawanan dengan instrumen utama penelitian (BTC/USDT Perpetual Futures). Lihat juga: Spot Trading, Perpetual Futures, Buy and Hold.</t>
         </is>
       </c>
     </row>
@@ -6049,12 +6049,12 @@
       </c>
       <c r="C252" s="101" t="inlineStr">
         <is>
-          <t>SSOT (Single Source of Truth)</t>
+          <t>Spot Trading (Perdagangan Spot)</t>
         </is>
       </c>
       <c r="D252" s="101" t="inlineStr">
         <is>
-          <t>Prinsip arsitektur sistem yang menetapkan SATU sumber tunggal sebagai referensi otoritatif untuk semua parameter dan logika — sehingga tidak ada ambiguitas atau inkonsistensi antar komponen sistem. Bayangkan sebuah perusahaan yang menggunakan satu database terpusat sebagai sumber kebenaran untuk semua divisi. Dalam penelitian ini, Python Tradingbot ditetapkan sebagai SSOT: semua parameter strategi (ATR Period, Multiplier, Risk per Trade, dll.) harus persis sama antara Python backtesting dan implementasi Pine Script live trading. Ini menjamin konsistensi total antara simulasi dan eksekusi nyata.</t>
+          <t>Perdagangan aset kripto secara langsung — membeli Bitcoin nyata dan menyimpannya, atau menjual Bitcoin yang dimiliki, pada harga pasar saat itu. Tidak ada leverage, tidak ada tanggal kadaluwarsa, tidak ada funding rate. Lebih sederhana dan tidak ada risiko likuidasi paksa. Namun tidak bisa short (profit dari penurunan harga) dan modal terblokir penuh dalam aset. Dalam penelitian ini, Buy &amp; Hold menggunakan BTC/USDT Spot sebagai benchmark, sementara strategi Supertrend aktif menggunakan BTC/USDT Perpetual Futures — perbedaan instrumen ini perlu diingat saat membandingkan kinerja keduanya.</t>
         </is>
       </c>
     </row>
@@ -6069,12 +6069,12 @@
       </c>
       <c r="C253" s="101" t="inlineStr">
         <is>
-          <t>Stablecoin</t>
+          <t>SSOT (Single Source of Truth)</t>
         </is>
       </c>
       <c r="D253" s="101" t="inlineStr">
         <is>
-          <t>Jenis aset kripto yang dirancang untuk mempertahankan nilai stabil dengan cara dipatok (peg) terhadap aset lain yang lebih stabil — biasanya Dolar Amerika Serikat. Ada tiga mekanisme utama: (1) Fiat-backed (dijamin cadangan dolar nyata), contohnya USDT dan USDC; (2) Crypto-backed (dijamin aset kripto lain dengan over-collateralization), contohnya DAI; dan (3) Algorithmic (menggunakan mekanisme algoritma suplai-permintaan tanpa cadangan nyata), contohnya TerraUSD (UST) yang runtuh pada 2022. Dalam penelitian ini, stablecoin memainkan peran krusial: USDT adalah mata uang kuotasi instrumen BTC/USDT Perpetual Futures sekaligus aset kolateral di akun Bybit. Modal yang "menganggur" saat tidak ada posisi aktif tersimpan sebagai USDT yang relatif stabil nilainya, tidak tergerus fluktuasi harga kripto spekulatif.</t>
+          <t>Prinsip arsitektur sistem yang menetapkan SATU sumber tunggal sebagai referensi otoritatif untuk semua parameter dan logika — sehingga tidak ada ambiguitas atau inkonsistensi antar komponen sistem. Bayangkan sebuah perusahaan yang menggunakan satu database terpusat sebagai sumber kebenaran untuk semua divisi. Dalam penelitian ini, Python Tradingbot ditetapkan sebagai SSOT: semua parameter strategi (ATR Period, Multiplier, Risk per Trade, dll.) harus persis sama antara Python backtesting dan implementasi Pine Script live trading. Ini menjamin konsistensi total antara simulasi dan eksekusi nyata.</t>
         </is>
       </c>
     </row>
@@ -6089,12 +6089,12 @@
       </c>
       <c r="C254" s="101" t="inlineStr">
         <is>
-          <t>Standard Deviation (Deviasi Standar)</t>
+          <t>Stablecoin</t>
         </is>
       </c>
       <c r="D254" s="101" t="inlineStr">
         <is>
-          <t>Ukuran statistik paling umum untuk mengukur seberapa tersebar nilai-nilai data dari rata-ratanya. Dalam keuangan, deviasi standar return harian digunakan sebagai ukuran volatilitas atau risiko total. Ia adalah penyebut dalam perhitungan Sharpe Ratio. Keterbatasan penting: deviasi standar bersifat simetris — ia "menghukum" volatilitas ke atas (keuntungan besar) sama seperti volatilitas ke bawah (kerugian besar). Inilah mengapa Sortino Ratio yang hanya menggunakan downside deviation lebih sesuai untuk mengevaluasi strategi long-only yang memang sering naik tajam.</t>
+          <t>Jenis aset kripto yang dirancang untuk mempertahankan nilai stabil dengan cara dipatok (peg) terhadap aset lain yang lebih stabil — biasanya Dolar Amerika Serikat. Ada tiga mekanisme utama: (1) Fiat-backed (dijamin cadangan dolar nyata), contohnya USDT dan USDC; (2) Crypto-backed (dijamin aset kripto lain dengan over-collateralization), contohnya DAI; dan (3) Algorithmic (menggunakan mekanisme algoritma suplai-permintaan tanpa cadangan nyata), contohnya TerraUSD (UST) yang runtuh pada 2022. Dalam penelitian ini, stablecoin memainkan peran krusial: USDT adalah mata uang kuotasi instrumen BTC/USDT Perpetual Futures sekaligus aset kolateral di akun Bybit. Modal yang "menganggur" saat tidak ada posisi aktif tersimpan sebagai USDT yang relatif stabil nilainya, tidak tergerus fluktuasi harga kripto spekulatif.</t>
         </is>
       </c>
     </row>
@@ -6109,12 +6109,12 @@
       </c>
       <c r="C255" s="101" t="inlineStr">
         <is>
-          <t>Stasioneritas (Stationarity)</t>
+          <t>Standard Deviation (Deviasi Standar)</t>
         </is>
       </c>
       <c r="D255" s="101" t="inlineStr">
         <is>
-          <t>Sifat statistik suatu deret waktu di mana karakteristik statistik dasarnya — rata-rata, variansi, dan pola korelasi — tidak berubah seiring berjalannya waktu. Deret waktu yang stasioner "berperilaku sama" di periode manapun, sehingga pola yang dipelajari dari data masa lalu masih relevan untuk masa kini. Dalam penelitian ini, uji ADF membuktikan: harga penutupan BTC bersifat NON-stasioner (terus naik, tidak kembali ke rata-rata) — wajar untuk aset dengan positive drift. Namun log return harian BTC bersifat stasioner — menjustifikasi penggunaan model statistik untuk analisis kinerja strategi.</t>
+          <t>Ukuran statistik paling umum untuk mengukur seberapa tersebar nilai-nilai data dari rata-ratanya. Dalam keuangan, deviasi standar return harian digunakan sebagai ukuran volatilitas atau risiko total. Ia adalah penyebut dalam perhitungan Sharpe Ratio. Keterbatasan penting: deviasi standar bersifat simetris — ia "menghukum" volatilitas ke atas (keuntungan besar) sama seperti volatilitas ke bawah (kerugian besar). Inilah mengapa Sortino Ratio yang hanya menggunakan downside deviation lebih sesuai untuk mengevaluasi strategi long-only yang memang sering naik tajam.</t>
         </is>
       </c>
     </row>
@@ -6129,12 +6129,12 @@
       </c>
       <c r="C256" s="101" t="inlineStr">
         <is>
-          <t>State Machine (Mesin Status)</t>
+          <t>Stasioneritas (Stationarity)</t>
         </is>
       </c>
       <c r="D256" s="101" t="inlineStr">
         <is>
-          <t>Lihat: State Machine (Mesin Status) di Huruf S. Konsep pemrograman yang merepresentasikan sistem sebagai kumpulan status (state) terbatas — FLAT, LONG, dan SHORT. Entri ini ditempatkan di Huruf P secara historis; entri lengkap dan kanonik ada di Huruf S. Lihat juga: Bar-by-Bar, Python Tradingbot.</t>
+          <t>Sifat statistik suatu deret waktu di mana karakteristik statistik dasarnya — rata-rata, variansi, dan pola korelasi — tidak berubah seiring berjalannya waktu. Deret waktu yang stasioner "berperilaku sama" di periode manapun, sehingga pola yang dipelajari dari data masa lalu masih relevan untuk masa kini. Dalam penelitian ini, uji ADF membuktikan: harga penutupan BTC bersifat NON-stasioner (terus naik, tidak kembali ke rata-rata) — wajar untuk aset dengan positive drift. Namun log return harian BTC bersifat stasioner — menjustifikasi penggunaan model statistik untuk analisis kinerja strategi.</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="D257" s="101" t="inlineStr">
         <is>
-          <t>Konsep pemrograman yang merepresentasikan sistem sebagai kumpulan status (state) yang terbatas — sistem selalu berada tepat dalam SATU status pada satu waktu. Dalam sistem perdagangan, terdapat tiga state: 'FLAT' (tidak ada posisi terbuka), 'LONG' (posisi beli aktif), dan 'SHORT' (posisi jual aktif, untuk skenario Both Sides). Perpindahan antar status dipicu oleh sinyal: sinyal BUY memindahkan dari FLAT ke LONG; sinyal SELL memindahkan dari LONG ke FLAT. State machine memastikan tidak ada kondisi anomali — sistem tidak mungkin 'beli lagi padahal sudah punya posisi beli.' Dalam penelitian ini, logika state machine diimplementasikan dalam loop bar-by-bar Python. Catatan penempatan: entri ini juga terdaftar di Huruf P (No.14) karena secara historis ditempatkan di sana. Entri kanonik ada di Huruf S ini. Lihat juga: Bar-by-Bar, Python Tradingbot, Loop.</t>
+          <t>Lihat: State Machine (Mesin Status) di Huruf S. Konsep pemrograman yang merepresentasikan sistem sebagai kumpulan status (state) terbatas — FLAT, LONG, dan SHORT. Entri ini ditempatkan di Huruf P secara historis; entri lengkap dan kanonik ada di Huruf S. Lihat juga: Bar-by-Bar, Python Tradingbot.</t>
         </is>
       </c>
     </row>
@@ -6169,12 +6169,12 @@
       </c>
       <c r="C258" s="101" t="inlineStr">
         <is>
-          <t>Stationary Bootstrap</t>
+          <t>State Machine (Mesin Status)</t>
         </is>
       </c>
       <c r="D258" s="101" t="inlineStr">
         <is>
-          <t>Lihat: Block Bootstrap. Metode ini secara teknis adalah varian dari Block Bootstrap dari Politis &amp; Romano (1994), di mana panjang setiap blok yang diambil saat resampling bersifat acak. Keistimewaannya: deret hasil resampling tetap mempertahankan sifat stasioneritas secara matematis. Dalam penelitian ini, Stationary Bootstrap digunakan untuk mengestimasi confidence interval 95% untuk metrik kinerja (Sharpe Ratio, Sortino Ratio, Calmar Ratio, Net P&amp;L) dengan 2.000 iterasi.</t>
+          <t>Konsep pemrograman yang merepresentasikan sistem sebagai kumpulan status (state) yang terbatas — sistem selalu berada tepat dalam SATU status pada satu waktu. Dalam sistem perdagangan, terdapat tiga state: 'FLAT' (tidak ada posisi terbuka), 'LONG' (posisi beli aktif), dan 'SHORT' (posisi jual aktif, untuk skenario Both Sides). Perpindahan antar status dipicu oleh sinyal: sinyal BUY memindahkan dari FLAT ke LONG; sinyal SELL memindahkan dari LONG ke FLAT. State machine memastikan tidak ada kondisi anomali — sistem tidak mungkin 'beli lagi padahal sudah punya posisi beli.' Dalam penelitian ini, logika state machine diimplementasikan dalam loop bar-by-bar Python. Catatan penempatan: entri ini juga terdaftar di Huruf P (No.14) karena secara historis ditempatkan di sana. Entri kanonik ada di Huruf S ini. Lihat juga: Bar-by-Bar, Python Tradingbot, Loop.</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="C259" s="101" t="inlineStr">
         <is>
-          <t>Statistical Power (Kekuatan Statistik)</t>
+          <t>Stationary Bootstrap</t>
         </is>
       </c>
       <c r="D259" s="101" t="inlineStr">
         <is>
-          <t>Kemampuan sebuah uji statistik untuk mendeteksi efek nyata yang memang ada — probabilitas bahwa uji akan menghasilkan "positif" (menolak H0) ketika H0 memang seharusnya ditolak. Bayangkan seperti sensitivitas alat deteksi: kekuatan tinggi seperti detektor yang bisa menemukan klip kertas kecil; kekuatan rendah seperti detektor yang hanya menemukan bongkahan besar. Faktor utama yang memengaruhi kekuatan statistik adalah ukuran sampel. Ini adalah keterbatasan inheren penelitian ini: dengan hanya 26 transaksi dalam 6,1 tahun, kekuatan statistik terbatas — efek nyata yang ada mungkin tidak terdeteksi karena sampel terlalu kecil.</t>
+          <t>Lihat: Block Bootstrap. Metode ini secara teknis adalah varian dari Block Bootstrap dari Politis &amp; Romano (1994), di mana panjang setiap blok yang diambil saat resampling bersifat acak. Keistimewaannya: deret hasil resampling tetap mempertahankan sifat stasioneritas secara matematis. Dalam penelitian ini, Stationary Bootstrap digunakan untuk mengestimasi confidence interval 95% untuk metrik kinerja (Sharpe Ratio, Sortino Ratio, Calmar Ratio, Net P&amp;L) dengan 2.000 iterasi.</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="C260" s="101" t="inlineStr">
         <is>
-          <t>Sticky Band (Pita Tren Dinamis Terkelunci)</t>
+          <t>Statistical Power (Kekuatan Statistik)</t>
         </is>
       </c>
       <c r="D260" s="101" t="inlineStr">
         <is>
-          <t>Mekanisme paling cerdas dalam indikator Supertrend yang membuat garis band "lengket" pada arah tren yang sedang berlangsung — tidak bisa bergerak berlawanan arah. Saat tren naik aktif, garis support (Upper Band) boleh naik atau diam, tetapi tidak boleh turun — "dikunci" agar tidak memberikan sinyal jual palsu hanya karena ATR sesaat mengecil. Sebaliknya saat tren turun, garis resistansi (Lower Band) boleh turun atau diam, tapi tidak boleh naik. Mekanisme "penguncian" ini membuat Supertrend jauh lebih tahan terhadap sinyal palsu (whipsaw) dibandingkan indikator band lain yang tidak memiliki mekanisme serupa.</t>
+          <t>Kemampuan sebuah uji statistik untuk mendeteksi efek nyata yang memang ada — probabilitas bahwa uji akan menghasilkan "positif" (menolak H0) ketika H0 memang seharusnya ditolak. Bayangkan seperti sensitivitas alat deteksi: kekuatan tinggi seperti detektor yang bisa menemukan klip kertas kecil; kekuatan rendah seperti detektor yang hanya menemukan bongkahan besar. Faktor utama yang memengaruhi kekuatan statistik adalah ukuran sampel. Ini adalah keterbatasan inheren penelitian ini: dengan hanya 26 transaksi dalam 6,1 tahun, kekuatan statistik terbatas — efek nyata yang ada mungkin tidak terdeteksi karena sampel terlalu kecil.</t>
         </is>
       </c>
     </row>
@@ -6229,12 +6229,12 @@
       </c>
       <c r="C261" s="101" t="inlineStr">
         <is>
-          <t>Stop Loss Distance</t>
+          <t>Sticky Band (Pita Tren Dinamis Terkelunci)</t>
         </is>
       </c>
       <c r="D261" s="101" t="inlineStr">
         <is>
-          <t>Jarak antara harga entry (harga Open candle esok hari saat order dieksekusi) dan level stop-loss (garis Upper Band saat sinyal beli terdeteksi), diukur dalam satuan harga absolut (dolar per Bitcoin). Nilai ini adalah komponen krusial dalam formula Fixed Fractional Position Sizing: Ukuran Posisi = (Modal x Risk%) dibagi Stop Loss Distance. Semakin jauh Stop Loss Distance (volatilitas tinggi), semakin kecil ukuran posisi untuk menjaga risiko tetap 5% ekuitas. Semakin dekat Stop Loss Distance (volatilitas rendah), semakin besar ukuran posisi yang bisa diambil. Inilah mekanisme Volatility-Adjusted Position Sizing yang bekerja secara otomatis. Lihat juga: Fixed Fractional Position Sizing, ATR, Upper Band, Volatility-Adjusted Position Sizing.</t>
+          <t>Mekanisme paling cerdas dalam indikator Supertrend yang membuat garis band "lengket" pada arah tren yang sedang berlangsung — tidak bisa bergerak berlawanan arah. Saat tren naik aktif, garis support (Upper Band) boleh naik atau diam, tetapi tidak boleh turun — "dikunci" agar tidak memberikan sinyal jual palsu hanya karena ATR sesaat mengecil. Sebaliknya saat tren turun, garis resistansi (Lower Band) boleh turun atau diam, tapi tidak boleh naik. Mekanisme "penguncian" ini membuat Supertrend jauh lebih tahan terhadap sinyal palsu (whipsaw) dibandingkan indikator band lain yang tidak memiliki mekanisme serupa.</t>
         </is>
       </c>
     </row>
@@ -6249,12 +6249,12 @@
       </c>
       <c r="C262" s="101" t="inlineStr">
         <is>
-          <t>Stop-Loss</t>
+          <t>Stop Loss Distance</t>
         </is>
       </c>
       <c r="D262" s="101" t="inlineStr">
         <is>
-          <t>Level harga yang telah ditentukan sebelumnya di mana sebuah posisi perdagangan akan ditutup secara otomatis untuk membatasi kerugian. Stop-loss adalah "batas kerugian yang bisa diterima" yang ditetapkan di muka sebelum emosi terlibat — seperti airbag mobil: tidak mencegah kecelakaan, tetapi membatasi dampaknya. Dalam strategi Supertrend, garis Upper Band berfungsi sebagai trailing stop-loss yang bergerak dinamis: saat harga naik, garis stop-loss ikut naik (mengunci keuntungan); saat harga jatuh dan menyentuh garis ini, posisi otomatis ditutup dan keuntungan yang sudah terkunci tidak akan hilang sepenuhnya.</t>
+          <t>Jarak antara harga entry (harga Open candle esok hari saat order dieksekusi) dan level stop-loss (garis Upper Band saat sinyal beli terdeteksi), diukur dalam satuan harga absolut (dolar per Bitcoin). Nilai ini adalah komponen krusial dalam formula Fixed Fractional Position Sizing: Ukuran Posisi = (Modal x Risk%) dibagi Stop Loss Distance. Semakin jauh Stop Loss Distance (volatilitas tinggi), semakin kecil ukuran posisi untuk menjaga risiko tetap 5% ekuitas. Semakin dekat Stop Loss Distance (volatilitas rendah), semakin besar ukuran posisi yang bisa diambil. Inilah mekanisme Volatility-Adjusted Position Sizing yang bekerja secara otomatis. Lihat juga: Fixed Fractional Position Sizing, ATR, Upper Band, Volatility-Adjusted Position Sizing.</t>
         </is>
       </c>
     </row>
@@ -6269,12 +6269,12 @@
       </c>
       <c r="C263" s="101" t="inlineStr">
         <is>
-          <t>Supertrend</t>
+          <t>Stop-Loss</t>
         </is>
       </c>
       <c r="D263" s="101" t="inlineStr">
         <is>
-          <t>Indikator analisis teknikal berbasis volatilitas yang menjadi fokus utama penelitian ini. Cara kerjanya: Supertrend menghasilkan dua garis band dinamis di sekitar grafik harga yang lebarnya otomatis menyesuaikan dengan volatilitas pasar (diukur oleh ATR). Saat harga berada di atas garis Upper Band, indikator menampilkan sinyal BULLISH/BUY — sistem dalam posisi long dengan Upper Band sebagai trailing stop. Saat harga jatuh ke bawah garis Upper Band, sinyal berganti BEARISH/SELL — posisi ditutup. Keunggulan Supertrend: (1) secara otomatis menyesuaikan sensitivitas terhadap volatilitas; (2) mekanisme Sticky Band mencegah sinyal palsu berulang saat sideways; dan (3) interpretasi biner yang tegas (bullish/bearish) yang mudah diimplementasikan dalam sistem otomatis.</t>
+          <t>Level harga yang telah ditentukan sebelumnya di mana sebuah posisi perdagangan akan ditutup secara otomatis untuk membatasi kerugian. Stop-loss adalah "batas kerugian yang bisa diterima" yang ditetapkan di muka sebelum emosi terlibat — seperti airbag mobil: tidak mencegah kecelakaan, tetapi membatasi dampaknya. Dalam strategi Supertrend, garis Upper Band berfungsi sebagai trailing stop-loss yang bergerak dinamis: saat harga naik, garis stop-loss ikut naik (mengunci keuntungan); saat harga jatuh dan menyentuh garis ini, posisi otomatis ditutup dan keuntungan yang sudah terkunci tidak akan hilang sepenuhnya.</t>
         </is>
       </c>
     </row>
@@ -6289,12 +6289,12 @@
       </c>
       <c r="C264" s="101" t="inlineStr">
         <is>
-          <t>Szakmary et al. (2010) --- Temuan Lag Trend-Following vs Buy-and-Hold</t>
+          <t>Supertrend</t>
         </is>
       </c>
       <c r="D264" s="101" t="inlineStr">
         <is>
-          <t>Studi akademis penting yang memberikan justifikasi teoretis penelitian ini. Temuannya: meskipun strategi trend-following terbukti sangat menguntungkan saat pasar bergejolak dan trending, strategi ini sering TIDAK mampu mengalahkan Buy &amp; Hold selama bull market panjang yang kuat — karena sifat lag indikator memangkas sebagian keuntungan di awal dan akhir setiap tren. Temuan ini konsisten dengan hasil penelitian ini: Buy &amp; Hold menghasilkan CAGR lebih tinggi (+50,29% vs +26,72%) karena periode 2020-2026 didominasi bull market Bitcoin. Namun Supertrend TETAP unggul secara risk-adjusted (Calmar Ratio +0,9533 vs +0,6481), membuktikan nilai Supertrend bukan di return mentah tetapi di efisiensi risiko.</t>
+          <t>Indikator analisis teknikal berbasis volatilitas yang menjadi fokus utama penelitian ini. Cara kerjanya: Supertrend menghasilkan dua garis band dinamis di sekitar grafik harga yang lebarnya otomatis menyesuaikan dengan volatilitas pasar (diukur oleh ATR). Saat harga berada di atas garis Upper Band, indikator menampilkan sinyal BULLISH/BUY — sistem dalam posisi long dengan Upper Band sebagai trailing stop. Saat harga jatuh ke bawah garis Upper Band, sinyal berganti BEARISH/SELL — posisi ditutup. Keunggulan Supertrend: (1) secara otomatis menyesuaikan sensitivitas terhadap volatilitas; (2) mekanisme Sticky Band mencegah sinyal palsu berulang saat sideways; dan (3) interpretasi biner yang tegas (bullish/bearish) yang mudah diimplementasikan dalam sistem otomatis.</t>
         </is>
       </c>
     </row>
@@ -6304,17 +6304,17 @@
       </c>
       <c r="B265" s="108" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C265" s="101" t="inlineStr">
         <is>
-          <t>t-ratio (Harvey et al.)</t>
+          <t>Szakmary et al. (2010) --- Temuan Lag Trend-Following vs Buy-and-Hold</t>
         </is>
       </c>
       <c r="D265" s="101" t="inlineStr">
         <is>
-          <t>Statistik uji yang mengukur seberapa "jauh dari nol" dan "seberapa dapat dipercaya" sebuah nilai metrik kinerja. Harvey et al. (2016) merekomendasikan standar yang LEBIH TINGGI dari t-ratio 1,96 yang biasa digunakan dalam statistik konvensional — sekitar 3,0 — sebagai koreksi atas risiko data snooping bias ketika banyak kombinasi parameter diuji. Logikanya: jika Anda menguji 120 kombinasi dan memilih yang terbaik, Anda perlu bukti yang lebih kuat agar hasilnya tidak dianggap keberuntungan. Dalam penelitian ini, t-ratio yang dihasilkan adalah 4,25 — melampaui threshold 3,0, mengkonfirmasi kinerja strategi bukan sekadar produk pencarian berlebihan.</t>
+          <t>Studi akademis penting yang memberikan justifikasi teoretis penelitian ini. Temuannya: meskipun strategi trend-following terbukti sangat menguntungkan saat pasar bergejolak dan trending, strategi ini sering TIDAK mampu mengalahkan Buy &amp; Hold selama bull market panjang yang kuat — karena sifat lag indikator memangkas sebagian keuntungan di awal dan akhir setiap tren. Temuan ini konsisten dengan hasil penelitian ini: Buy &amp; Hold menghasilkan CAGR lebih tinggi (+50,29% vs +26,72%) karena periode 2020-2026 didominasi bull market Bitcoin. Namun Supertrend TETAP unggul secara risk-adjusted (Calmar Ratio +0,9533 vs +0,6481), membuktikan nilai Supertrend bukan di return mentah tetapi di efisiensi risiko.</t>
         </is>
       </c>
     </row>
@@ -6329,12 +6329,12 @@
       </c>
       <c r="C266" s="101" t="inlineStr">
         <is>
-          <t>t-test Parametrik (Paired t-test)</t>
+          <t>t-ratio (Harvey et al.)</t>
         </is>
       </c>
       <c r="D266" s="101" t="inlineStr">
         <is>
-          <t>Uji statistik klasik yang membandingkan rata-rata dua kelompok data berpasangan, dengan ASUMSI bahwa data berdistribusi normal. Uji ini tidak valid ketika data menyimpang jauh dari normalitas. Data return harian Bitcoin terbukti sangat tidak normal (negative skewness yang kuat dan excess kurtosis sangat tinggi) — menggunakan uji-t pada data seperti ini bisa menghasilkan kesimpulan yang salah. Itulah mengapa dalam penelitian ini, paired t-test secara eksplisit DITOLAK dan digantikan oleh Mann-Whitney U Test yang tidak memerlukan asumsi normalitas.</t>
+          <t>Statistik uji yang mengukur seberapa "jauh dari nol" dan "seberapa dapat dipercaya" sebuah nilai metrik kinerja. Harvey et al. (2016) merekomendasikan standar yang LEBIH TINGGI dari t-ratio 1,96 yang biasa digunakan dalam statistik konvensional — sekitar 3,0 — sebagai koreksi atas risiko data snooping bias ketika banyak kombinasi parameter diuji. Logikanya: jika Anda menguji 120 kombinasi dan memilih yang terbaik, Anda perlu bukti yang lebih kuat agar hasilnya tidak dianggap keberuntungan. Dalam penelitian ini, t-ratio yang dihasilkan adalah 4,25 — melampaui threshold 3,0, mengkonfirmasi kinerja strategi bukan sekadar produk pencarian berlebihan.</t>
         </is>
       </c>
     </row>
@@ -6349,12 +6349,12 @@
       </c>
       <c r="C267" s="101" t="inlineStr">
         <is>
-          <t>Taker Fee / Maker Fee</t>
+          <t>t-test Parametrik (Paired t-test)</t>
         </is>
       </c>
       <c r="D267" s="101" t="inlineStr">
         <is>
-          <t>Dua struktur biaya transaksi di bursa kripto berdasarkan apakah order trader menambah atau mengurangi likuiditas dari order book. Maker Fee dikenakan kepada trader yang memasang order limit (beli/jual di harga tertentu yang belum tentu langsung tereksekusi) — karena order ini "membuat" likuiditas baru di order book. Taker Fee dikenakan kepada trader yang memasang order market (beli atau jual langsung di harga pasar saat itu) — karena order ini "mengambil" likuiditas yang sudah ada. Karena maker menambah likuiditas, maker fee biasanya lebih rendah dari taker fee. Di Bybit, taker fee standar adalah 0,05% per transaksi. Dalam penelitian ini, seluruh simulasi mengasumsikan eksekusi sebagai taker (order market) dengan komisi 0,05% per transaksi — pilihan konservatif yang sesuai dengan eksekusi otomatis berbasis sinyal harga penutupan candle harian.</t>
+          <t>Uji statistik klasik yang membandingkan rata-rata dua kelompok data berpasangan, dengan ASUMSI bahwa data berdistribusi normal. Uji ini tidak valid ketika data menyimpang jauh dari normalitas. Data return harian Bitcoin terbukti sangat tidak normal (negative skewness yang kuat dan excess kurtosis sangat tinggi) — menggunakan uji-t pada data seperti ini bisa menghasilkan kesimpulan yang salah. Itulah mengapa dalam penelitian ini, paired t-test secara eksplisit DITOLAK dan digantikan oleh Mann-Whitney U Test yang tidak memerlukan asumsi normalitas.</t>
         </is>
       </c>
     </row>
@@ -6369,12 +6369,12 @@
       </c>
       <c r="C268" s="101" t="inlineStr">
         <is>
-          <t>Terra/LUNA</t>
+          <t>Taker Fee / Maker Fee</t>
         </is>
       </c>
       <c r="D268" s="101" t="inlineStr">
         <is>
-          <t>Dua peristiwa katastrofik yang menjadi pemicu utama bear market kripto terpanjang dalam periode penelitian ini. Terra/LUNA: ekosistem blockchain Terraform Labs dengan stablecoin algoritmik TerraUSD (UST). Pada Mei 2022, mekanismenya mengalami "death spiral" — UST turun dari $1 memicu penjualan masif LUNA, yang semakin melemahkan kepercayaan pada UST, dan seterusnya — menghapus lebih dari $40 miliar nilai pasar dalam hitungan hari. FTX: bursa kripto besar yang terungkap pada November 2022 secara tidak sah menggunakan dana nasabah. Keduanya menjelaskan mengapa 2022 (fold WF-2 OOS) adalah tahun tersulit bagi strategi Supertrend long-only dalam penelitian ini.</t>
+          <t>Dua struktur biaya transaksi di bursa kripto berdasarkan apakah order trader menambah atau mengurangi likuiditas dari order book. Maker Fee dikenakan kepada trader yang memasang order limit (beli/jual di harga tertentu yang belum tentu langsung tereksekusi) — karena order ini "membuat" likuiditas baru di order book. Taker Fee dikenakan kepada trader yang memasang order market (beli atau jual langsung di harga pasar saat itu) — karena order ini "mengambil" likuiditas yang sudah ada. Karena maker menambah likuiditas, maker fee biasanya lebih rendah dari taker fee. Di Bybit, taker fee standar adalah 0,05% per transaksi. Dalam penelitian ini, seluruh simulasi mengasumsikan eksekusi sebagai taker (order market) dengan komisi 0,05% per transaksi — pilihan konservatif yang sesuai dengan eksekusi otomatis berbasis sinyal harga penutupan candle harian.</t>
         </is>
       </c>
     </row>
@@ -6389,12 +6389,12 @@
       </c>
       <c r="C269" s="101" t="inlineStr">
         <is>
-          <t>TerraUSD / UST (Stablecoin Algoritmik Terra)</t>
+          <t>Terra/LUNA</t>
         </is>
       </c>
       <c r="D269" s="101" t="inlineStr">
         <is>
-          <t>Stablecoin algoritmik milik ekosistem blockchain Terraform Labs yang dirancang mempertahankan nilai $1 bukan melalui cadangan dolar nyata, melainkan melalui mekanisme mint-dan-burn berpasangan dengan koin LUNA. Mekanisme stabilitasnya: jika UST turun di bawah $1, siapapun bisa menukar $1 UST dengan LUNA senilai $1 (untung dari arbitrage), mengurangi suplai UST sehingga harganya naik kembali. Namun mekanisme ini memiliki kelemahan fatal: jika kepercayaan pasar runtuh bersamaan, penjualan masif LUNA yang dihasilkan justru menghancurkan nilai LUNA, melemahkan mekanisme lebih jauh — death spiral tak terhindarkan. Ini persis yang terjadi pada Mei 2022: dalam sepekan, UST kehilangan peg-nya dan LUNA dari $80 jatuh mendekati $0, menghapus lebih dari $40 miliar nilai pasar. Peristiwa ini adalah salah satu pemicu utama bear market 2022 dan contoh konkret Black Swan di pasar kripto.</t>
+          <t>Dua peristiwa katastrofik yang menjadi pemicu utama bear market kripto terpanjang dalam periode penelitian ini. Terra/LUNA: ekosistem blockchain Terraform Labs dengan stablecoin algoritmik TerraUSD (UST). Pada Mei 2022, mekanismenya mengalami "death spiral" — UST turun dari $1 memicu penjualan masif LUNA, yang semakin melemahkan kepercayaan pada UST, dan seterusnya — menghapus lebih dari $40 miliar nilai pasar dalam hitungan hari. FTX: bursa kripto besar yang terungkap pada November 2022 secara tidak sah menggunakan dana nasabah. Keduanya menjelaskan mengapa 2022 (fold WF-2 OOS) adalah tahun tersulit bagi strategi Supertrend long-only dalam penelitian ini.</t>
         </is>
       </c>
     </row>
@@ -6409,12 +6409,12 @@
       </c>
       <c r="C270" s="101" t="inlineStr">
         <is>
-          <t>Threshold (Ambang Batas)</t>
+          <t>TerraUSD / UST (Stablecoin Algoritmik Terra)</t>
         </is>
       </c>
       <c r="D270" s="101" t="inlineStr">
         <is>
-          <t>Nilai batas minimum atau maksimum yang ditetapkan sebagai kriteria evaluasi (misalnya batas nilai Sharpe Ratio atau Drawdown) untuk menentukan kelayakan performa suatu strategi perdagangan.</t>
+          <t>Stablecoin algoritmik milik ekosistem blockchain Terraform Labs yang dirancang mempertahankan nilai $1 bukan melalui cadangan dolar nyata, melainkan melalui mekanisme mint-dan-burn berpasangan dengan koin LUNA. Mekanisme stabilitasnya: jika UST turun di bawah $1, siapapun bisa menukar $1 UST dengan LUNA senilai $1 (untung dari arbitrage), mengurangi suplai UST sehingga harganya naik kembali. Namun mekanisme ini memiliki kelemahan fatal: jika kepercayaan pasar runtuh bersamaan, penjualan masif LUNA yang dihasilkan justru menghancurkan nilai LUNA, melemahkan mekanisme lebih jauh — death spiral tak terhindarkan. Ini persis yang terjadi pada Mei 2022: dalam sepekan, UST kehilangan peg-nya dan LUNA dari $80 jatuh mendekati $0, menghapus lebih dari $40 miliar nilai pasar. Peristiwa ini adalah salah satu pemicu utama bear market 2022 dan contoh konkret Black Swan di pasar kripto.</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="C271" s="101" t="inlineStr">
         <is>
-          <t>Tick Size (Satuan Pergerakan Harga Minimum)</t>
+          <t>Threshold (Ambang Batas)</t>
         </is>
       </c>
       <c r="D271" s="101" t="inlineStr">
         <is>
-          <t>Unit terkecil yang diizinkan untuk pergerakan harga suatu instrumen di bursa. Pada kontrak BTC/USDT Perpetual Futures di Bybit, tick size ditetapkan $0,1 — artinya harga hanya bisa berubah dalam kelipatan $0,1. Tick size yang sangat kecil ($0,1 dari harga Bitcoin di atas $50.000) berarti perbedaan antara harga order dan harga eksekusi akibat "granularitas harga" sangat minimal dalam kondisi pasar normal — menjadi salah satu justifikasi asumsi slippage 0,03% yang digunakan dalam simulasi.</t>
+          <t>Nilai batas minimum atau maksimum yang ditetapkan sebagai kriteria evaluasi (misalnya batas nilai Sharpe Ratio atau Drawdown) untuk menentukan kelayakan performa suatu strategi perdagangan.</t>
         </is>
       </c>
     </row>
@@ -6449,12 +6449,12 @@
       </c>
       <c r="C272" s="101" t="inlineStr">
         <is>
-          <t>Timeframe (Kerangka Waktu)</t>
+          <t>Tick Size (Satuan Pergerakan Harga Minimum)</t>
         </is>
       </c>
       <c r="D272" s="101" t="inlineStr">
         <is>
-          <t>Interval waktu yang direpresentasikan oleh setiap candle pada grafik harga — berapa lama satu "batang" data merangkum pergerakan harga. Semakin kecil timeframe, semakin banyak candle dan sinyal, tetapi semakin banyak pula noise. Semakin besar timeframe, semakin sedikit dan lebih bermakna sinyalnya, namun reaksi lebih lambat. Dalam penelitian ini, timeframe harian (D1) dipilih secara deliberat karena tiga alasan: (1) menghasilkan sinyal yang lebih bersih karena noise intraday tersaring; (2) menghasilkan jauh lebih sedikit transaksi (hanya 26 dalam 6,1 tahun) yang mengurangi akumulasi biaya komisi; dan (3) kompatibel dengan pasar kripto yang beroperasi 24/7 — sistem hanya perlu "mengecek" kondisi sekali sehari saat candle tutup.</t>
+          <t>Unit terkecil yang diizinkan untuk pergerakan harga suatu instrumen di bursa. Pada kontrak BTC/USDT Perpetual Futures di Bybit, tick size ditetapkan $0,1 — artinya harga hanya bisa berubah dalam kelipatan $0,1. Tick size yang sangat kecil ($0,1 dari harga Bitcoin di atas $50.000) berarti perbedaan antara harga order dan harga eksekusi akibat "granularitas harga" sangat minimal dalam kondisi pasar normal — menjadi salah satu justifikasi asumsi slippage 0,03% yang digunakan dalam simulasi.</t>
         </is>
       </c>
     </row>
@@ -6469,12 +6469,12 @@
       </c>
       <c r="C273" s="101" t="inlineStr">
         <is>
-          <t>Timestamp Misalignment (Ketidakselarasan Stempel Waktu)</t>
+          <t>Timeframe (Kerangka Waktu)</t>
         </is>
       </c>
       <c r="D273" s="101" t="inlineStr">
         <is>
-          <t>Kondisi bermasalah di mana dua atau lebih komponen sistem menggunakan konvensi pencatatan waktu yang berbeda, menyebabkan data untuk "momen yang sama" tidak selaras. Dalam sistem perdagangan kripto, ini bisa muncul sebagai: perbedaan zona waktu (Python memakai UTC, TradingView memakai UTC+7), perbedaan konvensi label candle (apakah timestamp candle H=8:00 artinya dimulai atau berakhir pukul 8?), atau latensi webhook (sinyal dari TradingView tiba di Bybit beberapa detik terlambat). Dalam penelitian ini, timestamp misalignment disebutkan sebagai risiko implementasi yang nyata: jika tidak ditangani dengan benar, order bisa dieksekusi pada candle yang salah.</t>
+          <t>Interval waktu yang direpresentasikan oleh setiap candle pada grafik harga — berapa lama satu "batang" data merangkum pergerakan harga. Semakin kecil timeframe, semakin banyak candle dan sinyal, tetapi semakin banyak pula noise. Semakin besar timeframe, semakin sedikit dan lebih bermakna sinyalnya, namun reaksi lebih lambat. Dalam penelitian ini, timeframe harian (D1) dipilih secara deliberat karena tiga alasan: (1) menghasilkan sinyal yang lebih bersih karena noise intraday tersaring; (2) menghasilkan jauh lebih sedikit transaksi (hanya 26 dalam 6,1 tahun) yang mengurangi akumulasi biaya komisi; dan (3) kompatibel dengan pasar kripto yang beroperasi 24/7 — sistem hanya perlu "mengecek" kondisi sekali sehari saat candle tutup.</t>
         </is>
       </c>
     </row>
@@ -6489,12 +6489,12 @@
       </c>
       <c r="C274" s="101" t="inlineStr">
         <is>
-          <t>Total Return / Net P&amp;L Kumulatif</t>
+          <t>Timestamp Misalignment (Ketidakselarasan Stempel Waktu)</t>
         </is>
       </c>
       <c r="D274" s="101" t="inlineStr">
         <is>
-          <t>Total keuntungan atau kerugian yang dihasilkan strategi sepanjang seluruh periode pengujian, dinyatakan sebagai persentase dari modal awal atau nilai nominal dolar. Berbeda dari CAGR yang "menstandarisasi" pertumbuhan per tahun, Total Return adalah akumulasi mentah: "Dari $10.000 awal, berapa yang dimiliki di akhir?" Dalam penelitian ini, metrik ini menjadi pembanding krusial: Fixed Fractional 5% Risk menghasilkan Net P&amp;L kumulatif +321,70% (modal $10.000 menjadi sekitar $42.170) vs Fixed Capital 20% Allocation hanya +66,58% (menjadi sekitar $16.658) — perbedaan dramatis yang membuktikan keunggulan manajemen risiko dinamis.</t>
+          <t>Kondisi bermasalah di mana dua atau lebih komponen sistem menggunakan konvensi pencatatan waktu yang berbeda, menyebabkan data untuk "momen yang sama" tidak selaras. Dalam sistem perdagangan kripto, ini bisa muncul sebagai: perbedaan zona waktu (Python memakai UTC, TradingView memakai UTC+7), perbedaan konvensi label candle (apakah timestamp candle H=8:00 artinya dimulai atau berakhir pukul 8?), atau latensi webhook (sinyal dari TradingView tiba di Bybit beberapa detik terlambat). Dalam penelitian ini, timestamp misalignment disebutkan sebagai risiko implementasi yang nyata: jika tidak ditangani dengan benar, order bisa dieksekusi pada candle yang salah.</t>
         </is>
       </c>
     </row>
@@ -6509,12 +6509,12 @@
       </c>
       <c r="C275" s="101" t="inlineStr">
         <is>
-          <t>Trader (Pelaku Perdagangan)</t>
+          <t>Total Return / Net P&amp;L Kumulatif</t>
         </is>
       </c>
       <c r="D275" s="101" t="inlineStr">
         <is>
-          <t>Individu atau entitas yang melakukan transaksi beli dan jual di pasar keuangan dengan tujuan memperoleh keuntungan dari selisih perubahan harga dalam jangka pendek atau menengah.</t>
+          <t>Total keuntungan atau kerugian yang dihasilkan strategi sepanjang seluruh periode pengujian, dinyatakan sebagai persentase dari modal awal atau nilai nominal dolar. Berbeda dari CAGR yang "menstandarisasi" pertumbuhan per tahun, Total Return adalah akumulasi mentah: "Dari $10.000 awal, berapa yang dimiliki di akhir?" Dalam penelitian ini, metrik ini menjadi pembanding krusial: Fixed Fractional 5% Risk menghasilkan Net P&amp;L kumulatif +321,70% (modal $10.000 menjadi sekitar $42.170) vs Fixed Capital 20% Allocation hanya +66,58% (menjadi sekitar $16.658) — perbedaan dramatis yang membuktikan keunggulan manajemen risiko dinamis.</t>
         </is>
       </c>
     </row>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="C276" s="101" t="inlineStr">
         <is>
-          <t>Trading Bot</t>
+          <t>Trader (Pelaku Perdagangan)</t>
         </is>
       </c>
       <c r="D276" s="101" t="inlineStr">
         <is>
-          <t>Program komputer yang secara otomatis mengeksekusi transaksi perdagangan berdasarkan sinyal algoritmik, tanpa memerlukan intervensi manual dari trader. Sinonim informal dari algorithmic trading system atau autotrade. Dalam penelitian ini, Python Tradingbot merujuk secara spesifik pada file Jupyter Notebook supertrend_python.ipynb yang menjadi Single Source of Truth (SSOT) akademis — berisi seluruh logika backtesting, optimasi parameter, validasi statistik, dan simulasi. Sementara untuk live trading, bot diimplementasikan melalui Pine Script v5 di TradingView yang mengirimkan order ke Bybit melalui webhook. Lihat juga: Algorithmic Trading, Autotrade, Pine Script, Jupyter Notebook.</t>
+          <t>Individu atau entitas yang melakukan transaksi beli dan jual di pasar keuangan dengan tujuan memperoleh keuntungan dari selisih perubahan harga dalam jangka pendek atau menengah.</t>
         </is>
       </c>
     </row>
@@ -6549,12 +6549,12 @@
       </c>
       <c r="C277" s="101" t="inlineStr">
         <is>
-          <t>Trading Fees (Biaya Transaksi)</t>
+          <t>Trading Bot</t>
         </is>
       </c>
       <c r="D277" s="101" t="inlineStr">
         <is>
-          <t>Biaya yang dikenakan bursa atas setiap order perdagangan yang dieksekusi — sumber utama pendapatan bursa. Ada dua struktur fee: maker fee (untuk order limit yang menambah likuiditas ke order book, biasanya lebih murah) dan taker fee (untuk order market yang langsung dieksekusi, biasanya lebih mahal). Dalam penelitian ini, seluruh sinyal Supertrend diasumsikan dieksekusi sebagai order market (taker) dengan fee 0,05% per transaksi sesuai tarif standar Bybit. Total biaya per siklus penuh (beli + jual) adalah 0,10%. Biaya ini diterapkan konsisten pada setiap transaksi simulasi untuk menghasilkan estimasi kinerja bersih yang realistis.</t>
+          <t>Program komputer yang secara otomatis mengeksekusi transaksi perdagangan berdasarkan sinyal algoritmik, tanpa memerlukan intervensi manual dari trader. Sinonim informal dari algorithmic trading system atau autotrade. Dalam penelitian ini, Python Tradingbot merujuk secara spesifik pada file Jupyter Notebook supertrend_python.ipynb yang menjadi Single Source of Truth (SSOT) akademis — berisi seluruh logika backtesting, optimasi parameter, validasi statistik, dan simulasi. Sementara untuk live trading, bot diimplementasikan melalui Pine Script v5 di TradingView yang mengirimkan order ke Bybit melalui webhook. Lihat juga: Algorithmic Trading, Autotrade, Pine Script, Jupyter Notebook.</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="C278" s="101" t="inlineStr">
         <is>
-          <t>Trading Pair (Pasangan Perdagangan)</t>
+          <t>Trading Fees (Biaya Transaksi)</t>
         </is>
       </c>
       <c r="D278" s="101" t="inlineStr">
         <is>
-          <t>Kombinasi dua aset kripto yang diperdagangkan satu sama lain di bursa (misalnya BTC/USDT), di mana aset pertama (base currency) dibeli atau dijual menggunakan aset kedua (quote currency).</t>
+          <t>Biaya yang dikenakan bursa atas setiap order perdagangan yang dieksekusi — sumber utama pendapatan bursa. Ada dua struktur fee: maker fee (untuk order limit yang menambah likuiditas ke order book, biasanya lebih murah) dan taker fee (untuk order market yang langsung dieksekusi, biasanya lebih mahal). Dalam penelitian ini, seluruh sinyal Supertrend diasumsikan dieksekusi sebagai order market (taker) dengan fee 0,05% per transaksi sesuai tarif standar Bybit. Total biaya per siklus penuh (beli + jual) adalah 0,10%. Biaya ini diterapkan konsisten pada setiap transaksi simulasi untuk menghasilkan estimasi kinerja bersih yang realistis.</t>
         </is>
       </c>
     </row>
@@ -6589,12 +6589,12 @@
       </c>
       <c r="C279" s="101" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Trading Pair (Pasangan Perdagangan)</t>
         </is>
       </c>
       <c r="D279" s="101" t="inlineStr">
         <is>
-          <t>Platform analisis teknikal berbasis web yang paling banyak digunakan di dunia, menyediakan grafik interaktif berkualitas tinggi, ratusan indikator teknikal bawaan, lingkungan pemrograman Pine Script, dan konektivitas langsung ke berbagai bursa kripto termasuk Bybit. Keunggulan yang menjadi alasan pemilihannya: sistem alert yang bisa dikonfigurasi untuk mengirim pesan webhook secara otomatis ke API bursa saat kondisi tertentu terpenuhi. Dalam penelitian ini, TradingView berfungsi sebagai "monitor" strategi: Pine Script berjalan di TradingView, mendeteksi sinyal Supertrend secara real-time, dan otomatis mengirimkan perintah ke akun Bybit melalui webhook.</t>
+          <t>Kombinasi dua aset kripto yang diperdagangkan satu sama lain di bursa (misalnya BTC/USDT), di mana aset pertama (base currency) dibeli atau dijual menggunakan aset kedua (quote currency).</t>
         </is>
       </c>
     </row>
@@ -6609,12 +6609,12 @@
       </c>
       <c r="C280" s="101" t="inlineStr">
         <is>
-          <t>Trailing Stop</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D280" s="101" t="inlineStr">
         <is>
-          <t>Variasi cerdas stop-loss yang bergerak MENGIKUTI pergerakan harga yang menguntungkan, namun tidak bergerak ke arah yang merugikan. Bayangkan tali yang diikatkan ke harga — tali ini hanya bisa diperpanjang (mengikuti harga naik), tidak bisa dipersingkat (tidak turun saat harga sedikit koreksi). Saat harga naik $1.000, trailing stop ikut naik $1.000; saat harga turun $200, trailing stop diam di posisi terakhir. Hasilnya: keuntungan yang sudah diraih "terkunci" secara bertahap. Dalam sistem Supertrend, garis Upper Band berfungsi sebagai trailing stop berbasis volatilitas: naik mengikuti harga saat tren naik, memberikan ruang napas untuk fluktuasi normal namun menutup posisi saat tren benar-benar berbalik.</t>
+          <t>Platform analisis teknikal berbasis web yang paling banyak digunakan di dunia, menyediakan grafik interaktif berkualitas tinggi, ratusan indikator teknikal bawaan, lingkungan pemrograman Pine Script, dan konektivitas langsung ke berbagai bursa kripto termasuk Bybit. Keunggulan yang menjadi alasan pemilihannya: sistem alert yang bisa dikonfigurasi untuk mengirim pesan webhook secara otomatis ke API bursa saat kondisi tertentu terpenuhi. Dalam penelitian ini, TradingView berfungsi sebagai "monitor" strategi: Pine Script berjalan di TradingView, mendeteksi sinyal Supertrend secara real-time, dan otomatis mengirimkan perintah ke akun Bybit melalui webhook.</t>
         </is>
       </c>
     </row>
@@ -6629,12 +6629,12 @@
       </c>
       <c r="C281" s="101" t="inlineStr">
         <is>
-          <t>Trend-Following (Mengikuti Tren)</t>
+          <t>Trailing Stop</t>
         </is>
       </c>
       <c r="D281" s="101" t="inlineStr">
         <is>
-          <t>Filosofi perdagangan yang sederhana namun terbukti efektif secara empiris: identifikasi tren yang sedang berlangsung, buka posisi searah tren tersebut, dan pertahankan posisi selama tren masih berlanjut. Tidak mencoba memprediksi kapan tren dimulai atau berakhir — cukup reaktif mengikuti tren yang sudah terjadi. Prinsipnya diabadikan dalam adagium: "The trend is your friend." Strategi trend-following menghasilkan profil kinerja yang khas: banyak transaksi kecil yang merugi (saat pasar sideways), namun diimbangi beberapa transaksi yang sangat menguntungkan (saat tren kuat panjang tertangkap). Supertrend adalah indikator trend-following berbasis ATR yang secara otomatis menyesuaikan sensitivitas terhadap volatilitas.</t>
+          <t>Variasi cerdas stop-loss yang bergerak MENGIKUTI pergerakan harga yang menguntungkan, namun tidak bergerak ke arah yang merugikan. Bayangkan tali yang diikatkan ke harga — tali ini hanya bisa diperpanjang (mengikuti harga naik), tidak bisa dipersingkat (tidak turun saat harga sedikit koreksi). Saat harga naik $1.000, trailing stop ikut naik $1.000; saat harga turun $200, trailing stop diam di posisi terakhir. Hasilnya: keuntungan yang sudah diraih "terkunci" secara bertahap. Dalam sistem Supertrend, garis Upper Band berfungsi sebagai trailing stop berbasis volatilitas: naik mengikuti harga saat tren naik, memberikan ruang napas untuk fluktuasi normal namun menutup posisi saat tren benar-benar berbalik.</t>
         </is>
       </c>
     </row>
@@ -6649,12 +6649,12 @@
       </c>
       <c r="C282" s="101" t="inlineStr">
         <is>
-          <t>Trend-Following Long-Only</t>
+          <t>Trend-Following (Mengikuti Tren)</t>
         </is>
       </c>
       <c r="D282" s="101" t="inlineStr">
         <is>
-          <t>Spesifikasi strategi yang menggabungkan dua keputusan metodologis utama penelitian ini: (1) menggunakan filosofi trend-following berbasis indikator Supertrend untuk menentukan timing masuk dan keluar posisi — mengikuti tren yang sudah terbentuk, bukan memprediksi; (2) hanya mengambil posisi beli (long), tidak pernah short. Kombinasi ini dipilih berdasarkan dua bukti empiris: (a) Bitcoin memiliki positive drift jangka panjang yang sangat kuat; dan (b) strategi long-only terbukti menghasilkan risk-adjusted return lebih baik dari short-only pada Bitcoin historis. Profil kinerja khasnya: win rate di bawah 50%, namun payoff ratio tinggi. Lihat juga: Trend-Following, Long-Only, Positive Drift, Supertrend.</t>
+          <t>Filosofi perdagangan yang sederhana namun terbukti efektif secara empiris: identifikasi tren yang sedang berlangsung, buka posisi searah tren tersebut, dan pertahankan posisi selama tren masih berlanjut. Tidak mencoba memprediksi kapan tren dimulai atau berakhir — cukup reaktif mengikuti tren yang sudah terjadi. Prinsipnya diabadikan dalam adagium: "The trend is your friend." Strategi trend-following menghasilkan profil kinerja yang khas: banyak transaksi kecil yang merugi (saat pasar sideways), namun diimbangi beberapa transaksi yang sangat menguntungkan (saat tren kuat panjang tertangkap). Supertrend adalah indikator trend-following berbasis ATR yang secara otomatis menyesuaikan sensitivitas terhadap volatilitas.</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="C283" s="101" t="inlineStr">
         <is>
-          <t>True Range (TR)</t>
+          <t>Trend-Following Long-Only</t>
         </is>
       </c>
       <c r="D283" s="101" t="inlineStr">
         <is>
-          <t>Komponen dasar dalam perhitungan ATR yang mengukur "rentang harga sebenarnya" dari satu candle, memperhitungkan tidak hanya selisih High dan Low hari ini, tetapi juga lompatan harga dari penutupan kemarin. True Range diambil dari nilai terbesar di antara tiga perhitungan: (1) High hari ini dikurang Low hari ini; (2) nilai absolut High hari ini dikurang Close kemarin; (3) nilai absolut Low hari ini dikurang Close kemarin. Mengapa ada pilihan (2) dan (3)? Untuk menangkap gap antar sesi — jika harga "melompat" dari penutupan kemarin ke pembukaan hari ini. ATR kemudian adalah rata-rata bergerak dari True Range menggunakan Wilder Smoothing.</t>
+          <t>Spesifikasi strategi yang menggabungkan dua keputusan metodologis utama penelitian ini: (1) menggunakan filosofi trend-following berbasis indikator Supertrend untuk menentukan timing masuk dan keluar posisi — mengikuti tren yang sudah terbentuk, bukan memprediksi; (2) hanya mengambil posisi beli (long), tidak pernah short. Kombinasi ini dipilih berdasarkan dua bukti empiris: (a) Bitcoin memiliki positive drift jangka panjang yang sangat kuat; dan (b) strategi long-only terbukti menghasilkan risk-adjusted return lebih baik dari short-only pada Bitcoin historis. Profil kinerja khasnya: win rate di bawah 50%, namun payoff ratio tinggi. Lihat juga: Trend-Following, Long-Only, Positive Drift, Supertrend.</t>
         </is>
       </c>
     </row>
@@ -6684,17 +6684,17 @@
       </c>
       <c r="B284" s="108" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C284" s="101" t="inlineStr">
         <is>
-          <t>Unknown-HighVol</t>
+          <t>True Range (TR)</t>
         </is>
       </c>
       <c r="D284" s="101" t="inlineStr">
         <is>
-          <t>Sub-kategori regime pasar: periode transisi atau kondisi tidak terklasifikasi dengan volatilitas tinggi. Biasanya terjadi di awal dataset ketika MA50 belum memiliki cukup data historis (minimal 50 candle) untuk menghasilkan sinyal yang valid. Menariknya, dalam analisis regime penelitian ini, periode Unknown-HighVol mencatat Sharpe Ratio tertinggi (3,36) di antara semua regime — mengindikasikan bahwa sinyal Supertrend sangat efektif di periode transisi awal yang volatile, kemungkinan karena tren naik kuat yang konsisten di awal periode penelitian (April 2020, awal bull market pasca-COVID). Lihat juga: Regime Pasar, MA50, Unknown-LowVol.</t>
+          <t>Komponen dasar dalam perhitungan ATR yang mengukur "rentang harga sebenarnya" dari satu candle, memperhitungkan tidak hanya selisih High dan Low hari ini, tetapi juga lompatan harga dari penutupan kemarin. True Range diambil dari nilai terbesar di antara tiga perhitungan: (1) High hari ini dikurang Low hari ini; (2) nilai absolut High hari ini dikurang Close kemarin; (3) nilai absolut Low hari ini dikurang Close kemarin. Mengapa ada pilihan (2) dan (3)? Untuk menangkap gap antar sesi — jika harga "melompat" dari penutupan kemarin ke pembukaan hari ini. ATR kemudian adalah rata-rata bergerak dari True Range menggunakan Wilder Smoothing.</t>
         </is>
       </c>
     </row>
@@ -6709,12 +6709,12 @@
       </c>
       <c r="C285" s="101" t="inlineStr">
         <is>
-          <t>Unknown-LowVol</t>
+          <t>Unknown-HighVol</t>
         </is>
       </c>
       <c r="D285" s="101" t="inlineStr">
         <is>
-          <t>Sub-kategori regime pasar: periode transisi atau kondisi tidak terklasifikasi dengan volatilitas rendah. Biasanya terjadi di awal dataset ketika MA50 belum memiliki cukup data historis (minimal 50 candle) untuk menghasilkan sinyal yang valid, namun volatilitas harian berada di bawah median historis. Dalam analisis regime penelitian ini, Unknown-LowVol mencakup candle-candle awal sebelum MA50 terbentuk yang kebetulan jatuh pada periode tenang — berbeda dari Unknown-HighVol yang mencatat Sharpe Ratio tertinggi (3,36) karena tren naik kuat awal 2020. Unknown-LowVol umumnya hanya sedikit candle dan tidak memberikan sinyal tradable yang signifikan. Lihat juga: Regime Pasar, Unknown-HighVol, MA50, Sideways-LowVol.</t>
+          <t>Sub-kategori regime pasar: periode transisi atau kondisi tidak terklasifikasi dengan volatilitas tinggi. Biasanya terjadi di awal dataset ketika MA50 belum memiliki cukup data historis (minimal 50 candle) untuk menghasilkan sinyal yang valid. Menariknya, dalam analisis regime penelitian ini, periode Unknown-HighVol mencatat Sharpe Ratio tertinggi (3,36) di antara semua regime — mengindikasikan bahwa sinyal Supertrend sangat efektif di periode transisi awal yang volatile, kemungkinan karena tren naik kuat yang konsisten di awal periode penelitian (April 2020, awal bull market pasca-COVID). Lihat juga: Regime Pasar, MA50, Unknown-LowVol.</t>
         </is>
       </c>
     </row>
@@ -6729,12 +6729,12 @@
       </c>
       <c r="C286" s="101" t="inlineStr">
         <is>
-          <t>Upper Band (Band Atas Supertrend)</t>
+          <t>Unknown-LowVol</t>
         </is>
       </c>
       <c r="D286" s="101" t="inlineStr">
         <is>
-          <t>Garis batas atas dari indikator Supertrend yang, saat tren naik aktif, berfungsi sebagai garis support dinamis dan trailing stop. Dihitung sebagai harga penutupan dikurangi (Multiplier x ATR) — semakin volatile pasar (ATR besar), semakin jauh garis ini dari harga, memberikan "ruang bernapas" lebih besar agar posisi tidak ditutup oleh fluktuasi sementara. Mekanisme Sticky Band memastikan Upper Band hanya bisa bergerak ke ATAS selama tren naik — tidak pernah turun, sehingga garis stop-loss secara bertahap "naik" mengikuti kenaikan harga dan mengunci keuntungan yang terakumulasi. Ketika harga akhirnya jatuh cukup dalam untuk menyentuh Upper Band, sinyal SELL dihasilkan dan posisi ditutup.</t>
+          <t>Sub-kategori regime pasar: periode transisi atau kondisi tidak terklasifikasi dengan volatilitas rendah. Biasanya terjadi di awal dataset ketika MA50 belum memiliki cukup data historis (minimal 50 candle) untuk menghasilkan sinyal yang valid, namun volatilitas harian berada di bawah median historis. Dalam analisis regime penelitian ini, Unknown-LowVol mencakup candle-candle awal sebelum MA50 terbentuk yang kebetulan jatuh pada periode tenang — berbeda dari Unknown-HighVol yang mencatat Sharpe Ratio tertinggi (3,36) karena tren naik kuat awal 2020. Unknown-LowVol umumnya hanya sedikit candle dan tidak memberikan sinyal tradable yang signifikan. Lihat juga: Regime Pasar, Unknown-HighVol, MA50, Sideways-LowVol.</t>
         </is>
       </c>
     </row>
@@ -6749,12 +6749,12 @@
       </c>
       <c r="C287" s="101" t="inlineStr">
         <is>
-          <t>Uptrend (Tren Naik)</t>
+          <t>Upper Band (Band Atas Supertrend)</t>
         </is>
       </c>
       <c r="D287" s="101" t="inlineStr">
         <is>
-          <t>Kondisi pasar di mana harga secara konsisten bergerak ke level yang lebih tinggi dari waktu ke waktu, membentuk pola serangkaian puncak dan lembah yang terus meningkat — seperti tangga yang terus naik. Dalam sistem Supertrend penelitian ini, uptrend dimulai ketika harga penutupan berhasil menembus ke ATAS garis Lower Band — peristiwa inilah yang memicu sinyal BUY. Selama uptrend berlangsung, garis aktif yang relevan adalah Upper Band yang terus bergerak naik sebagai trailing stop. Strategi long-only hanya AKTIF selama uptrend berlangsung — sistem menunggu dengan "kas" selama downtrend dan kembali aktif saat uptrend baru terdeteksi.</t>
+          <t>Garis batas atas dari indikator Supertrend yang, saat tren naik aktif, berfungsi sebagai garis support dinamis dan trailing stop. Dihitung sebagai harga penutupan dikurangi (Multiplier x ATR) — semakin volatile pasar (ATR besar), semakin jauh garis ini dari harga, memberikan "ruang bernapas" lebih besar agar posisi tidak ditutup oleh fluktuasi sementara. Mekanisme Sticky Band memastikan Upper Band hanya bisa bergerak ke ATAS selama tren naik — tidak pernah turun, sehingga garis stop-loss secara bertahap "naik" mengikuti kenaikan harga dan mengunci keuntungan yang terakumulasi. Ketika harga akhirnya jatuh cukup dalam untuk menyentuh Upper Band, sinyal SELL dihasilkan dan posisi ditutup.</t>
         </is>
       </c>
     </row>
@@ -6769,12 +6769,12 @@
       </c>
       <c r="C288" s="101" t="inlineStr">
         <is>
-          <t>USDT / Tether (Mata Uang Kuotasi)</t>
+          <t>Uptrend (Tren Naik)</t>
         </is>
       </c>
       <c r="D288" s="101" t="inlineStr">
         <is>
-          <t>Stablecoin yang nilainya dipatok 1:1 terhadap Dolar Amerika Serikat — satu USDT selalu bernilai $1. Tether (USDT) adalah stablecoin terbesar berdasarkan kapitalisasi pasar dan paling banyak digunakan di bursa kripto global. Dalam penelitian ini, USDT memainkan dua peran krusial: (1) sebagai mata uang kuotasi instrumen BTC/USDT Perpetual Futures — semua perhitungan harga, keuntungan, kerugian, dan biaya dinyatakan dalam USDT; dan (2) sebagai modal kolateral yang disimpan di akun Bybit. Penggunaan USDT menghilangkan "lapisan risiko" tambahan: investor tidak perlu khawatir nilai kolateralnya berfluktuasi.</t>
+          <t>Kondisi pasar di mana harga secara konsisten bergerak ke level yang lebih tinggi dari waktu ke waktu, membentuk pola serangkaian puncak dan lembah yang terus meningkat — seperti tangga yang terus naik. Dalam sistem Supertrend penelitian ini, uptrend dimulai ketika harga penutupan berhasil menembus ke ATAS garis Lower Band — peristiwa inilah yang memicu sinyal BUY. Selama uptrend berlangsung, garis aktif yang relevan adalah Upper Band yang terus bergerak naik sebagai trailing stop. Strategi long-only hanya AKTIF selama uptrend berlangsung — sistem menunggu dengan "kas" selama downtrend dan kembali aktif saat uptrend baru terdeteksi.</t>
         </is>
       </c>
     </row>
@@ -6784,17 +6784,17 @@
       </c>
       <c r="B289" s="108" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>U</t>
         </is>
       </c>
       <c r="C289" s="101" t="inlineStr">
         <is>
-          <t>Validasi Buta</t>
+          <t>USDT / Tether (Mata Uang Kuotasi)</t>
         </is>
       </c>
       <c r="D289" s="101" t="inlineStr">
         <is>
-          <t>Pengujian strategi pada data yang benar-benar belum pernah dilihat, diakses, atau digunakan selama seluruh proses pengembangan dan optimasi — disebut buta karena data OOS sengaja disembunyikan dari peneliti selama fase optimasi untuk mencegah bias tidak disadari. Sinonim dari Out-of-Sample testing dalam konteks Walk-Forward Analysis. Berbeda dari backtesting biasa di mana data yang sama digunakan untuk mengembangkan dan menguji strategi, validasi buta mensimulasikan kondisi nyata: strategi diuji di masa depan yang belum pernah dilihat sebelumnya. Dalam penelitian ini, 4 periode OOS berbeda (masing-masing ~12 bulan) berfungsi sebagai 4 lapisan validasi buta independen. Lihat juga: Out-of-Sample, Walk-Forward Analysis, Overfitting.</t>
+          <t>Stablecoin yang nilainya dipatok 1:1 terhadap Dolar Amerika Serikat — satu USDT selalu bernilai $1. Tether (USDT) adalah stablecoin terbesar berdasarkan kapitalisasi pasar dan paling banyak digunakan di bursa kripto global. Dalam penelitian ini, USDT memainkan dua peran krusial: (1) sebagai mata uang kuotasi instrumen BTC/USDT Perpetual Futures — semua perhitungan harga, keuntungan, kerugian, dan biaya dinyatakan dalam USDT; dan (2) sebagai modal kolateral yang disimpan di akun Bybit. Penggunaan USDT menghilangkan "lapisan risiko" tambahan: investor tidak perlu khawatir nilai kolateralnya berfluktuasi.</t>
         </is>
       </c>
     </row>
@@ -6809,12 +6809,12 @@
       </c>
       <c r="C290" s="101" t="inlineStr">
         <is>
-          <t>Vince, Ralph — Fixed Fractional Framework</t>
+          <t>Validasi Buta</t>
         </is>
       </c>
       <c r="D290" s="101" t="inlineStr">
         <is>
-          <t>Ralph Vince adalah ahli manajemen risiko yang mempopulerkan metode Fixed Fractional Position Sizing melalui karyanya "Portfolio Management Formulas" (1990) dan "The Mathematics of Money Management" (1992). Vince mengembangkan konsep Optimal f — fraksi optimal dari modal yang harus dipertaruhkan per transaksi untuk memaksimalkan pertumbuhan geometris modal jangka panjang. Dalam penelitian ini, kerangka Fixed Fractional yang dikembangkan Vince menjadi fondasi metode manajemen posisi yang diimplementasikan — dengan Risk per Trade 5% yang berada dalam kisaran fractional Kelly yang direkomendasikan Thorp (2006).</t>
+          <t>Pengujian strategi pada data yang benar-benar belum pernah dilihat, diakses, atau digunakan selama seluruh proses pengembangan dan optimasi — disebut buta karena data OOS sengaja disembunyikan dari peneliti selama fase optimasi untuk mencegah bias tidak disadari. Sinonim dari Out-of-Sample testing dalam konteks Walk-Forward Analysis. Berbeda dari backtesting biasa di mana data yang sama digunakan untuk mengembangkan dan menguji strategi, validasi buta mensimulasikan kondisi nyata: strategi diuji di masa depan yang belum pernah dilihat sebelumnya. Dalam penelitian ini, 4 periode OOS berbeda (masing-masing ~12 bulan) berfungsi sebagai 4 lapisan validasi buta independen. Lihat juga: Out-of-Sample, Walk-Forward Analysis, Overfitting.</t>
         </is>
       </c>
     </row>
@@ -6829,12 +6829,12 @@
       </c>
       <c r="C291" s="101" t="inlineStr">
         <is>
-          <t>Volatilitas (Volatility)</t>
+          <t>Vince, Ralph — Fixed Fractional Framework</t>
         </is>
       </c>
       <c r="D291" s="101" t="inlineStr">
         <is>
-          <t>Ukuran seberapa besar dan seberapa cepat harga suatu aset berubah-ubah dalam periode tertentu. Bitcoin memiliki volatilitas yang jauh lebih tinggi dari aset konvensional: volatilitas harian rata-rata Bitcoin sekitar 4,8% vs indeks saham S&amp;P 500 sekitar 0,7% — perbedaan yang mencerminkan risiko sekaligus peluang. Dalam sistem Supertrend penelitian ini, volatilitas adalah konsep fondasi yang menghubungkan seluruh komponen: ATR mengukur volatilitas terkini → Multiplier x ATR menentukan lebar band → lebar band menentukan sensitivitas sinyal → dan Fixed Fractional Position Sizing menggunakan lebar band sebagai jarak stop-loss untuk menentukan ukuran posisi.</t>
+          <t>Ralph Vince adalah ahli manajemen risiko yang mempopulerkan metode Fixed Fractional Position Sizing melalui karyanya "Portfolio Management Formulas" (1990) dan "The Mathematics of Money Management" (1992). Vince mengembangkan konsep Optimal f — fraksi optimal dari modal yang harus dipertaruhkan per transaksi untuk memaksimalkan pertumbuhan geometris modal jangka panjang. Dalam penelitian ini, kerangka Fixed Fractional yang dikembangkan Vince menjadi fondasi metode manajemen posisi yang diimplementasikan — dengan Risk per Trade 5% yang berada dalam kisaran fractional Kelly yang direkomendasikan Thorp (2006).</t>
         </is>
       </c>
     </row>
@@ -6849,12 +6849,12 @@
       </c>
       <c r="C292" s="101" t="inlineStr">
         <is>
-          <t>Volatility-Adjusted Position Sizing (Penentuan Ukuran Posisi Berbasis Volatilitas)</t>
+          <t>Volatilitas (Volatility)</t>
         </is>
       </c>
       <c r="D292" s="101" t="inlineStr">
         <is>
-          <t>Pendekatan manajemen risiko di mana ukuran posisi setiap transaksi disesuaikan secara otomatis dengan tingkat volatilitas pasar saat itu, sehingga risiko nominal (dalam dolar) yang dipertaruhkan per transaksi tetap konstan. Prinsipnya: saat pasar sangat volatile (ATR besar, stop-loss harus ditempatkan lebih jauh), ukuran posisi diperkecil agar "kerugian maksimal jika stop-loss tersentuh" tetap sama 5%. Saat pasar tenang (ATR kecil, stop-loss lebih dekat), posisi bisa diperbesar. Ini adalah inti mekanisme Fixed Fractional Position Sizing: karena stop-loss selalu merupakan kelipatan ATR, sistem secara otomatis menyesuaikan ukuran posisi dengan kondisi volatilitas tanpa intervensi manual.</t>
+          <t>Ukuran seberapa besar dan seberapa cepat harga suatu aset berubah-ubah dalam periode tertentu. Bitcoin memiliki volatilitas yang jauh lebih tinggi dari aset konvensional: volatilitas harian rata-rata Bitcoin sekitar 4,8% vs indeks saham S&amp;P 500 sekitar 0,7% — perbedaan yang mencerminkan risiko sekaligus peluang. Dalam sistem Supertrend penelitian ini, volatilitas adalah konsep fondasi yang menghubungkan seluruh komponen: ATR mengukur volatilitas terkini → Multiplier x ATR menentukan lebar band → lebar band menentukan sensitivitas sinyal → dan Fixed Fractional Position Sizing menggunakan lebar band sebagai jarak stop-loss untuk menentukan ukuran posisi.</t>
         </is>
       </c>
     </row>
@@ -6864,17 +6864,17 @@
       </c>
       <c r="B293" s="108" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C293" s="101" t="inlineStr">
         <is>
-          <t>Walk-Forward Analysis (WFA)</t>
+          <t>Volatility-Adjusted Position Sizing (Penentuan Ukuran Posisi Berbasis Volatilitas)</t>
         </is>
       </c>
       <c r="D293" s="101" t="inlineStr">
         <is>
-          <t>Metode validasi strategi perdagangan yang jauh lebih kuat dari backtesting biasa karena mensimulasikan proses yang dilakukan peneliti/trader dalam kondisi nyata. Caranya: data historis dibagi menjadi beberapa pasang periode latih (In-Sample) dan periode uji (Out-of-Sample) secara berurutan maju dalam waktu: (1) gunakan IS pertama untuk mencari parameter optimal; (2) uji parameter tersebut di OOS pertama yang belum pernah "dilihat"; (3) geser jendela waktu maju; (4) ulangi. Dengan melakukan ini di 4 fold berbeda (seperti dalam penelitian ini), peneliti dapat melihat apakah strategi bekerja konsisten di berbagai periode pasar. Konsistensi kinerja di keempat OOS adalah bukti terkuat bahwa strategi memiliki edge yang generalizable.</t>
+          <t>Pendekatan manajemen risiko di mana ukuran posisi setiap transaksi disesuaikan secara otomatis dengan tingkat volatilitas pasar saat itu, sehingga risiko nominal (dalam dolar) yang dipertaruhkan per transaksi tetap konstan. Prinsipnya: saat pasar sangat volatile (ATR besar, stop-loss harus ditempatkan lebih jauh), ukuran posisi diperkecil agar "kerugian maksimal jika stop-loss tersentuh" tetap sama 5%. Saat pasar tenang (ATR kecil, stop-loss lebih dekat), posisi bisa diperbesar. Ini adalah inti mekanisme Fixed Fractional Position Sizing: karena stop-loss selalu merupakan kelipatan ATR, sistem secara otomatis menyesuaikan ukuran posisi dengan kondisi volatilitas tanpa intervensi manual.</t>
         </is>
       </c>
     </row>
@@ -6889,12 +6889,12 @@
       </c>
       <c r="C294" s="101" t="inlineStr">
         <is>
-          <t>Walk-Forward Rubric (Rubrik Evaluasi Walk-Forward)</t>
+          <t>Walk-Forward Analysis (WFA)</t>
         </is>
       </c>
       <c r="D294" s="101" t="inlineStr">
         <is>
-          <t>Sistem penilaian kualitatif (terdiri dari predikat KUAT, MODERAT, dan LEMAH) yang digunakan untuk menilai konsistensi hasil pengujian Walk-Forward berdasarkan persentase split OOS yang profitabel dan efisiensi rasio kinerja.</t>
+          <t>Metode validasi strategi perdagangan yang jauh lebih kuat dari backtesting biasa karena mensimulasikan proses yang dilakukan peneliti/trader dalam kondisi nyata. Caranya: data historis dibagi menjadi beberapa pasang periode latih (In-Sample) dan periode uji (Out-of-Sample) secara berurutan maju dalam waktu: (1) gunakan IS pertama untuk mencari parameter optimal; (2) uji parameter tersebut di OOS pertama yang belum pernah "dilihat"; (3) geser jendela waktu maju; (4) ulangi. Dengan melakukan ini di 4 fold berbeda (seperti dalam penelitian ini), peneliti dapat melihat apakah strategi bekerja konsisten di berbagai periode pasar. Konsistensi kinerja di keempat OOS adalah bukti terkuat bahwa strategi memiliki edge yang generalizable.</t>
         </is>
       </c>
     </row>
@@ -6909,12 +6909,12 @@
       </c>
       <c r="C295" s="101" t="inlineStr">
         <is>
-          <t>Webhook (Mekanisme Penerusan Sinyal)</t>
+          <t>Walk-Forward Rubric (Rubrik Evaluasi Walk-Forward)</t>
         </is>
       </c>
       <c r="D295" s="101" t="inlineStr">
         <is>
-          <t>Mekanisme komunikasi otomatis berbasis internet di mana sistem A secara proaktif mengirimkan notifikasi ke sistem B melalui permintaan HTTP ketika suatu peristiwa terjadi — tanpa perlu sistem B terus-menerus "menanyakan" apakah ada update baru. Analoginya: bukan Anda yang terus menelepon bank menanyakan "ada transaksi baru?" (polling), melainkan bank yang langsung mengirim SMS notifikasi ke Anda saat transaksi terjadi (webhook). Dalam penelitian ini, webhook adalah komponen kritis yang menghubungkan TradingView dan Bybit: saat Pine Script mendeteksi sinyal Supertrend, ia otomatis mengirimkan instruksi order ke URL API Bybit yang sudah dikonfigurasi — seluruh proses terjadi dalam hitungan detik tanpa intervensi manual.</t>
+          <t>Sistem penilaian kualitatif (terdiri dari predikat KUAT, MODERAT, dan LEMAH) yang digunakan untuk menilai konsistensi hasil pengujian Walk-Forward berdasarkan persentase split OOS yang profitabel dan efisiensi rasio kinerja.</t>
         </is>
       </c>
     </row>
@@ -6929,12 +6929,12 @@
       </c>
       <c r="C296" s="101" t="inlineStr">
         <is>
-          <t>WF Efficiency Ratio</t>
+          <t>Webhook (Mekanisme Penerusan Sinyal)</t>
         </is>
       </c>
       <c r="D296" s="101" t="inlineStr">
         <is>
-          <t>Label yang digunakan dalam output Python Tradingbot untuk metrik IS/OOS Efficiency Ratio — keduanya merujuk pada konsep yang PERSIS SAMA: rasio Sharpe Ratio Out-of-Sample (OOS) dibagi Sharpe Ratio In-Sample (IS) dalam Walk-Forward Analysis. Istilah "WF Efficiency Ratio" muncul secara spesifik pada tabel ringkasan scorecard Python (Cell 37–40) dan tabel WFA per-split (Cell 29), sedangkan "IS/OOS Efficiency Ratio" digunakan dalam penjelasan metodologis naskah. Nilai ≥ 0,5 mengindikasikan transfer kinerja yang memuaskan dari data latih ke data uji; nilai negatif mengindikasikan overfitting parah. Dalam penelitian ini, rata-rata WF Efficiency Ratio dari 4 fold WFA adalah −0,12 — dipengaruhi besar oleh split WF-1 (OOS 2022, bear market ekstrem), namun 3 dari 4 split tetap mencatat nilai positif. Lihat juga: IS/OOS Efficiency Ratio, Walk-Forward Analysis, Sharpe Ratio, OOS.</t>
+          <t>Mekanisme komunikasi otomatis berbasis internet di mana sistem A secara proaktif mengirimkan notifikasi ke sistem B melalui permintaan HTTP ketika suatu peristiwa terjadi — tanpa perlu sistem B terus-menerus "menanyakan" apakah ada update baru. Analoginya: bukan Anda yang terus menelepon bank menanyakan "ada transaksi baru?" (polling), melainkan bank yang langsung mengirim SMS notifikasi ke Anda saat transaksi terjadi (webhook). Dalam penelitian ini, webhook adalah komponen kritis yang menghubungkan TradingView dan Bybit: saat Pine Script mendeteksi sinyal Supertrend, ia otomatis mengirimkan instruksi order ke URL API Bybit yang sudah dikonfigurasi — seluruh proses terjadi dalam hitungan detik tanpa intervensi manual.</t>
         </is>
       </c>
     </row>
@@ -6949,12 +6949,12 @@
       </c>
       <c r="C297" s="101" t="inlineStr">
         <is>
-          <t>WF-1 / WF-2 / WF-3 / WF-4 (Label Split Walk-Forward)</t>
+          <t>WF Efficiency Ratio</t>
         </is>
       </c>
       <c r="D297" s="101" t="inlineStr">
         <is>
-          <t>Label bernomor yang digunakan dalam penelitian ini untuk merujuk pada keempat split (pasang periode IS/OOS) dalam Walk-Forward Analysis secara individual. Setiap label terdiri dari 'WF-' diikuti nomor urut split: WF-1: IS April 2020–Des 2021 → OOS Jan–Des 2022 (tahun paling menantang: kolaps Terra/LUNA &amp; FTX, bear market ekstrem); WF-2: IS April 2020–Des 2022 → OOS Jan–Des 2023 (periode pemulihan pasca-bear market); WF-3: IS April 2020–Des 2023 → OOS Jan–Des 2024 (bull market pasca-halving April 2024, split terbaik untuk Supertrend); WF-4: IS April 2020–Des 2024 → OOS Jan–Des 2025 (pasar sideways–konsolidasi). Keempat label ini dikunci secara eksplisit dalam variabel WF_SPLITS di Cell 2 Python Tradingbot (SSOT) — peneliti yang menjalankan kode setelah periode berlalu tidak perlu mengubah WF_SPLITS karena kode tetap mengambil data historis dari Bybit API sesuai rentang tanggal yang sudah di-hardcode. Konsistensi kinerja positif di keempat split OOS adalah bukti terkuat bahwa strategi tidak overfit ke satu periode pasar tertentu. Lihat juga: Walk-Forward Analysis, Split, Fold, IS, OOS.</t>
+          <t>Label yang digunakan dalam output Python Tradingbot untuk metrik IS/OOS Efficiency Ratio — keduanya merujuk pada konsep yang PERSIS SAMA: rasio Sharpe Ratio Out-of-Sample (OOS) dibagi Sharpe Ratio In-Sample (IS) dalam Walk-Forward Analysis. Istilah "WF Efficiency Ratio" muncul secara spesifik pada tabel ringkasan scorecard Python (Cell 37–40) dan tabel WFA per-split (Cell 29), sedangkan "IS/OOS Efficiency Ratio" digunakan dalam penjelasan metodologis naskah. Nilai ≥ 0,5 mengindikasikan transfer kinerja yang memuaskan dari data latih ke data uji; nilai negatif mengindikasikan overfitting parah. Dalam penelitian ini, rata-rata WF Efficiency Ratio dari 4 fold WFA adalah −0,12 — dipengaruhi besar oleh split WF-1 (OOS 2022, bear market ekstrem), namun 3 dari 4 split tetap mencatat nilai positif. Lihat juga: IS/OOS Efficiency Ratio, Walk-Forward Analysis, Sharpe Ratio, OOS.</t>
         </is>
       </c>
     </row>
@@ -6969,12 +6969,12 @@
       </c>
       <c r="C298" s="101" t="inlineStr">
         <is>
-          <t>Whipsaw</t>
+          <t>WF-1 / WF-2 / WF-3 / WF-4 (Label Split Walk-Forward)</t>
         </is>
       </c>
       <c r="D298" s="101" t="inlineStr">
         <is>
-          <t>Kondisi frustrasi bagi strategi trend-following: sinyal beli dan jual bergantian muncul dalam waktu sangat singkat karena harga bergerak naik-turun tanpa membentuk tren yang jelas (sideways). Setiap transaksi individual ruginya kecil, namun jika terjadi banyak whipsaw berturut-turut, akumulasinya bisa signifikan — "kematian dengan seribu luka." Dua mekanisme utama menekan whipsaw dalam penelitian ini: Sticky Band (mencegah band bergerak-gerak bolak-balik) dan Multiplier = 3,0 (membutuhkan pergerakan cukup besar sebelum memicu sinyal). Hasilnya: hanya 26 transaksi dalam 6,1 tahun, dengan sangat sedikit sinyal whipsaw.</t>
+          <t>Label bernomor yang digunakan dalam penelitian ini untuk merujuk pada keempat split (pasang periode IS/OOS) dalam Walk-Forward Analysis secara individual. Setiap label terdiri dari 'WF-' diikuti nomor urut split: WF-1: IS April 2020–Des 2021 → OOS Jan–Des 2022 (tahun paling menantang: kolaps Terra/LUNA &amp; FTX, bear market ekstrem); WF-2: IS April 2020–Des 2022 → OOS Jan–Des 2023 (periode pemulihan pasca-bear market); WF-3: IS April 2020–Des 2023 → OOS Jan–Des 2024 (bull market pasca-halving April 2024, split terbaik untuk Supertrend); WF-4: IS April 2020–Des 2024 → OOS Jan–Des 2025 (pasar sideways–konsolidasi). Keempat label ini dikunci secara eksplisit dalam variabel WF_SPLITS di Cell 2 Python Tradingbot (SSOT) — peneliti yang menjalankan kode setelah periode berlalu tidak perlu mengubah WF_SPLITS karena kode tetap mengambil data historis dari Bybit API sesuai rentang tanggal yang sudah di-hardcode. Konsistensi kinerja positif di keempat split OOS adalah bukti terkuat bahwa strategi tidak overfit ke satu periode pasar tertentu. Lihat juga: Walk-Forward Analysis, Split, Fold, IS, OOS.</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="C299" s="101" t="inlineStr">
         <is>
-          <t>Wilder Smoothing (RMA)</t>
+          <t>Whipsaw</t>
         </is>
       </c>
       <c r="D299" s="101" t="inlineStr">
         <is>
-          <t>Metode khusus perhitungan rata-rata bergerak yang diperkenalkan oleh Welles Wilder (1978) — sang pencipta ATR, RSI, dan Parabolic SAR. Secara matematis identik dengan EMA namun dengan faktor pemulusan alpha = 1/n (lebih kecil dari EMA konvensional yang menggunakan 2/(n+1)), sehingga memberikan "memori" yang lebih panjang dan respons yang lebih halus terhadap perubahan nilai baru. Juga dikenal sebagai RMA (Running Moving Average). Perbedaan praktis: Wilder Smoothing dengan n=7 tidak "melupakan" data tua secepat EMA dengan n=7 yang sama, menghasilkan estimasi ATR yang lebih stabil. Dalam penelitian ini, RMA digunakan secara konsisten pada kedua implementasi (Python Tradingbot dan Pine Script v5) untuk menghitung ATR.</t>
+          <t>Kondisi frustrasi bagi strategi trend-following: sinyal beli dan jual bergantian muncul dalam waktu sangat singkat karena harga bergerak naik-turun tanpa membentuk tren yang jelas (sideways). Setiap transaksi individual ruginya kecil, namun jika terjadi banyak whipsaw berturut-turut, akumulasinya bisa signifikan — "kematian dengan seribu luka." Dua mekanisme utama menekan whipsaw dalam penelitian ini: Sticky Band (mencegah band bergerak-gerak bolak-balik) dan Multiplier = 3,0 (membutuhkan pergerakan cukup besar sebelum memicu sinyal). Hasilnya: hanya 26 transaksi dalam 6,1 tahun, dengan sangat sedikit sinyal whipsaw.</t>
         </is>
       </c>
     </row>
@@ -7009,10 +7009,30 @@
       </c>
       <c r="C300" s="101" t="inlineStr">
         <is>
+          <t>Wilder Smoothing (RMA)</t>
+        </is>
+      </c>
+      <c r="D300" s="101" t="inlineStr">
+        <is>
+          <t>Metode khusus perhitungan rata-rata bergerak yang diperkenalkan oleh Welles Wilder (1978) — sang pencipta ATR, RSI, dan Parabolic SAR. Secara matematis identik dengan EMA namun dengan faktor pemulusan alpha = 1/n (lebih kecil dari EMA konvensional yang menggunakan 2/(n+1)), sehingga memberikan "memori" yang lebih panjang dan respons yang lebih halus terhadap perubahan nilai baru. Juga dikenal sebagai RMA (Running Moving Average). Perbedaan praktis: Wilder Smoothing dengan n=7 tidak "melupakan" data tua secepat EMA dengan n=7 yang sama, menghasilkan estimasi ATR yang lebih stabil. Dalam penelitian ini, RMA digunakan secara konsisten pada kedua implementasi (Python Tradingbot dan Pine Script v5) untuk menghitung ATR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="107" t="n">
+        <v>298</v>
+      </c>
+      <c r="B301" s="108" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C301" s="101" t="inlineStr">
+        <is>
           <t>Win Rate</t>
         </is>
       </c>
-      <c r="D300" s="101" t="inlineStr">
+      <c r="D301" s="101" t="inlineStr">
         <is>
           <t>Persentase dari total transaksi yang menghasilkan keuntungan bersih. Win Rate 46,15% dalam penelitian ini berarti dari setiap 100 transaksi, 46 berhasil menguntungkan dan 54 merugi. Win Rate di bawah 50% mungkin terdengar buruk — lebih banyak yang kalah dari yang menang. Namun ini adalah kesalahpahaman umum: Win Rate saja tidak cukup tanpa mempertimbangkan Payoff Ratio. Strategi trend-following yang baik biasanya memiliki Win Rate rendah namun Payoff Ratio sangat tinggi — sedikit kali menang, namun saat menang hasilnya besar. Kombinasi Win Rate 46,15% dan Payoff Ratio 3,84 menghasilkan ekspektansi positif +$1.228,59 per transaksi — sistem yang menguntungkan meskipun lebih sering kalah.</t>
         </is>

--- a/daftar_istilah.xlsx
+++ b/daftar_istilah.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr/>
   <bookViews>
-    <workbookView firstSheet="4" activeTab="11"/>
+    <workbookView firstSheet="2" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" name="Daftar Istilah" sheetId="1"/>
@@ -920,7 +920,14 @@
     <t>Kelly Criterion (Kriteria Kelly)</t>
   </si>
   <si>
-    <t>Formula matematis yang menentukan berapa persen modal yang seharusnya dipertaruhkan pada setiap transaksi untuk memaksimalkan pertumbuhan modal jangka panjang secara geometris. Dikembangkan oleh John Kelly Jr. pada 1956. Dalam praktik, para profesional biasanya menggunakan "fractional Kelly" (setengah atau seperempat dari nilai Kelly penuh) untuk mengurangi volatilitas — karena Kelly penuh seringkali terlalu agresif. Batas atas 5% Risk per Trade dalam penelitian ini didasarkan pada kisaran fractional Kelly yang direkomendasikan oleh Thorp (2006), memastikan pertumbuhan yang optimal tanpa mengambil risiko berlebihan.</t>
+    <t>Formula matematis yang digunakan untuk menentukan ukuran posisi optimal (fraksi modal) pada setiap transaksi untuk memaksimalkan pertumbuhan modal jangka panjang secara geometris berdasarkan probabilitas keuntungan (win rate) dan rasio keuntungan/kerugian (reward-to-risk ratio).
+Formulanya adalah: f* = (bp - q) / b, di mana:
+- f* adalah fraksi modal yang dipertaruhkan.
+- p adalah peluang menang (win rate).
+- q adalah peluang kalah (1 - p).
+- b adalah rasio pembayaran (reward-to-risk ratio, yaitu rata-rata keuntungan dibagi rata-rata kerugian).
+Sebagai analogi sederhana, bayangkan permainan lempar koin berat sebelah (biased coin) dengan peluang angka (menang) sebesar 60% (p = 0,60) dan peluang gambar (kalah) sebesar 40% (q = 0,40) dengan pembayaran 1:1 (b = 1). Maka f* = (1 x 0,60 - 0,40) / 1 = 0,20, sehingga ukuran taruhan yang optimal adalah 20% dari total modal. Jika peluang menang turun menjadi 40% (p = 0,40) tetapi dengan pembayaran 2:1 (b = 2), maka f* = (2 x 0,40 - 0,60) / 2 = 0,10, sehingga ukuran taruhan optimal menjadi 10% dari modal. Jika hasil rumus bernilai negatif (f* &lt; 0), hal itu berarti transaksi memiliki ekspektasi negatif dan tidak boleh diambil.
+Dalam praktik perdagangan nyata, kriteria Kelly penuh (Full Kelly) jarang digunakan karena menghasilkan volatilitas ekuitas yang sangat tinggi. Trader profesional umumnya menerapkan 'fractional Kelly' (seperti Half-Kelly atau Quarter-Kelly) dengan mengambil sebagian kecil saja dari f* (misal 1/4 dari hasil Kelly) untuk mengurangi fluktuasi modal dan menghindari risiko kebangkrutan (risk of ruin) akibat fluktuasi tak terduga. Batas atas fraksi risiko 5% yang diuji dalam penelitian ini terinspirasi dari penerapan fractional Kelly yang direkomendasikan oleh Thorp (2006), untuk mencapai pertumbuhan modal yang optimal secara aman di pasar kripto yang volatil.</t>
   </si>
   <si>
     <t>Koreksi Multiple Comparison (Harvey et al., 2016)</t>
@@ -2146,13 +2153,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i val="0"/>
-      <sz val="14"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -2178,6 +2178,13 @@
     <font>
       <b/>
       <i val="0"/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <i val="0"/>
       <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
@@ -2192,17 +2199,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F3864"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF2E75B6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
       </patternFill>
     </fill>
   </fills>
@@ -2235,38 +2242,38 @@
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" quotePrefix="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" quotePrefix="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" quotePrefix="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" quotePrefix="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" quotePrefix="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" quotePrefix="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" quotePrefix="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" xfId="0" quotePrefix="0">
+    <xf numFmtId="10" fontId="2" fillId="3" borderId="1" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" quotePrefix="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2584,33 +2591,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{AFC9E39E-675E-4164-ACAF-E3D990B0C426}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{7C608A20-C524-4CF0-A7CD-48E2962B680D}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:D301"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="6.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="8.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="35.00390625" customWidth="1"/>
-    <col min="4" max="4" style="1" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="6.00390625" customWidth="1"/>
+    <col min="2" max="2" width="8.00390625" customWidth="1"/>
+    <col min="3" max="3" width="35.00390625" customWidth="1"/>
+    <col min="4" max="4" width="80.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="1" customFormat="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" ht="21.75" customHeight="1" s="1" customFormat="1">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" ht="21.75" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -2624,7 +2631,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -2638,7 +2645,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="147.75" customHeight="1">
       <c r="A5" s="5">
         <v>2</v>
       </c>
@@ -2652,7 +2659,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="6" ht="122.25" customHeight="1">
       <c r="A6" s="5">
         <v>3</v>
       </c>
@@ -2666,7 +2673,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="7" ht="159.75" customHeight="1">
       <c r="A7" s="5">
         <v>4</v>
       </c>
@@ -2680,7 +2687,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="8" ht="159.75" customHeight="1">
       <c r="A8" s="5">
         <v>5</v>
       </c>
@@ -2694,7 +2701,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="9" ht="147.75" customHeight="1">
       <c r="A9" s="5">
         <v>6</v>
       </c>
@@ -2708,7 +2715,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" ht="197.25" customHeight="1" s="1" customFormat="1">
+    <row r="10" ht="197.25" customHeight="1">
       <c r="A10" s="5">
         <v>7</v>
       </c>
@@ -2722,7 +2729,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="11" ht="159.75" customHeight="1">
       <c r="A11" s="5">
         <v>8</v>
       </c>
@@ -2736,7 +2743,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" ht="197.25" customHeight="1" s="1" customFormat="1">
+    <row r="12" ht="197.25" customHeight="1">
       <c r="A12" s="5">
         <v>9</v>
       </c>
@@ -2750,7 +2757,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="13" ht="135" customHeight="1">
       <c r="A13" s="5">
         <v>10</v>
       </c>
@@ -2764,7 +2771,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" ht="172.5" customHeight="1" s="1" customFormat="1">
+    <row r="14" ht="172.5" customHeight="1">
       <c r="A14" s="5">
         <v>11</v>
       </c>
@@ -2778,7 +2785,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="15" ht="147.75" customHeight="1">
       <c r="A15" s="5">
         <v>12</v>
       </c>
@@ -2792,7 +2799,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="16" ht="122.25" customHeight="1">
       <c r="A16" s="5">
         <v>13</v>
       </c>
@@ -2806,7 +2813,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="17" ht="97.5" customHeight="1">
       <c r="A17" s="5">
         <v>14</v>
       </c>
@@ -2820,7 +2827,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="18" ht="97.5" customHeight="1">
       <c r="A18" s="5">
         <v>15</v>
       </c>
@@ -2834,7 +2841,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="19" ht="147.75" customHeight="1">
       <c r="A19" s="5">
         <v>16</v>
       </c>
@@ -2848,7 +2855,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="20" ht="159.75" customHeight="1">
       <c r="A20" s="5">
         <v>17</v>
       </c>
@@ -2862,7 +2869,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="21" ht="147.75" customHeight="1">
       <c r="A21" s="5">
         <v>18</v>
       </c>
@@ -2876,7 +2883,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="22" ht="159.75" customHeight="1">
       <c r="A22" s="5">
         <v>19</v>
       </c>
@@ -2890,7 +2897,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1" s="1" customFormat="1">
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="5">
         <v>20</v>
       </c>
@@ -2904,7 +2911,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="24" ht="122.25" customHeight="1">
       <c r="A24" s="5">
         <v>21</v>
       </c>
@@ -2918,7 +2925,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="25" ht="97.5" customHeight="1">
       <c r="A25" s="5">
         <v>22</v>
       </c>
@@ -2932,7 +2939,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="26" ht="159.75" customHeight="1">
       <c r="A26" s="5">
         <v>23</v>
       </c>
@@ -2946,7 +2953,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="27" ht="159.75" customHeight="1">
       <c r="A27" s="5">
         <v>24</v>
       </c>
@@ -2960,7 +2967,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="28" ht="97.5" customHeight="1">
       <c r="A28" s="5">
         <v>25</v>
       </c>
@@ -2974,7 +2981,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="29" ht="97.5" customHeight="1">
       <c r="A29" s="5">
         <v>26</v>
       </c>
@@ -2988,7 +2995,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="30" ht="122.25" customHeight="1">
       <c r="A30" s="5">
         <v>27</v>
       </c>
@@ -3002,7 +3009,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="31" ht="159.75" customHeight="1">
       <c r="A31" s="5">
         <v>28</v>
       </c>
@@ -3016,7 +3023,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="32" ht="185.25" customHeight="1" s="1" customFormat="1">
+    <row r="32" ht="185.25" customHeight="1">
       <c r="A32" s="5">
         <v>29</v>
       </c>
@@ -3030,7 +3037,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="33" ht="147.75" customHeight="1">
       <c r="A33" s="5">
         <v>30</v>
       </c>
@@ -3044,7 +3051,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="34" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="34" ht="135" customHeight="1">
       <c r="A34" s="5">
         <v>31</v>
       </c>
@@ -3058,7 +3065,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="35" ht="147.75" customHeight="1">
       <c r="A35" s="5">
         <v>32</v>
       </c>
@@ -3072,7 +3079,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="36" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="36" ht="147.75" customHeight="1">
       <c r="A36" s="5">
         <v>33</v>
       </c>
@@ -3086,7 +3093,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="37" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="37" ht="97.5" customHeight="1">
       <c r="A37" s="5">
         <v>34</v>
       </c>
@@ -3100,7 +3107,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="38" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="38" ht="122.25" customHeight="1">
       <c r="A38" s="5">
         <v>35</v>
       </c>
@@ -3114,7 +3121,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="39" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="39" ht="110.25" customHeight="1">
       <c r="A39" s="5">
         <v>36</v>
       </c>
@@ -3128,7 +3135,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="40" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="40" ht="122.25" customHeight="1">
       <c r="A40" s="5">
         <v>37</v>
       </c>
@@ -3142,7 +3149,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="41" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="41" ht="147.75" customHeight="1">
       <c r="A41" s="5">
         <v>38</v>
       </c>
@@ -3156,7 +3163,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="42" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="42" ht="147.75" customHeight="1">
       <c r="A42" s="5">
         <v>39</v>
       </c>
@@ -3170,7 +3177,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="43" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="43" ht="110.25" customHeight="1">
       <c r="A43" s="5">
         <v>40</v>
       </c>
@@ -3184,7 +3191,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="44" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="44" ht="122.25" customHeight="1">
       <c r="A44" s="5">
         <v>41</v>
       </c>
@@ -3198,7 +3205,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="45" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="45" ht="97.5" customHeight="1">
       <c r="A45" s="5">
         <v>42</v>
       </c>
@@ -3212,7 +3219,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="46" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="46" ht="97.5" customHeight="1">
       <c r="A46" s="5">
         <v>43</v>
       </c>
@@ -3226,7 +3233,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="47" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="47" ht="135" customHeight="1">
       <c r="A47" s="5">
         <v>44</v>
       </c>
@@ -3240,7 +3247,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="48" ht="172.5" customHeight="1" s="1" customFormat="1">
+    <row r="48" ht="172.5" customHeight="1">
       <c r="A48" s="5">
         <v>45</v>
       </c>
@@ -3254,7 +3261,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="49" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="49" ht="122.25" customHeight="1">
       <c r="A49" s="5">
         <v>46</v>
       </c>
@@ -3268,7 +3275,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="50" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="50" ht="135" customHeight="1">
       <c r="A50" s="5">
         <v>47</v>
       </c>
@@ -3282,7 +3289,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="51" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="51" ht="122.25" customHeight="1">
       <c r="A51" s="5">
         <v>48</v>
       </c>
@@ -3296,7 +3303,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="52" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="52" ht="110.25" customHeight="1">
       <c r="A52" s="5">
         <v>49</v>
       </c>
@@ -3310,7 +3317,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="53" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="53" ht="122.25" customHeight="1">
       <c r="A53" s="5">
         <v>50</v>
       </c>
@@ -3324,7 +3331,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="54" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="54" ht="135" customHeight="1">
       <c r="A54" s="5">
         <v>51</v>
       </c>
@@ -3338,7 +3345,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="55" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="55" ht="147.75" customHeight="1">
       <c r="A55" s="5">
         <v>52</v>
       </c>
@@ -3352,7 +3359,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="56" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="56" ht="135" customHeight="1">
       <c r="A56" s="5">
         <v>53</v>
       </c>
@@ -3366,7 +3373,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="57" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="57" ht="47.25" customHeight="1">
       <c r="A57" s="5">
         <v>54</v>
       </c>
@@ -3380,7 +3387,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="58" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="58" ht="147.75" customHeight="1">
       <c r="A58" s="5">
         <v>55</v>
       </c>
@@ -3394,7 +3401,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="59" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="59" ht="159.75" customHeight="1">
       <c r="A59" s="5">
         <v>56</v>
       </c>
@@ -3408,7 +3415,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="60" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="60" ht="110.25" customHeight="1">
       <c r="A60" s="5">
         <v>57</v>
       </c>
@@ -3422,7 +3429,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="61" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="61" ht="47.25" customHeight="1">
       <c r="A61" s="5">
         <v>58</v>
       </c>
@@ -3436,7 +3443,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="62" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="62" ht="122.25" customHeight="1">
       <c r="A62" s="5">
         <v>59</v>
       </c>
@@ -3450,7 +3457,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="63" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="63" ht="147.75" customHeight="1">
       <c r="A63" s="5">
         <v>60</v>
       </c>
@@ -3464,7 +3471,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="64" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="64" ht="122.25" customHeight="1">
       <c r="A64" s="5">
         <v>61</v>
       </c>
@@ -3478,7 +3485,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="65" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="65" ht="122.25" customHeight="1">
       <c r="A65" s="5">
         <v>62</v>
       </c>
@@ -3492,7 +3499,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="66" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="66" ht="122.25" customHeight="1">
       <c r="A66" s="5">
         <v>63</v>
       </c>
@@ -3506,7 +3513,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="67" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="67" ht="135" customHeight="1">
       <c r="A67" s="5">
         <v>64</v>
       </c>
@@ -3520,7 +3527,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="68" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="68" ht="159.75" customHeight="1">
       <c r="A68" s="5">
         <v>65</v>
       </c>
@@ -3534,7 +3541,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="69" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="69" ht="135" customHeight="1">
       <c r="A69" s="5">
         <v>66</v>
       </c>
@@ -3548,7 +3555,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="70" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="70" ht="110.25" customHeight="1">
       <c r="A70" s="5">
         <v>67</v>
       </c>
@@ -3562,7 +3569,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="71" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="71" ht="122.25" customHeight="1">
       <c r="A71" s="5">
         <v>68</v>
       </c>
@@ -3576,7 +3583,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="72" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="72" ht="122.25" customHeight="1">
       <c r="A72" s="5">
         <v>69</v>
       </c>
@@ -3590,7 +3597,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="73" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="73" ht="122.25" customHeight="1">
       <c r="A73" s="5">
         <v>70</v>
       </c>
@@ -3604,7 +3611,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="74" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="74" ht="122.25" customHeight="1">
       <c r="A74" s="5">
         <v>71</v>
       </c>
@@ -3618,7 +3625,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="75" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="75" ht="122.25" customHeight="1">
       <c r="A75" s="5">
         <v>72</v>
       </c>
@@ -3632,7 +3639,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="76" ht="172.5" customHeight="1" s="1" customFormat="1">
+    <row r="76" ht="172.5" customHeight="1">
       <c r="A76" s="5">
         <v>73</v>
       </c>
@@ -3646,7 +3653,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="77" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="77" ht="97.5" customHeight="1">
       <c r="A77" s="5">
         <v>74</v>
       </c>
@@ -3660,7 +3667,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="78" ht="110.25" customHeight="1">
       <c r="A78" s="5">
         <v>75</v>
       </c>
@@ -3674,7 +3681,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="79" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="79" ht="122.25" customHeight="1">
       <c r="A79" s="5">
         <v>76</v>
       </c>
@@ -3688,7 +3695,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="80" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="80" ht="110.25" customHeight="1">
       <c r="A80" s="5">
         <v>77</v>
       </c>
@@ -3702,7 +3709,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="81" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="81" ht="122.25" customHeight="1">
       <c r="A81" s="5">
         <v>78</v>
       </c>
@@ -3716,7 +3723,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="82" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="82" ht="159.75" customHeight="1">
       <c r="A82" s="5">
         <v>79</v>
       </c>
@@ -3730,7 +3737,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="83" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="83" ht="135" customHeight="1">
       <c r="A83" s="5">
         <v>80</v>
       </c>
@@ -3744,7 +3751,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="84" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="84" ht="122.25" customHeight="1">
       <c r="A84" s="5">
         <v>81</v>
       </c>
@@ -3758,7 +3765,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="85" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="85" ht="122.25" customHeight="1">
       <c r="A85" s="5">
         <v>82</v>
       </c>
@@ -3772,7 +3779,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="86" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="86" ht="110.25" customHeight="1">
       <c r="A86" s="5">
         <v>83</v>
       </c>
@@ -3786,7 +3793,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="87" ht="210" customHeight="1" s="1" customFormat="1">
+    <row r="87" ht="210" customHeight="1">
       <c r="A87" s="5">
         <v>84</v>
       </c>
@@ -3800,7 +3807,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="88" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="88" ht="122.25" customHeight="1">
       <c r="A88" s="5">
         <v>85</v>
       </c>
@@ -3814,7 +3821,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="89" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="89" ht="110.25" customHeight="1">
       <c r="A89" s="5">
         <v>86</v>
       </c>
@@ -3828,7 +3835,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="90" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="90" ht="47.25" customHeight="1">
       <c r="A90" s="5">
         <v>87</v>
       </c>
@@ -3842,7 +3849,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="91" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="91" ht="122.25" customHeight="1">
       <c r="A91" s="5">
         <v>88</v>
       </c>
@@ -3856,7 +3863,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="92" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="92" ht="110.25" customHeight="1">
       <c r="A92" s="5">
         <v>89</v>
       </c>
@@ -3870,7 +3877,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="93" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="93" ht="147.75" customHeight="1">
       <c r="A93" s="5">
         <v>90</v>
       </c>
@@ -3884,7 +3891,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="94" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="94" ht="122.25" customHeight="1">
       <c r="A94" s="5">
         <v>91</v>
       </c>
@@ -3898,7 +3905,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="95" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="95" ht="122.25" customHeight="1">
       <c r="A95" s="5">
         <v>92</v>
       </c>
@@ -3912,7 +3919,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="96" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="96" ht="135" customHeight="1">
       <c r="A96" s="5">
         <v>93</v>
       </c>
@@ -3926,7 +3933,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="97" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="97" ht="122.25" customHeight="1">
       <c r="A97" s="5">
         <v>94</v>
       </c>
@@ -3940,7 +3947,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="98" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="98" ht="135" customHeight="1">
       <c r="A98" s="5">
         <v>95</v>
       </c>
@@ -3954,7 +3961,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="99" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="99" ht="147.75" customHeight="1">
       <c r="A99" s="5">
         <v>96</v>
       </c>
@@ -3968,7 +3975,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="100" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="100" ht="135" customHeight="1">
       <c r="A100" s="5">
         <v>97</v>
       </c>
@@ -3982,7 +3989,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="101" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="101" ht="122.25" customHeight="1">
       <c r="A101" s="5">
         <v>98</v>
       </c>
@@ -3996,7 +4003,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="102" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="102" ht="47.25" customHeight="1">
       <c r="A102" s="5">
         <v>99</v>
       </c>
@@ -4010,7 +4017,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="103" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="103" ht="122.25" customHeight="1">
       <c r="A103" s="5">
         <v>100</v>
       </c>
@@ -4024,7 +4031,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="104" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="104" ht="135" customHeight="1">
       <c r="A104" s="5">
         <v>101</v>
       </c>
@@ -4038,7 +4045,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="105" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="105" ht="110.25" customHeight="1">
       <c r="A105" s="5">
         <v>102</v>
       </c>
@@ -4052,7 +4059,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="106" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="106" ht="135" customHeight="1">
       <c r="A106" s="5">
         <v>103</v>
       </c>
@@ -4066,7 +4073,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="107" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="107" ht="110.25" customHeight="1">
       <c r="A107" s="5">
         <v>104</v>
       </c>
@@ -4080,7 +4087,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="108" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="108" ht="122.25" customHeight="1">
       <c r="A108" s="5">
         <v>105</v>
       </c>
@@ -4094,7 +4101,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1" s="1" customFormat="1">
+    <row r="109" ht="60" customHeight="1">
       <c r="A109" s="5">
         <v>106</v>
       </c>
@@ -4108,7 +4115,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="110" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="110" ht="47.25" customHeight="1">
       <c r="A110" s="5">
         <v>107</v>
       </c>
@@ -4122,7 +4129,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="111" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="111" ht="135" customHeight="1">
       <c r="A111" s="5">
         <v>108</v>
       </c>
@@ -4136,7 +4143,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="112" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="112" ht="122.25" customHeight="1">
       <c r="A112" s="5">
         <v>109</v>
       </c>
@@ -4150,7 +4157,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="113" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="113" ht="135" customHeight="1">
       <c r="A113" s="5">
         <v>110</v>
       </c>
@@ -4164,7 +4171,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="114" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="114" ht="110.25" customHeight="1">
       <c r="A114" s="5">
         <v>111</v>
       </c>
@@ -4178,7 +4185,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="115" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="115" ht="122.25" customHeight="1">
       <c r="A115" s="5">
         <v>112</v>
       </c>
@@ -4192,7 +4199,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="116" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="116" ht="135" customHeight="1">
       <c r="A116" s="5">
         <v>113</v>
       </c>
@@ -4206,7 +4213,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="117" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="117" ht="135" customHeight="1">
       <c r="A117" s="5">
         <v>114</v>
       </c>
@@ -4220,7 +4227,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="118" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="118" ht="122.25" customHeight="1">
       <c r="A118" s="5">
         <v>115</v>
       </c>
@@ -4234,7 +4241,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="119" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="119" ht="122.25" customHeight="1">
       <c r="A119" s="5">
         <v>116</v>
       </c>
@@ -4248,7 +4255,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="120" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="120" ht="110.25" customHeight="1">
       <c r="A120" s="5">
         <v>117</v>
       </c>
@@ -4262,7 +4269,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="121" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="121" ht="110.25" customHeight="1">
       <c r="A121" s="5">
         <v>118</v>
       </c>
@@ -4276,7 +4283,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="122" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="122" ht="122.25" customHeight="1">
       <c r="A122" s="5">
         <v>119</v>
       </c>
@@ -4290,7 +4297,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="123" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="123" ht="135" customHeight="1">
       <c r="A123" s="5">
         <v>120</v>
       </c>
@@ -4304,7 +4311,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="124" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="124" ht="122.25" customHeight="1">
       <c r="A124" s="5">
         <v>121</v>
       </c>
@@ -4318,7 +4325,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="125" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="125" ht="159.75" customHeight="1">
       <c r="A125" s="5">
         <v>122</v>
       </c>
@@ -4332,7 +4339,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="126" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="126" ht="135" customHeight="1">
       <c r="A126" s="5">
         <v>123</v>
       </c>
@@ -4346,7 +4353,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="127" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="127" ht="122.25" customHeight="1">
       <c r="A127" s="5">
         <v>124</v>
       </c>
@@ -4360,7 +4367,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="128" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="128" ht="122.25" customHeight="1">
       <c r="A128" s="5">
         <v>125</v>
       </c>
@@ -4374,7 +4381,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="129" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="129" ht="122.25" customHeight="1">
       <c r="A129" s="5">
         <v>126</v>
       </c>
@@ -4388,7 +4395,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="130" ht="22.5" customHeight="1" s="1" customFormat="1">
+    <row r="130" ht="22.5" customHeight="1">
       <c r="A130" s="5">
         <v>127</v>
       </c>
@@ -4402,7 +4409,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="131" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="131" ht="147.75" customHeight="1">
       <c r="A131" s="5">
         <v>128</v>
       </c>
@@ -4416,7 +4423,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="132" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="132" ht="47.25" customHeight="1">
       <c r="A132" s="5">
         <v>129</v>
       </c>
@@ -4430,7 +4437,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="133" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="133" ht="110.25" customHeight="1">
       <c r="A133" s="5">
         <v>130</v>
       </c>
@@ -4444,7 +4451,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="134" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="134" ht="159.75" customHeight="1">
       <c r="A134" s="5">
         <v>131</v>
       </c>
@@ -4458,7 +4465,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="135" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="135" ht="122.25" customHeight="1">
       <c r="A135" s="5">
         <v>132</v>
       </c>
@@ -4472,7 +4479,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="136" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="136" ht="110.25" customHeight="1">
       <c r="A136" s="5">
         <v>133</v>
       </c>
@@ -4486,7 +4493,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="137" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="137" ht="147.75" customHeight="1">
       <c r="A137" s="5">
         <v>134</v>
       </c>
@@ -4500,7 +4507,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="138" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="138" ht="122.25" customHeight="1">
       <c r="A138" s="5">
         <v>135</v>
       </c>
@@ -4514,7 +4521,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="139" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="139" ht="122.25" customHeight="1">
       <c r="A139" s="5">
         <v>136</v>
       </c>
@@ -4528,7 +4535,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="140" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="140" ht="110.25" customHeight="1">
       <c r="A140" s="5">
         <v>137</v>
       </c>
@@ -4542,7 +4549,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="141" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="141" ht="159.75" customHeight="1">
       <c r="A141" s="5">
         <v>138</v>
       </c>
@@ -4556,7 +4563,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="142" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="142" ht="110.25" customHeight="1">
       <c r="A142" s="5">
         <v>139</v>
       </c>
@@ -4570,7 +4577,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="143" ht="210" customHeight="1" s="1" customFormat="1">
+    <row r="143" ht="210" customHeight="1">
       <c r="A143" s="5">
         <v>140</v>
       </c>
@@ -4584,7 +4591,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="144" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="144" ht="122.25" customHeight="1">
       <c r="A144" s="5">
         <v>141</v>
       </c>
@@ -4598,7 +4605,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="145" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="145" ht="159.75" customHeight="1">
       <c r="A145" s="5">
         <v>142</v>
       </c>
@@ -4612,7 +4619,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="146" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="146" ht="135" customHeight="1">
       <c r="A146" s="5">
         <v>143</v>
       </c>
@@ -4626,7 +4633,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="147" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="147" ht="122.25" customHeight="1">
       <c r="A147" s="5">
         <v>144</v>
       </c>
@@ -4640,7 +4647,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="148" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="148" ht="122.25" customHeight="1">
       <c r="A148" s="5">
         <v>145</v>
       </c>
@@ -4654,7 +4661,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="149" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="149" ht="97.5" customHeight="1">
       <c r="A149" s="5">
         <v>146</v>
       </c>
@@ -4668,7 +4675,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="150" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="150" ht="47.25" customHeight="1">
       <c r="A150" s="5">
         <v>147</v>
       </c>
@@ -4682,7 +4689,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="151" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="151" ht="110.25" customHeight="1">
       <c r="A151" s="5">
         <v>148</v>
       </c>
@@ -4696,7 +4703,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="152" ht="72.75" customHeight="1" s="1" customFormat="1">
+    <row r="152" ht="72.75" customHeight="1">
       <c r="A152" s="5">
         <v>149</v>
       </c>
@@ -4710,7 +4717,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="153" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="153" ht="122.25" customHeight="1">
       <c r="A153" s="5">
         <v>150</v>
       </c>
@@ -4724,7 +4731,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="154" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="154" ht="110.25" customHeight="1">
       <c r="A154" s="5">
         <v>151</v>
       </c>
@@ -4738,7 +4745,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="155" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="155" ht="110.25" customHeight="1">
       <c r="A155" s="5">
         <v>152</v>
       </c>
@@ -4752,7 +4759,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="156" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="156" ht="110.25" customHeight="1">
       <c r="A156" s="5">
         <v>153</v>
       </c>
@@ -4766,7 +4773,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="157" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="157" ht="122.25" customHeight="1">
       <c r="A157" s="5">
         <v>154</v>
       </c>
@@ -4780,7 +4787,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="158" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="158" ht="110.25" customHeight="1">
       <c r="A158" s="5">
         <v>155</v>
       </c>
@@ -4794,7 +4801,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="159" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="159" ht="135" customHeight="1">
       <c r="A159" s="5">
         <v>156</v>
       </c>
@@ -4808,7 +4815,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="160" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="160" ht="122.25" customHeight="1">
       <c r="A160" s="5">
         <v>157</v>
       </c>
@@ -4822,7 +4829,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="161" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="161" ht="135" customHeight="1">
       <c r="A161" s="5">
         <v>158</v>
       </c>
@@ -4836,7 +4843,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="162" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="162" ht="122.25" customHeight="1">
       <c r="A162" s="5">
         <v>159</v>
       </c>
@@ -4850,7 +4857,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="163" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="163" ht="135" customHeight="1">
       <c r="A163" s="5">
         <v>160</v>
       </c>
@@ -4864,7 +4871,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="164" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="164" ht="122.25" customHeight="1">
       <c r="A164" s="5">
         <v>161</v>
       </c>
@@ -4878,7 +4885,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="165" ht="197.25" customHeight="1" s="1" customFormat="1">
+    <row r="165" ht="197.25" customHeight="1">
       <c r="A165" s="5">
         <v>162</v>
       </c>
@@ -4892,7 +4899,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="166" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="166" ht="135" customHeight="1">
       <c r="A166" s="5">
         <v>163</v>
       </c>
@@ -4906,7 +4913,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="167" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="167" ht="135" customHeight="1">
       <c r="A167" s="5">
         <v>164</v>
       </c>
@@ -4920,7 +4927,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="168" ht="60" customHeight="1" s="1" customFormat="1">
+    <row r="168" ht="60" customHeight="1">
       <c r="A168" s="5">
         <v>165</v>
       </c>
@@ -4934,7 +4941,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="169" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="169" ht="122.25" customHeight="1">
       <c r="A169" s="5">
         <v>166</v>
       </c>
@@ -4948,7 +4955,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="170" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="170" ht="122.25" customHeight="1">
       <c r="A170" s="5">
         <v>167</v>
       </c>
@@ -4962,7 +4969,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="171" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="171" ht="110.25" customHeight="1">
       <c r="A171" s="5">
         <v>168</v>
       </c>
@@ -4976,7 +4983,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="172" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="172" ht="122.25" customHeight="1">
       <c r="A172" s="5">
         <v>169</v>
       </c>
@@ -4990,7 +4997,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="173" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="173" ht="122.25" customHeight="1">
       <c r="A173" s="5">
         <v>170</v>
       </c>
@@ -5004,7 +5011,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="174" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="174" ht="147.75" customHeight="1">
       <c r="A174" s="5">
         <v>171</v>
       </c>
@@ -5018,7 +5025,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="175" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="175" ht="122.25" customHeight="1">
       <c r="A175" s="5">
         <v>172</v>
       </c>
@@ -5032,7 +5039,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="176" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="176" ht="122.25" customHeight="1">
       <c r="A176" s="5">
         <v>173</v>
       </c>
@@ -5046,7 +5053,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="177" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="177" ht="97.5" customHeight="1">
       <c r="A177" s="5">
         <v>174</v>
       </c>
@@ -5060,7 +5067,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="178" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="178" ht="135" customHeight="1">
       <c r="A178" s="5">
         <v>175</v>
       </c>
@@ -5074,7 +5081,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="179" ht="172.5" customHeight="1" s="1" customFormat="1">
+    <row r="179" ht="172.5" customHeight="1">
       <c r="A179" s="5">
         <v>176</v>
       </c>
@@ -5088,7 +5095,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="180" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="180" ht="110.25" customHeight="1">
       <c r="A180" s="5">
         <v>177</v>
       </c>
@@ -5102,7 +5109,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="181" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="181" ht="122.25" customHeight="1">
       <c r="A181" s="5">
         <v>178</v>
       </c>
@@ -5116,7 +5123,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="182" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="182" ht="47.25" customHeight="1">
       <c r="A182" s="5">
         <v>179</v>
       </c>
@@ -5130,7 +5137,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="183" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="183" ht="47.25" customHeight="1">
       <c r="A183" s="5">
         <v>180</v>
       </c>
@@ -5144,7 +5151,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="184" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="184" ht="122.25" customHeight="1">
       <c r="A184" s="5">
         <v>181</v>
       </c>
@@ -5158,7 +5165,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="185" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="185" ht="110.25" customHeight="1">
       <c r="A185" s="5">
         <v>182</v>
       </c>
@@ -5172,7 +5179,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="186" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="186" ht="122.25" customHeight="1">
       <c r="A186" s="5">
         <v>183</v>
       </c>
@@ -5186,7 +5193,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="187" ht="84.75" customHeight="1" s="1" customFormat="1">
+    <row r="187" ht="84.75" customHeight="1">
       <c r="A187" s="5">
         <v>184</v>
       </c>
@@ -5200,7 +5207,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="188" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="188" ht="122.25" customHeight="1">
       <c r="A188" s="5">
         <v>185</v>
       </c>
@@ -5214,7 +5221,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="189" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="189" ht="122.25" customHeight="1">
       <c r="A189" s="5">
         <v>186</v>
       </c>
@@ -5228,7 +5235,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="190" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="190" ht="122.25" customHeight="1">
       <c r="A190" s="5">
         <v>187</v>
       </c>
@@ -5242,7 +5249,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="191" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="191" ht="110.25" customHeight="1">
       <c r="A191" s="5">
         <v>188</v>
       </c>
@@ -5256,7 +5263,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="192" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="192" ht="122.25" customHeight="1">
       <c r="A192" s="5">
         <v>189</v>
       </c>
@@ -5270,7 +5277,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="193" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="193" ht="122.25" customHeight="1">
       <c r="A193" s="5">
         <v>190</v>
       </c>
@@ -5284,7 +5291,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="194" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="194" ht="135" customHeight="1">
       <c r="A194" s="5">
         <v>191</v>
       </c>
@@ -5298,7 +5305,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="195" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="195" ht="110.25" customHeight="1">
       <c r="A195" s="5">
         <v>192</v>
       </c>
@@ -5312,7 +5319,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="196" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="196" ht="110.25" customHeight="1">
       <c r="A196" s="5">
         <v>193</v>
       </c>
@@ -5326,7 +5333,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="197" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="197" ht="122.25" customHeight="1">
       <c r="A197" s="5">
         <v>194</v>
       </c>
@@ -5340,7 +5347,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="198" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="198" ht="110.25" customHeight="1">
       <c r="A198" s="5">
         <v>195</v>
       </c>
@@ -5354,7 +5361,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="199" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="199" ht="110.25" customHeight="1">
       <c r="A199" s="5">
         <v>196</v>
       </c>
@@ -5368,7 +5375,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="200" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="200" ht="110.25" customHeight="1">
       <c r="A200" s="5">
         <v>197</v>
       </c>
@@ -5382,7 +5389,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="201" ht="72.75" customHeight="1" s="1" customFormat="1">
+    <row r="201" ht="72.75" customHeight="1">
       <c r="A201" s="5">
         <v>198</v>
       </c>
@@ -5396,7 +5403,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="202" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="202" ht="110.25" customHeight="1">
       <c r="A202" s="5">
         <v>199</v>
       </c>
@@ -5410,7 +5417,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="203" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="203" ht="110.25" customHeight="1">
       <c r="A203" s="5">
         <v>200</v>
       </c>
@@ -5424,7 +5431,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="204" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="204" ht="110.25" customHeight="1">
       <c r="A204" s="5">
         <v>201</v>
       </c>
@@ -5438,7 +5445,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="205" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="205" ht="122.25" customHeight="1">
       <c r="A205" s="5">
         <v>202</v>
       </c>
@@ -5452,7 +5459,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="206" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="206" ht="122.25" customHeight="1">
       <c r="A206" s="5">
         <v>203</v>
       </c>
@@ -5466,7 +5473,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="207" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="207" ht="110.25" customHeight="1">
       <c r="A207" s="5">
         <v>204</v>
       </c>
@@ -5480,7 +5487,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="208" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="208" ht="47.25" customHeight="1">
       <c r="A208" s="5">
         <v>205</v>
       </c>
@@ -5494,7 +5501,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="209" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="209" ht="122.25" customHeight="1">
       <c r="A209" s="5">
         <v>206</v>
       </c>
@@ -5508,7 +5515,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="210" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="210" ht="110.25" customHeight="1">
       <c r="A210" s="5">
         <v>207</v>
       </c>
@@ -5522,7 +5529,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="211" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="211" ht="122.25" customHeight="1">
       <c r="A211" s="5">
         <v>208</v>
       </c>
@@ -5536,7 +5543,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="212" ht="497.25" customHeight="1" s="1" customFormat="1">
+    <row r="212" ht="409.5" customHeight="1">
       <c r="A212" s="5">
         <v>209</v>
       </c>
@@ -5550,7 +5557,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="213" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="213" ht="122.25" customHeight="1">
       <c r="A213" s="5">
         <v>210</v>
       </c>
@@ -5564,7 +5571,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="214" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="214" ht="122.25" customHeight="1">
       <c r="A214" s="5">
         <v>211</v>
       </c>
@@ -5578,7 +5585,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="215" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="215" ht="135" customHeight="1">
       <c r="A215" s="5">
         <v>212</v>
       </c>
@@ -5592,7 +5599,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="216" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="216" ht="110.25" customHeight="1">
       <c r="A216" s="5">
         <v>213</v>
       </c>
@@ -5606,7 +5613,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="217" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="217" ht="122.25" customHeight="1">
       <c r="A217" s="5">
         <v>214</v>
       </c>
@@ -5620,7 +5627,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="218" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="218" ht="122.25" customHeight="1">
       <c r="A218" s="5">
         <v>215</v>
       </c>
@@ -5634,7 +5641,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="219" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="219" ht="47.25" customHeight="1">
       <c r="A219" s="5">
         <v>216</v>
       </c>
@@ -5648,7 +5655,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="220" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="220" ht="110.25" customHeight="1">
       <c r="A220" s="5">
         <v>217</v>
       </c>
@@ -5662,7 +5669,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="221" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="221" ht="110.25" customHeight="1">
       <c r="A221" s="5">
         <v>218</v>
       </c>
@@ -5676,7 +5683,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="222" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="222" ht="122.25" customHeight="1">
       <c r="A222" s="5">
         <v>219</v>
       </c>
@@ -5690,7 +5697,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="223" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="223" ht="110.25" customHeight="1">
       <c r="A223" s="5">
         <v>220</v>
       </c>
@@ -5704,7 +5711,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="224" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="224" ht="110.25" customHeight="1">
       <c r="A224" s="5">
         <v>221</v>
       </c>
@@ -5718,7 +5725,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="225" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="225" ht="122.25" customHeight="1">
       <c r="A225" s="5">
         <v>222</v>
       </c>
@@ -5732,7 +5739,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="226" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="226" ht="110.25" customHeight="1">
       <c r="A226" s="5">
         <v>223</v>
       </c>
@@ -5746,7 +5753,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="227" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="227" ht="97.5" customHeight="1">
       <c r="A227" s="5">
         <v>224</v>
       </c>
@@ -5760,7 +5767,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="228" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="228" ht="122.25" customHeight="1">
       <c r="A228" s="5">
         <v>225</v>
       </c>
@@ -5774,7 +5781,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="229" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="229" ht="97.5" customHeight="1">
       <c r="A229" s="5">
         <v>226</v>
       </c>
@@ -5788,7 +5795,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="230" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="230" ht="122.25" customHeight="1">
       <c r="A230" s="5">
         <v>227</v>
       </c>
@@ -5802,7 +5809,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="231" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="231" ht="110.25" customHeight="1">
       <c r="A231" s="5">
         <v>228</v>
       </c>
@@ -5816,7 +5823,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="232" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="232" ht="122.25" customHeight="1">
       <c r="A232" s="5">
         <v>229</v>
       </c>
@@ -5830,7 +5837,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="233" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="233" ht="110.25" customHeight="1">
       <c r="A233" s="5">
         <v>230</v>
       </c>
@@ -5844,7 +5851,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="234" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="234" ht="122.25" customHeight="1">
       <c r="A234" s="5">
         <v>231</v>
       </c>
@@ -5858,7 +5865,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="235" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="235" ht="110.25" customHeight="1">
       <c r="A235" s="5">
         <v>232</v>
       </c>
@@ -5872,7 +5879,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="236" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="236" ht="122.25" customHeight="1">
       <c r="A236" s="5">
         <v>233</v>
       </c>
@@ -5886,7 +5893,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="237" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="237" ht="97.5" customHeight="1">
       <c r="A237" s="5">
         <v>234</v>
       </c>
@@ -5900,7 +5907,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="238" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="238" ht="47.25" customHeight="1">
       <c r="A238" s="5">
         <v>235</v>
       </c>
@@ -5914,7 +5921,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="239" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="239" ht="110.25" customHeight="1">
       <c r="A239" s="5">
         <v>236</v>
       </c>
@@ -5928,7 +5935,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="240" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="240" ht="110.25" customHeight="1">
       <c r="A240" s="5">
         <v>237</v>
       </c>
@@ -5942,7 +5949,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="241" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="241" ht="110.25" customHeight="1">
       <c r="A241" s="5">
         <v>238</v>
       </c>
@@ -5956,7 +5963,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="242" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="242" ht="97.5" customHeight="1">
       <c r="A242" s="5">
         <v>239</v>
       </c>
@@ -5970,7 +5977,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="243" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="243" ht="110.25" customHeight="1">
       <c r="A243" s="5">
         <v>240</v>
       </c>
@@ -5984,7 +5991,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="244" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="244" ht="97.5" customHeight="1">
       <c r="A244" s="5">
         <v>241</v>
       </c>
@@ -5998,7 +6005,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="245" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="245" ht="97.5" customHeight="1">
       <c r="A245" s="5">
         <v>242</v>
       </c>
@@ -6012,7 +6019,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="246" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="246" ht="110.25" customHeight="1">
       <c r="A246" s="5">
         <v>243</v>
       </c>
@@ -6026,7 +6033,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="247" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="247" ht="159.75" customHeight="1">
       <c r="A247" s="5">
         <v>244</v>
       </c>
@@ -6040,7 +6047,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="248" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="248" ht="110.25" customHeight="1">
       <c r="A248" s="5">
         <v>245</v>
       </c>
@@ -6054,7 +6061,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="249" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="249" ht="147.75" customHeight="1">
       <c r="A249" s="5">
         <v>246</v>
       </c>
@@ -6068,7 +6075,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="250" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="250" ht="97.5" customHeight="1">
       <c r="A250" s="5">
         <v>247</v>
       </c>
@@ -6082,7 +6089,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="251" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="251" ht="110.25" customHeight="1">
       <c r="A251" s="5">
         <v>248</v>
       </c>
@@ -6096,7 +6103,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="252" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="252" ht="110.25" customHeight="1">
       <c r="A252" s="5">
         <v>249</v>
       </c>
@@ -6110,7 +6117,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="253" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="253" ht="147.75" customHeight="1">
       <c r="A253" s="5">
         <v>250</v>
       </c>
@@ -6124,7 +6131,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="254" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="254" ht="110.25" customHeight="1">
       <c r="A254" s="5">
         <v>251</v>
       </c>
@@ -6138,7 +6145,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="255" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="255" ht="110.25" customHeight="1">
       <c r="A255" s="5">
         <v>252</v>
       </c>
@@ -6152,7 +6159,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="256" ht="60" customHeight="1" s="1" customFormat="1">
+    <row r="256" ht="60" customHeight="1">
       <c r="A256" s="5">
         <v>253</v>
       </c>
@@ -6166,7 +6173,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="257" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="257" ht="159.75" customHeight="1">
       <c r="A257" s="5">
         <v>254</v>
       </c>
@@ -6180,7 +6187,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="258" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="258" ht="97.5" customHeight="1">
       <c r="A258" s="5">
         <v>255</v>
       </c>
@@ -6194,7 +6201,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="259" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="259" ht="122.25" customHeight="1">
       <c r="A259" s="5">
         <v>256</v>
       </c>
@@ -6208,7 +6215,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="260" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="260" ht="110.25" customHeight="1">
       <c r="A260" s="5">
         <v>257</v>
       </c>
@@ -6222,7 +6229,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="261" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="261" ht="135" customHeight="1">
       <c r="A261" s="5">
         <v>258</v>
       </c>
@@ -6236,7 +6243,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="262" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="262" ht="110.25" customHeight="1">
       <c r="A262" s="5">
         <v>259</v>
       </c>
@@ -6250,7 +6257,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="263" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="263" ht="135" customHeight="1">
       <c r="A263" s="5">
         <v>260</v>
       </c>
@@ -6264,7 +6271,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="264" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="264" ht="135" customHeight="1">
       <c r="A264" s="5">
         <v>261</v>
       </c>
@@ -6278,7 +6285,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="265" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="265" ht="122.25" customHeight="1">
       <c r="A265" s="5">
         <v>262</v>
       </c>
@@ -6292,7 +6299,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="266" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="266" ht="110.25" customHeight="1">
       <c r="A266" s="5">
         <v>263</v>
       </c>
@@ -6306,7 +6313,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="267" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="267" ht="147.75" customHeight="1">
       <c r="A267" s="5">
         <v>264</v>
       </c>
@@ -6320,7 +6327,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="268" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="268" ht="122.25" customHeight="1">
       <c r="A268" s="5">
         <v>265</v>
       </c>
@@ -6334,7 +6341,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="269" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="269" ht="159.75" customHeight="1">
       <c r="A269" s="5">
         <v>266</v>
       </c>
@@ -6348,7 +6355,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="270" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="270" ht="47.25" customHeight="1">
       <c r="A270" s="5">
         <v>267</v>
       </c>
@@ -6362,7 +6369,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="271" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="271" ht="97.5" customHeight="1">
       <c r="A271" s="5">
         <v>268</v>
       </c>
@@ -6376,7 +6383,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="272" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="272" ht="135" customHeight="1">
       <c r="A272" s="5">
         <v>269</v>
       </c>
@@ -6390,7 +6397,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="273" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="273" ht="122.25" customHeight="1">
       <c r="A273" s="5">
         <v>270</v>
       </c>
@@ -6404,7 +6411,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="274" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="274" ht="122.25" customHeight="1">
       <c r="A274" s="5">
         <v>271</v>
       </c>
@@ -6418,7 +6425,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="275" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="275" ht="47.25" customHeight="1">
       <c r="A275" s="5">
         <v>272</v>
       </c>
@@ -6432,7 +6439,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="276" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="276" ht="122.25" customHeight="1">
       <c r="A276" s="5">
         <v>273</v>
       </c>
@@ -6446,7 +6453,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="277" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="277" ht="122.25" customHeight="1">
       <c r="A277" s="5">
         <v>274</v>
       </c>
@@ -6460,7 +6467,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="278" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="278" ht="47.25" customHeight="1">
       <c r="A278" s="5">
         <v>275</v>
       </c>
@@ -6474,7 +6481,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="279" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="279" ht="122.25" customHeight="1">
       <c r="A279" s="5">
         <v>276</v>
       </c>
@@ -6488,7 +6495,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="280" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="280" ht="135" customHeight="1">
       <c r="A280" s="5">
         <v>277</v>
       </c>
@@ -6502,7 +6509,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="281" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="281" ht="135" customHeight="1">
       <c r="A281" s="5">
         <v>278</v>
       </c>
@@ -6516,7 +6523,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="282" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="282" ht="135" customHeight="1">
       <c r="A282" s="5">
         <v>279</v>
       </c>
@@ -6530,7 +6537,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="283" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="283" ht="122.25" customHeight="1">
       <c r="A283" s="5">
         <v>280</v>
       </c>
@@ -6544,7 +6551,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="284" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="284" ht="122.25" customHeight="1">
       <c r="A284" s="5">
         <v>281</v>
       </c>
@@ -6558,7 +6565,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="285" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="285" ht="135" customHeight="1">
       <c r="A285" s="5">
         <v>282</v>
       </c>
@@ -6572,7 +6579,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="286" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="286" ht="122.25" customHeight="1">
       <c r="A286" s="5">
         <v>283</v>
       </c>
@@ -6586,7 +6593,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="287" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="287" ht="122.25" customHeight="1">
       <c r="A287" s="5">
         <v>284</v>
       </c>
@@ -6600,7 +6607,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="288" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="288" ht="110.25" customHeight="1">
       <c r="A288" s="5">
         <v>285</v>
       </c>
@@ -6614,7 +6621,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="289" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="289" ht="135" customHeight="1">
       <c r="A289" s="5">
         <v>286</v>
       </c>
@@ -6628,7 +6635,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="290" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="290" ht="110.25" customHeight="1">
       <c r="A290" s="5">
         <v>287</v>
       </c>
@@ -6642,7 +6649,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="291" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="291" ht="122.25" customHeight="1">
       <c r="A291" s="5">
         <v>288</v>
       </c>
@@ -6656,7 +6663,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="292" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="292" ht="122.25" customHeight="1">
       <c r="A292" s="5">
         <v>289</v>
       </c>
@@ -6670,7 +6677,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="293" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="293" ht="135" customHeight="1">
       <c r="A293" s="5">
         <v>290</v>
       </c>
@@ -6684,7 +6691,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="294" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="294" ht="47.25" customHeight="1">
       <c r="A294" s="5">
         <v>291</v>
       </c>
@@ -6698,7 +6705,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="295" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="295" ht="135" customHeight="1">
       <c r="A295" s="5">
         <v>292</v>
       </c>
@@ -6712,7 +6719,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="296" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="296" ht="159.75" customHeight="1">
       <c r="A296" s="5">
         <v>293</v>
       </c>
@@ -6726,7 +6733,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="297" ht="197.25" customHeight="1" s="1" customFormat="1">
+    <row r="297" ht="197.25" customHeight="1">
       <c r="A297" s="5">
         <v>294</v>
       </c>
@@ -6740,7 +6747,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="298" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="298" ht="110.25" customHeight="1">
       <c r="A298" s="5">
         <v>295</v>
       </c>
@@ -6754,7 +6761,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="299" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="299" ht="135" customHeight="1">
       <c r="A299" s="5">
         <v>296</v>
       </c>
@@ -6768,7 +6775,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="300" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="300" ht="122.25" customHeight="1">
       <c r="A300" s="5">
         <v>297</v>
       </c>
@@ -6813,23 +6820,23 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{B0864C70-D626-4A16-9DAB-7573DA7F56A0}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{984A91EB-621E-4DA2-90BB-223342584594}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="6.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="38.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="6.00390625" customWidth="1"/>
+    <col min="2" max="2" width="38.00390625" customWidth="1"/>
+    <col min="3" max="3" width="80.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -6840,7 +6847,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="3" ht="122.25" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -6851,7 +6858,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="4" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="110.25" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -6862,7 +6869,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="5" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="147.75" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -6873,7 +6880,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="6" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="6" ht="122.25" customHeight="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -6900,23 +6907,23 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{0ED991A7-9223-4977-9149-A8D11EF2B904}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{7E98D815-1772-4978-935F-5F1C48087688}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="6.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="38.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="6.00390625" customWidth="1"/>
+    <col min="2" max="2" width="38.00390625" customWidth="1"/>
+    <col min="3" max="3" width="80.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -6927,7 +6934,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="3" ht="122.25" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -6938,7 +6945,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="4" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="110.25" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -6949,7 +6956,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="5" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="159.75" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -6976,23 +6983,23 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{CB124B4F-F041-4754-B05B-845F3EC26AB8}" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{5E7FEF38-C585-4337-B44D-EF8F4F9C9916}" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="6.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="38.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="6.00390625" customWidth="1"/>
+    <col min="2" max="2" width="38.00390625" customWidth="1"/>
+    <col min="3" max="3" width="80.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -7003,7 +7010,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="3" ht="279" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -7014,7 +7021,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="4" ht="210" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="210" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -7025,7 +7032,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="5" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="122.25" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -7036,7 +7043,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="6" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="6" ht="159.75" customHeight="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -7063,23 +7070,23 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{2D933BA2-201A-46AF-84FD-CB2C82867254}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{CAB38FB4-1460-4208-A3DA-76EC647B7F0E}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="6.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="38.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="6.00390625" customWidth="1"/>
+    <col min="2" max="2" width="38.00390625" customWidth="1"/>
+    <col min="3" max="3" width="80.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>634</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -7090,7 +7097,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="3" ht="135" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -7101,7 +7108,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="4" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="122.25" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -7112,7 +7119,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="5" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="122.25" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -7123,7 +7130,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="6" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="6" ht="97.5" customHeight="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -7134,7 +7141,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="7" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="7" ht="47.25" customHeight="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -7145,7 +7152,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="8" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="8" ht="110.25" customHeight="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -7156,7 +7163,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="9" ht="72.75" customHeight="1" s="1" customFormat="1">
+    <row r="9" ht="72.75" customHeight="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -7167,7 +7174,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="10" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="10" ht="122.25" customHeight="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -7178,7 +7185,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="11" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="11" ht="110.25" customHeight="1">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -7189,7 +7196,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="12" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="12" ht="110.25" customHeight="1">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -7200,7 +7207,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="13" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="13" ht="110.25" customHeight="1">
       <c r="A13" s="6">
         <v>11</v>
       </c>
@@ -7211,7 +7218,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="14" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="14" ht="122.25" customHeight="1">
       <c r="A14" s="6">
         <v>12</v>
       </c>
@@ -7222,7 +7229,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="15" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="15" ht="110.25" customHeight="1">
       <c r="A15" s="6">
         <v>13</v>
       </c>
@@ -7233,7 +7240,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="16" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="16" ht="135" customHeight="1">
       <c r="A16" s="6">
         <v>14</v>
       </c>
@@ -7244,7 +7251,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="17" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="17" ht="122.25" customHeight="1">
       <c r="A17" s="6">
         <v>15</v>
       </c>
@@ -7255,7 +7262,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="18" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="18" ht="135" customHeight="1">
       <c r="A18" s="6">
         <v>16</v>
       </c>
@@ -7266,7 +7273,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="19" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="19" ht="122.25" customHeight="1">
       <c r="A19" s="6">
         <v>17</v>
       </c>
@@ -7293,23 +7300,23 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{4DF04368-2FBC-429A-8A32-1F4691A8667E}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{01A7D8E7-F427-4509-AA81-59A7971DDB05}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="6.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="38.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="6.00390625" customWidth="1"/>
+    <col min="2" max="2" width="38.00390625" customWidth="1"/>
+    <col min="3" max="3" width="80.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>635</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -7320,7 +7327,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="3" ht="135" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -7331,7 +7338,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="4" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="122.25" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -7342,7 +7349,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="5" ht="197.25" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="197.25" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -7353,7 +7360,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="6" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="6" ht="135" customHeight="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -7364,7 +7371,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="7" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="7" ht="135" customHeight="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -7375,7 +7382,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1" s="1" customFormat="1">
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -7386,7 +7393,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="9" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="9" ht="122.25" customHeight="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -7397,7 +7404,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="10" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="10" ht="122.25" customHeight="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -7408,7 +7415,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="11" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="11" ht="110.25" customHeight="1">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -7419,7 +7426,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="12" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="12" ht="122.25" customHeight="1">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -7430,7 +7437,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="13" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="13" ht="122.25" customHeight="1">
       <c r="A13" s="6">
         <v>11</v>
       </c>
@@ -7441,7 +7448,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="14" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="14" ht="147.75" customHeight="1">
       <c r="A14" s="6">
         <v>12</v>
       </c>
@@ -7468,23 +7475,23 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{5D8B0733-DCFD-4BD5-B63D-AC8481AD1C8A}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{2B159CD8-0EBA-4914-8E3B-560F2346998A}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="6.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="38.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="6.00390625" customWidth="1"/>
+    <col min="2" max="2" width="38.00390625" customWidth="1"/>
+    <col min="3" max="3" width="80.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>636</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -7495,7 +7502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="3" ht="122.25" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -7506,7 +7513,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="4" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="122.25" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -7517,7 +7524,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="5" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="97.5" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -7528,7 +7535,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="6" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="6" ht="135" customHeight="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -7539,7 +7546,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="7" ht="172.5" customHeight="1" s="1" customFormat="1">
+    <row r="7" ht="172.5" customHeight="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -7566,23 +7573,23 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{E0354A40-F73E-459B-B0EE-DBAAD1C69B91}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{3E3E02AF-91A6-46FE-ABF8-ED3CB88CB75B}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="6.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="38.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="6.00390625" customWidth="1"/>
+    <col min="2" max="2" width="38.00390625" customWidth="1"/>
+    <col min="3" max="3" width="80.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>637</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -7593,7 +7600,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="3" ht="110.25" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -7604,7 +7611,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="4" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="122.25" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -7615,7 +7622,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="5" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="47.25" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -7626,7 +7633,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="6" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="6" ht="47.25" customHeight="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -7637,7 +7644,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="7" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="7" ht="122.25" customHeight="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -7648,7 +7655,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="8" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="8" ht="110.25" customHeight="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -7659,7 +7666,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="9" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="9" ht="122.25" customHeight="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -7670,7 +7677,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="10" ht="84.75" customHeight="1" s="1" customFormat="1">
+    <row r="10" ht="84.75" customHeight="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -7697,23 +7704,23 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{C37D42E8-EB5F-4BA3-815F-C96E39A96FF2}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{17D3CA40-BA99-4417-BED2-A3C1EA95CF0E}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="6.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="38.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="6.00390625" customWidth="1"/>
+    <col min="2" max="2" width="38.00390625" customWidth="1"/>
+    <col min="3" max="3" width="80.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>638</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -7724,7 +7731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="3" ht="122.25" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -7735,7 +7742,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="4" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="122.25" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -7746,7 +7753,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="5" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="122.25" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -7757,7 +7764,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="6" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="6" ht="110.25" customHeight="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -7768,7 +7775,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="7" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="7" ht="122.25" customHeight="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -7779,7 +7786,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="8" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="8" ht="122.25" customHeight="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -7790,7 +7797,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="9" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="9" ht="135" customHeight="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -7801,7 +7808,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="10" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="10" ht="110.25" customHeight="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -7812,7 +7819,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="11" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="11" ht="110.25" customHeight="1">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -7823,7 +7830,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="12" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="12" ht="122.25" customHeight="1">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -7834,7 +7841,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="13" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="13" ht="110.25" customHeight="1">
       <c r="A13" s="6">
         <v>11</v>
       </c>
@@ -7845,7 +7852,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="14" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="14" ht="110.25" customHeight="1">
       <c r="A14" s="6">
         <v>12</v>
       </c>
@@ -7856,7 +7863,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="15" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="15" ht="110.25" customHeight="1">
       <c r="A15" s="6">
         <v>13</v>
       </c>
@@ -7867,7 +7874,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="16" ht="72.75" customHeight="1" s="1" customFormat="1">
+    <row r="16" ht="72.75" customHeight="1">
       <c r="A16" s="6">
         <v>14</v>
       </c>
@@ -7878,7 +7885,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="17" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="17" ht="110.25" customHeight="1">
       <c r="A17" s="6">
         <v>15</v>
       </c>
@@ -7889,7 +7896,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="18" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="18" ht="110.25" customHeight="1">
       <c r="A18" s="6">
         <v>16</v>
       </c>
@@ -7900,7 +7907,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="19" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="19" ht="110.25" customHeight="1">
       <c r="A19" s="6">
         <v>17</v>
       </c>
@@ -7911,7 +7918,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="20" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="20" ht="122.25" customHeight="1">
       <c r="A20" s="6">
         <v>18</v>
       </c>
@@ -7922,7 +7929,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="21" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="21" ht="122.25" customHeight="1">
       <c r="A21" s="6">
         <v>19</v>
       </c>
@@ -7933,7 +7940,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="22" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="22" ht="110.25" customHeight="1">
       <c r="A22" s="6">
         <v>20</v>
       </c>
@@ -7944,7 +7951,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="23" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="23" ht="47.25" customHeight="1">
       <c r="A23" s="6">
         <v>21</v>
       </c>
@@ -7955,7 +7962,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="24" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="24" ht="122.25" customHeight="1">
       <c r="A24" s="6">
         <v>22</v>
       </c>
@@ -7966,7 +7973,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="25" ht="80.25" customHeight="1" s="1" customFormat="1"/>
+    <row r="25" ht="80.25" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:C1"/>
@@ -7983,23 +7990,23 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{9D89B7E0-5203-448A-BA8C-8BED3AA015DF}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{23DC0269-9A7D-4AF5-9576-500B2110F879}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="6.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="38.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="6.00390625" customWidth="1"/>
+    <col min="2" max="2" width="38.00390625" customWidth="1"/>
+    <col min="3" max="3" width="80.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>639</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -8010,7 +8017,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="3" ht="110.25" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -8021,7 +8028,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="4" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="122.25" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -8032,7 +8039,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="5" ht="497.25" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="409.5" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -8043,7 +8050,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="6" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="6" ht="122.25" customHeight="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -8054,7 +8061,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="7" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="7" ht="122.25" customHeight="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -8065,7 +8072,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="8" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="8" ht="135" customHeight="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -8076,7 +8083,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="9" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="9" ht="110.25" customHeight="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -8087,7 +8094,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="10" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="10" ht="122.25" customHeight="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -8098,7 +8105,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="11" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="11" ht="122.25" customHeight="1">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -8109,7 +8116,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="12" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="12" ht="47.25" customHeight="1">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -8120,7 +8127,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="13" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="13" ht="110.25" customHeight="1">
       <c r="A13" s="6">
         <v>11</v>
       </c>
@@ -8131,7 +8138,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="14" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="14" ht="110.25" customHeight="1">
       <c r="A14" s="6">
         <v>12</v>
       </c>
@@ -8142,7 +8149,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="15" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="15" ht="122.25" customHeight="1">
       <c r="A15" s="6">
         <v>13</v>
       </c>
@@ -8153,7 +8160,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="16" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="16" ht="110.25" customHeight="1">
       <c r="A16" s="6">
         <v>14</v>
       </c>
@@ -8164,7 +8171,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="17" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="17" ht="110.25" customHeight="1">
       <c r="A17" s="6">
         <v>15</v>
       </c>
@@ -8175,7 +8182,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="18" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="18" ht="122.25" customHeight="1">
       <c r="A18" s="6">
         <v>16</v>
       </c>
@@ -8186,7 +8193,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="19" ht="80.25" customHeight="1" s="1" customFormat="1"/>
+    <row r="19" ht="80.25" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:C1"/>
@@ -8203,23 +8210,23 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{2EA74B09-0CC9-4EB7-8EA0-373954166F47}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{3444590D-3E07-45ED-92B5-C9B13345720F}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C41"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="6.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="38.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="6.00390625" customWidth="1"/>
+    <col min="2" max="2" width="38.00390625" customWidth="1"/>
+    <col min="3" max="3" width="80.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>640</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -8230,7 +8237,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="3" ht="110.25" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -8241,7 +8248,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="4" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="97.5" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -8252,7 +8259,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="5" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="122.25" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -8263,7 +8270,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="6" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="6" ht="97.5" customHeight="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -8274,7 +8281,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="7" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="7" ht="122.25" customHeight="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -8285,7 +8292,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="8" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="8" ht="110.25" customHeight="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -8296,7 +8303,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="9" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="9" ht="122.25" customHeight="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -8307,7 +8314,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="10" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="10" ht="110.25" customHeight="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -8318,7 +8325,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="11" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="11" ht="122.25" customHeight="1">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -8329,7 +8336,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="12" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="12" ht="110.25" customHeight="1">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -8340,7 +8347,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="13" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="13" ht="122.25" customHeight="1">
       <c r="A13" s="6">
         <v>11</v>
       </c>
@@ -8351,7 +8358,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="14" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="14" ht="97.5" customHeight="1">
       <c r="A14" s="6">
         <v>12</v>
       </c>
@@ -8362,7 +8369,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="15" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="15" ht="47.25" customHeight="1">
       <c r="A15" s="6">
         <v>13</v>
       </c>
@@ -8373,7 +8380,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="16" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="16" ht="110.25" customHeight="1">
       <c r="A16" s="6">
         <v>14</v>
       </c>
@@ -8384,7 +8391,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="17" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="17" ht="110.25" customHeight="1">
       <c r="A17" s="6">
         <v>15</v>
       </c>
@@ -8395,7 +8402,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="18" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="18" ht="110.25" customHeight="1">
       <c r="A18" s="6">
         <v>16</v>
       </c>
@@ -8406,7 +8413,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="19" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="19" ht="97.5" customHeight="1">
       <c r="A19" s="6">
         <v>17</v>
       </c>
@@ -8417,7 +8424,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="20" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="20" ht="110.25" customHeight="1">
       <c r="A20" s="6">
         <v>18</v>
       </c>
@@ -8428,7 +8435,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="21" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="21" ht="97.5" customHeight="1">
       <c r="A21" s="6">
         <v>19</v>
       </c>
@@ -8439,7 +8446,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="22" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="22" ht="97.5" customHeight="1">
       <c r="A22" s="6">
         <v>20</v>
       </c>
@@ -8450,7 +8457,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="23" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="23" ht="110.25" customHeight="1">
       <c r="A23" s="6">
         <v>21</v>
       </c>
@@ -8461,7 +8468,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="24" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="24" ht="159.75" customHeight="1">
       <c r="A24" s="6">
         <v>22</v>
       </c>
@@ -8472,7 +8479,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="25" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="25" ht="110.25" customHeight="1">
       <c r="A25" s="6">
         <v>23</v>
       </c>
@@ -8483,7 +8490,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="26" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="26" ht="147.75" customHeight="1">
       <c r="A26" s="6">
         <v>24</v>
       </c>
@@ -8494,7 +8501,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="27" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="27" ht="97.5" customHeight="1">
       <c r="A27" s="6">
         <v>25</v>
       </c>
@@ -8505,7 +8512,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="28" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="28" ht="110.25" customHeight="1">
       <c r="A28" s="6">
         <v>26</v>
       </c>
@@ -8516,7 +8523,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="29" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="29" ht="110.25" customHeight="1">
       <c r="A29" s="6">
         <v>27</v>
       </c>
@@ -8527,7 +8534,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="30" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="30" ht="147.75" customHeight="1">
       <c r="A30" s="6">
         <v>28</v>
       </c>
@@ -8538,7 +8545,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="31" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="31" ht="110.25" customHeight="1">
       <c r="A31" s="6">
         <v>29</v>
       </c>
@@ -8549,7 +8556,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="32" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="32" ht="110.25" customHeight="1">
       <c r="A32" s="6">
         <v>30</v>
       </c>
@@ -8560,7 +8567,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1" s="1" customFormat="1">
+    <row r="33" ht="60" customHeight="1">
       <c r="A33" s="6">
         <v>31</v>
       </c>
@@ -8571,7 +8578,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="34" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="34" ht="159.75" customHeight="1">
       <c r="A34" s="6">
         <v>32</v>
       </c>
@@ -8582,7 +8589,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="35" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="35" ht="97.5" customHeight="1">
       <c r="A35" s="6">
         <v>33</v>
       </c>
@@ -8593,7 +8600,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="36" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="36" ht="122.25" customHeight="1">
       <c r="A36" s="6">
         <v>34</v>
       </c>
@@ -8604,7 +8611,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="37" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="37" ht="110.25" customHeight="1">
       <c r="A37" s="6">
         <v>35</v>
       </c>
@@ -8615,7 +8622,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="38" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="38" ht="135" customHeight="1">
       <c r="A38" s="6">
         <v>36</v>
       </c>
@@ -8626,7 +8633,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="39" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="39" ht="110.25" customHeight="1">
       <c r="A39" s="6">
         <v>37</v>
       </c>
@@ -8637,7 +8644,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="40" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="40" ht="135" customHeight="1">
       <c r="A40" s="6">
         <v>38</v>
       </c>
@@ -8648,7 +8655,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="41" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="41" ht="135" customHeight="1">
       <c r="A41" s="6">
         <v>39</v>
       </c>
@@ -8675,23 +8682,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{7917B5C3-3819-4966-85C4-6A12997225C3}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{4B45370A-B4DB-4BFF-8280-92F224BE10A2}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="6.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="38.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="6.00390625" customWidth="1"/>
+    <col min="2" max="2" width="38.00390625" customWidth="1"/>
+    <col min="3" max="3" width="80.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>623</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -8702,7 +8709,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1" s="1" customFormat="1">
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -8713,7 +8720,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="147.75" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -8724,7 +8731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="122.25" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -8735,7 +8742,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="6" ht="159.75" customHeight="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -8746,7 +8753,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="7" ht="159.75" customHeight="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -8757,7 +8764,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="8" ht="147.75" customHeight="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -8768,7 +8775,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" ht="197.25" customHeight="1" s="1" customFormat="1">
+    <row r="9" ht="197.25" customHeight="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -8779,7 +8786,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="10" ht="159.75" customHeight="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -8790,7 +8797,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" ht="197.25" customHeight="1" s="1" customFormat="1">
+    <row r="11" ht="197.25" customHeight="1">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -8801,7 +8808,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="12" ht="135" customHeight="1">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -8812,7 +8819,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" ht="172.5" customHeight="1" s="1" customFormat="1">
+    <row r="13" ht="172.5" customHeight="1">
       <c r="A13" s="6">
         <v>11</v>
       </c>
@@ -8823,7 +8830,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="14" ht="147.75" customHeight="1">
       <c r="A14" s="6">
         <v>12</v>
       </c>
@@ -8834,7 +8841,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="15" ht="122.25" customHeight="1">
       <c r="A15" s="6">
         <v>13</v>
       </c>
@@ -8845,7 +8852,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="16" ht="97.5" customHeight="1">
       <c r="A16" s="6">
         <v>14</v>
       </c>
@@ -8856,7 +8863,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="17" ht="97.5" customHeight="1">
       <c r="A17" s="6">
         <v>15</v>
       </c>
@@ -8883,23 +8890,23 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{784E77B9-F97F-4682-9CCD-0B1D3FBB41C1}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{E01A2ABE-C9BC-4796-93A7-8966A460AB13}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="6.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="38.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="6.00390625" customWidth="1"/>
+    <col min="2" max="2" width="38.00390625" customWidth="1"/>
+    <col min="3" max="3" width="80.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>641</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -8910,7 +8917,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="3" ht="122.25" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -8921,7 +8928,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="4" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="110.25" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -8932,7 +8939,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="5" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="147.75" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -8943,7 +8950,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="6" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="6" ht="122.25" customHeight="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -8954,7 +8961,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="7" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="7" ht="159.75" customHeight="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -8965,7 +8972,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="8" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="8" ht="47.25" customHeight="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -8976,7 +8983,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="9" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="9" ht="97.5" customHeight="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -8987,7 +8994,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="10" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="10" ht="135" customHeight="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -8998,7 +9005,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="11" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="11" ht="122.25" customHeight="1">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -9009,7 +9016,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="12" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="12" ht="122.25" customHeight="1">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -9020,7 +9027,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="13" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="13" ht="47.25" customHeight="1">
       <c r="A13" s="6">
         <v>11</v>
       </c>
@@ -9031,7 +9038,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="14" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="14" ht="122.25" customHeight="1">
       <c r="A14" s="6">
         <v>12</v>
       </c>
@@ -9042,7 +9049,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="15" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="15" ht="122.25" customHeight="1">
       <c r="A15" s="6">
         <v>13</v>
       </c>
@@ -9053,7 +9060,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="16" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="16" ht="47.25" customHeight="1">
       <c r="A16" s="6">
         <v>14</v>
       </c>
@@ -9064,7 +9071,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="17" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="17" ht="122.25" customHeight="1">
       <c r="A17" s="6">
         <v>15</v>
       </c>
@@ -9075,7 +9082,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="18" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="18" ht="135" customHeight="1">
       <c r="A18" s="6">
         <v>16</v>
       </c>
@@ -9086,7 +9093,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="19" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="19" ht="135" customHeight="1">
       <c r="A19" s="6">
         <v>17</v>
       </c>
@@ -9097,7 +9104,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="20" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="20" ht="135" customHeight="1">
       <c r="A20" s="6">
         <v>18</v>
       </c>
@@ -9108,7 +9115,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="21" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="21" ht="122.25" customHeight="1">
       <c r="A21" s="6">
         <v>19</v>
       </c>
@@ -9135,23 +9142,23 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{6B8F45D7-E7CA-440F-92A5-81A3084AD0F0}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{064A04AE-E93C-4121-B8A3-FD8B2126716C}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="6.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="38.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="6.00390625" customWidth="1"/>
+    <col min="2" max="2" width="38.00390625" customWidth="1"/>
+    <col min="3" max="3" width="80.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>642</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -9162,7 +9169,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="3" ht="122.25" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -9173,7 +9180,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="4" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="135" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -9184,7 +9191,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="5" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="122.25" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -9195,7 +9202,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="6" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="6" ht="122.25" customHeight="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -9206,7 +9213,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="7" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="7" ht="110.25" customHeight="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -9233,23 +9240,23 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{D1A523AB-F82F-4B06-BEEB-F9565CEBD309}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{E7556EB9-4B32-428C-A5FA-95192E46D842}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="6.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="38.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="6.00390625" customWidth="1"/>
+    <col min="2" max="2" width="38.00390625" customWidth="1"/>
+    <col min="3" max="3" width="80.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>643</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -9260,7 +9267,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="3" ht="135" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -9271,7 +9278,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="4" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="110.25" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -9282,7 +9289,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="5" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="122.25" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -9293,7 +9300,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="6" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="6" ht="122.25" customHeight="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -9320,23 +9327,23 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{E5F726DC-6A2C-41AF-BA1A-D7898427874A}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{BCDC8BC2-5633-4153-BD20-37878E48C046}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="6.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="38.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="6.00390625" customWidth="1"/>
+    <col min="2" max="2" width="38.00390625" customWidth="1"/>
+    <col min="3" max="3" width="80.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>644</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -9347,7 +9354,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="3" ht="135" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -9358,7 +9365,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="4" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="47.25" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -9369,7 +9376,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="5" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="135" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -9380,7 +9387,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="6" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="6" ht="159.75" customHeight="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -9391,7 +9398,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="7" ht="197.25" customHeight="1" s="1" customFormat="1">
+    <row r="7" ht="197.25" customHeight="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -9402,7 +9409,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="8" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="8" ht="110.25" customHeight="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -9413,7 +9420,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="9" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="9" ht="135" customHeight="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -9424,7 +9431,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="10" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="10" ht="122.25" customHeight="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -9451,25 +9458,25 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{6A64FBDC-524A-40D9-8834-7F5C64D5B7A2}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{38FFBC20-F077-4C96-BE1F-ED0D20507884}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="22.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="16.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="14.00390625" customWidth="1"/>
-    <col min="4" max="4" style="1" width="16.00390625" customWidth="1"/>
+    <col min="1" max="1" width="22.00390625" customWidth="1"/>
+    <col min="2" max="2" width="16.00390625" customWidth="1"/>
+    <col min="3" max="3" width="14.00390625" customWidth="1"/>
+    <col min="4" max="4" width="16.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>645</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>646</v>
       </c>
@@ -9483,7 +9490,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" s="1" customFormat="1">
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="9" t="s">
         <v>650</v>
       </c>
@@ -9497,7 +9504,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="18" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>652</v>
       </c>
@@ -9511,7 +9518,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="18" customHeight="1">
       <c r="A5" s="9" t="s">
         <v>654</v>
       </c>
@@ -9525,7 +9532,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1" s="1" customFormat="1">
+    <row r="6" ht="18" customHeight="1">
       <c r="A6" s="9" t="s">
         <v>656</v>
       </c>
@@ -9539,7 +9546,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1" s="1" customFormat="1">
+    <row r="7" ht="18" customHeight="1">
       <c r="A7" s="9" t="s">
         <v>658</v>
       </c>
@@ -9553,7 +9560,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1" s="1" customFormat="1">
+    <row r="8" ht="18" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>660</v>
       </c>
@@ -9567,7 +9574,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1" s="1" customFormat="1">
+    <row r="9" ht="18" customHeight="1">
       <c r="A9" s="9" t="s">
         <v>662</v>
       </c>
@@ -9581,7 +9588,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1" s="1" customFormat="1">
+    <row r="10" ht="18" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>664</v>
       </c>
@@ -9595,7 +9602,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1" s="1" customFormat="1">
+    <row r="11" ht="18" customHeight="1">
       <c r="A11" s="9" t="s">
         <v>666</v>
       </c>
@@ -9609,7 +9616,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1" s="1" customFormat="1">
+    <row r="12" ht="18" customHeight="1">
       <c r="A12" s="9" t="s">
         <v>668</v>
       </c>
@@ -9623,7 +9630,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1" s="1" customFormat="1">
+    <row r="13" ht="18" customHeight="1">
       <c r="A13" s="9" t="s">
         <v>670</v>
       </c>
@@ -9637,7 +9644,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1" s="1" customFormat="1">
+    <row r="14" ht="18" customHeight="1">
       <c r="A14" s="9" t="s">
         <v>672</v>
       </c>
@@ -9651,7 +9658,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1" s="1" customFormat="1">
+    <row r="15" ht="18" customHeight="1">
       <c r="A15" s="9" t="s">
         <v>674</v>
       </c>
@@ -9665,7 +9672,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1" s="1" customFormat="1">
+    <row r="16" ht="18" customHeight="1">
       <c r="A16" s="9" t="s">
         <v>676</v>
       </c>
@@ -9679,7 +9686,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1" s="1" customFormat="1">
+    <row r="17" ht="18" customHeight="1">
       <c r="A17" s="9" t="s">
         <v>678</v>
       </c>
@@ -9693,7 +9700,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1" s="1" customFormat="1">
+    <row r="18" ht="18" customHeight="1">
       <c r="A18" s="9" t="s">
         <v>680</v>
       </c>
@@ -9707,7 +9714,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1" s="1" customFormat="1">
+    <row r="19" ht="18" customHeight="1">
       <c r="A19" s="9" t="s">
         <v>682</v>
       </c>
@@ -9721,7 +9728,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1" s="1" customFormat="1">
+    <row r="20" ht="18" customHeight="1">
       <c r="A20" s="9" t="s">
         <v>684</v>
       </c>
@@ -9735,7 +9742,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1" s="1" customFormat="1">
+    <row r="21" ht="18" customHeight="1">
       <c r="A21" s="9" t="s">
         <v>686</v>
       </c>
@@ -9749,7 +9756,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1" s="1" customFormat="1">
+    <row r="22" ht="18" customHeight="1">
       <c r="A22" s="9" t="s">
         <v>688</v>
       </c>
@@ -9763,7 +9770,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1" s="1" customFormat="1">
+    <row r="23" ht="18" customHeight="1">
       <c r="A23" s="9" t="s">
         <v>690</v>
       </c>
@@ -9777,7 +9784,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1" s="1" customFormat="1">
+    <row r="24" ht="18" customHeight="1">
       <c r="A24" s="9" t="s">
         <v>692</v>
       </c>
@@ -9791,7 +9798,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1" s="1" customFormat="1">
+    <row r="25" ht="18" customHeight="1">
       <c r="A25" s="12" t="s">
         <v>694</v>
       </c>
@@ -9805,12 +9812,12 @@
         <v>695</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1" s="1" customFormat="1"/>
-    <row r="28" ht="14.25" customHeight="1" s="1" customFormat="1"/>
-    <row r="29" ht="14.25" customHeight="1" s="1" customFormat="1"/>
-    <row r="30" ht="14.25" customHeight="1" s="1" customFormat="1"/>
-    <row r="31" ht="14.25" customHeight="1" s="1" customFormat="1"/>
-    <row r="32" ht="14.25" customHeight="1" s="1" customFormat="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="14.25" customHeight="1"/>
+    <row r="29" ht="14.25" customHeight="1"/>
+    <row r="30" ht="14.25" customHeight="1"/>
+    <row r="31" ht="14.25" customHeight="1"/>
+    <row r="32" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:D1"/>
@@ -9827,23 +9834,23 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{F2F07DDF-81F6-4E23-A0EE-EEB3C787728F}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{35297EB2-5EC7-4D13-9EA1-E737A672E291}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="6.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="38.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="6.00390625" customWidth="1"/>
+    <col min="2" max="2" width="38.00390625" customWidth="1"/>
+    <col min="3" max="3" width="80.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -9854,7 +9861,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="3" ht="147.75" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -9865,7 +9872,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="159.75" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -9876,7 +9883,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="147.75" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -9887,7 +9894,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="6" ht="159.75" customHeight="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -9898,7 +9905,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1" s="1" customFormat="1">
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -9909,7 +9916,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="8" ht="122.25" customHeight="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -9920,7 +9927,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="9" ht="97.5" customHeight="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -9931,7 +9938,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="10" ht="159.75" customHeight="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -9942,7 +9949,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="11" ht="159.75" customHeight="1">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -9953,7 +9960,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="12" ht="97.5" customHeight="1">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -9964,7 +9971,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="13" ht="97.5" customHeight="1">
       <c r="A13" s="6">
         <v>11</v>
       </c>
@@ -9975,7 +9982,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="14" ht="122.25" customHeight="1">
       <c r="A14" s="6">
         <v>12</v>
       </c>
@@ -9986,7 +9993,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="15" ht="159.75" customHeight="1">
       <c r="A15" s="6">
         <v>13</v>
       </c>
@@ -9997,7 +10004,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" ht="185.25" customHeight="1" s="1" customFormat="1">
+    <row r="16" ht="185.25" customHeight="1">
       <c r="A16" s="6">
         <v>14</v>
       </c>
@@ -10008,7 +10015,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="17" ht="147.75" customHeight="1">
       <c r="A17" s="6">
         <v>15</v>
       </c>
@@ -10019,7 +10026,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="18" ht="135" customHeight="1">
       <c r="A18" s="6">
         <v>16</v>
       </c>
@@ -10030,7 +10037,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="19" ht="147.75" customHeight="1">
       <c r="A19" s="6">
         <v>17</v>
       </c>
@@ -10041,7 +10048,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="20" ht="147.75" customHeight="1">
       <c r="A20" s="6">
         <v>18</v>
       </c>
@@ -10052,7 +10059,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="21" ht="97.5" customHeight="1">
       <c r="A21" s="6">
         <v>19</v>
       </c>
@@ -10063,7 +10070,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="22" ht="122.25" customHeight="1">
       <c r="A22" s="6">
         <v>20</v>
       </c>
@@ -10074,7 +10081,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="23" ht="110.25" customHeight="1">
       <c r="A23" s="6">
         <v>21</v>
       </c>
@@ -10085,7 +10092,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="24" ht="122.25" customHeight="1">
       <c r="A24" s="6">
         <v>22</v>
       </c>
@@ -10096,7 +10103,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="25" ht="147.75" customHeight="1">
       <c r="A25" s="6">
         <v>23</v>
       </c>
@@ -10107,7 +10114,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="26" ht="147.75" customHeight="1">
       <c r="A26" s="6">
         <v>24</v>
       </c>
@@ -10118,7 +10125,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="27" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="27" ht="110.25" customHeight="1">
       <c r="A27" s="6">
         <v>25</v>
       </c>
@@ -10129,7 +10136,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="28" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="28" ht="122.25" customHeight="1">
       <c r="A28" s="6">
         <v>26</v>
       </c>
@@ -10140,7 +10147,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="29" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="29" ht="97.5" customHeight="1">
       <c r="A29" s="6">
         <v>27</v>
       </c>
@@ -10151,7 +10158,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="30" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="30" ht="97.5" customHeight="1">
       <c r="A30" s="6">
         <v>28</v>
       </c>
@@ -10162,7 +10169,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="31" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="31" ht="135" customHeight="1">
       <c r="A31" s="6">
         <v>29</v>
       </c>
@@ -10173,7 +10180,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="32" ht="172.5" customHeight="1" s="1" customFormat="1">
+    <row r="32" ht="172.5" customHeight="1">
       <c r="A32" s="6">
         <v>30</v>
       </c>
@@ -10184,7 +10191,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="33" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="33" ht="122.25" customHeight="1">
       <c r="A33" s="6">
         <v>31</v>
       </c>
@@ -10195,7 +10202,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="34" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="34" ht="135" customHeight="1">
       <c r="A34" s="6">
         <v>32</v>
       </c>
@@ -10206,7 +10213,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="35" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="35" ht="122.25" customHeight="1">
       <c r="A35" s="6">
         <v>33</v>
       </c>
@@ -10217,7 +10224,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="36" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="36" ht="110.25" customHeight="1">
       <c r="A36" s="6">
         <v>34</v>
       </c>
@@ -10228,7 +10235,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="37" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="37" ht="122.25" customHeight="1">
       <c r="A37" s="6">
         <v>35</v>
       </c>
@@ -10255,23 +10262,23 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{2C5837DC-EA51-441F-8B91-D5E1DB857CBC}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{20398771-DC32-4A82-9972-00EBD6F9ADEC}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="6.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="38.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="6.00390625" customWidth="1"/>
+    <col min="2" max="2" width="38.00390625" customWidth="1"/>
+    <col min="3" max="3" width="80.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -10282,7 +10289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="3" ht="135" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -10293,7 +10300,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="4" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="147.75" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -10304,7 +10311,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="5" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="135" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -10315,7 +10322,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="6" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="6" ht="47.25" customHeight="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -10326,7 +10333,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="7" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="7" ht="147.75" customHeight="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -10337,7 +10344,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="8" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="8" ht="159.75" customHeight="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -10348,7 +10355,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="9" ht="110.25" customHeight="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -10359,7 +10366,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="10" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="10" ht="47.25" customHeight="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -10370,7 +10377,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="11" ht="122.25" customHeight="1">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -10381,7 +10388,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="12" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="12" ht="147.75" customHeight="1">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -10392,7 +10399,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="13" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="13" ht="122.25" customHeight="1">
       <c r="A13" s="6">
         <v>11</v>
       </c>
@@ -10403,7 +10410,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="14" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="14" ht="122.25" customHeight="1">
       <c r="A14" s="6">
         <v>12</v>
       </c>
@@ -10414,7 +10421,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="15" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="15" ht="122.25" customHeight="1">
       <c r="A15" s="6">
         <v>13</v>
       </c>
@@ -10425,7 +10432,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="16" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="16" ht="135" customHeight="1">
       <c r="A16" s="6">
         <v>14</v>
       </c>
@@ -10436,7 +10443,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="17" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="17" ht="159.75" customHeight="1">
       <c r="A17" s="6">
         <v>15</v>
       </c>
@@ -10447,7 +10454,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="18" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="18" ht="135" customHeight="1">
       <c r="A18" s="6">
         <v>16</v>
       </c>
@@ -10458,7 +10465,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="19" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="19" ht="110.25" customHeight="1">
       <c r="A19" s="6">
         <v>17</v>
       </c>
@@ -10485,23 +10492,23 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{0BF02C57-D444-438D-801A-FEF7FE0626A6}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{71BFF236-353C-4AE0-BC5F-D31376230DA7}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="6.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="38.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="6.00390625" customWidth="1"/>
+    <col min="2" max="2" width="38.00390625" customWidth="1"/>
+    <col min="3" max="3" width="80.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>626</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -10512,7 +10519,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="3" ht="122.25" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -10523,7 +10530,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="122.25" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -10534,7 +10541,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="5" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="122.25" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -10545,7 +10552,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="6" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="6" ht="122.25" customHeight="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -10556,7 +10563,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="7" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="7" ht="122.25" customHeight="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -10567,7 +10574,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="8" ht="172.5" customHeight="1" s="1" customFormat="1">
+    <row r="8" ht="172.5" customHeight="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -10578,7 +10585,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="9" ht="97.5" customHeight="1" s="1" customFormat="1">
+    <row r="9" ht="97.5" customHeight="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -10589,7 +10596,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="10" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="10" ht="110.25" customHeight="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -10600,7 +10607,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="11" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="11" ht="122.25" customHeight="1">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -10611,7 +10618,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="12" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="12" ht="110.25" customHeight="1">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -10622,7 +10629,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="13" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="13" ht="122.25" customHeight="1">
       <c r="A13" s="6">
         <v>11</v>
       </c>
@@ -10633,7 +10640,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="14" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="14" ht="159.75" customHeight="1">
       <c r="A14" s="6">
         <v>12</v>
       </c>
@@ -10644,7 +10651,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="15" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="15" ht="135" customHeight="1">
       <c r="A15" s="6">
         <v>13</v>
       </c>
@@ -10671,23 +10678,23 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{644D3674-AB09-46EC-A2BC-DBAC3A5F5C92}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{A616EBD0-3F73-474B-BBA1-7654D37A70D7}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="6.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="38.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="6.00390625" customWidth="1"/>
+    <col min="2" max="2" width="38.00390625" customWidth="1"/>
+    <col min="3" max="3" width="80.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -10698,7 +10705,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="3" ht="122.25" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -10709,7 +10716,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="4" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="122.25" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -10720,7 +10727,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="5" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="110.25" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -10731,7 +10738,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="6" ht="210" customHeight="1" s="1" customFormat="1">
+    <row r="6" ht="210" customHeight="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -10742,7 +10749,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="7" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="7" ht="122.25" customHeight="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -10753,7 +10760,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="8" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="8" ht="110.25" customHeight="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -10764,7 +10771,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="9" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="9" ht="47.25" customHeight="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -10775,7 +10782,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="10" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="10" ht="122.25" customHeight="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -10786,7 +10793,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="11" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="11" ht="110.25" customHeight="1">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -10797,7 +10804,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="12" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="12" ht="147.75" customHeight="1">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -10808,7 +10815,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="13" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="13" ht="122.25" customHeight="1">
       <c r="A13" s="6">
         <v>11</v>
       </c>
@@ -10819,7 +10826,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="14" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="14" ht="122.25" customHeight="1">
       <c r="A14" s="6">
         <v>12</v>
       </c>
@@ -10830,7 +10837,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="15" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="15" ht="135" customHeight="1">
       <c r="A15" s="6">
         <v>13</v>
       </c>
@@ -10857,23 +10864,23 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{46B953CB-2BC8-434D-9B5F-EF64EDEDC718}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{02BB06CC-3F25-4D69-866B-FAF86994CB39}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="6.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="38.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="6.00390625" customWidth="1"/>
+    <col min="2" max="2" width="38.00390625" customWidth="1"/>
+    <col min="3" max="3" width="80.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>628</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -10884,7 +10891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="3" ht="122.25" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -10895,7 +10902,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="4" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="135" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -10906,7 +10913,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="5" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="147.75" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -10917,7 +10924,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="6" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="6" ht="135" customHeight="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -10928,7 +10935,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="7" ht="122.25" customHeight="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -10939,7 +10946,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="8" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="8" ht="47.25" customHeight="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -10950,7 +10957,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="9" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="9" ht="122.25" customHeight="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -10961,7 +10968,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="10" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="10" ht="135" customHeight="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -10972,7 +10979,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="11" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="11" ht="110.25" customHeight="1">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -10983,7 +10990,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="12" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="12" ht="135" customHeight="1">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -10994,7 +11001,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="13" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="13" ht="110.25" customHeight="1">
       <c r="A13" s="6">
         <v>11</v>
       </c>
@@ -11005,7 +11012,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="14" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="14" ht="122.25" customHeight="1">
       <c r="A14" s="6">
         <v>12</v>
       </c>
@@ -11016,7 +11023,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1" s="1" customFormat="1">
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="6">
         <v>13</v>
       </c>
@@ -11027,7 +11034,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="16" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="16" ht="47.25" customHeight="1">
       <c r="A16" s="6">
         <v>14</v>
       </c>
@@ -11038,7 +11045,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="17" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="17" ht="135" customHeight="1">
       <c r="A17" s="6">
         <v>15</v>
       </c>
@@ -11049,7 +11056,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="18" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="18" ht="122.25" customHeight="1">
       <c r="A18" s="6">
         <v>16</v>
       </c>
@@ -11060,7 +11067,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="19" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="19" ht="135" customHeight="1">
       <c r="A19" s="6">
         <v>17</v>
       </c>
@@ -11071,7 +11078,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="20" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="20" ht="110.25" customHeight="1">
       <c r="A20" s="6">
         <v>18</v>
       </c>
@@ -11082,7 +11089,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="21" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="21" ht="122.25" customHeight="1">
       <c r="A21" s="6">
         <v>19</v>
       </c>
@@ -11093,7 +11100,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="22" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="22" ht="135" customHeight="1">
       <c r="A22" s="6">
         <v>20</v>
       </c>
@@ -11104,7 +11111,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="23" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="23" ht="135" customHeight="1">
       <c r="A23" s="6">
         <v>21</v>
       </c>
@@ -11115,7 +11122,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="24" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="24" ht="122.25" customHeight="1">
       <c r="A24" s="6">
         <v>22</v>
       </c>
@@ -11126,7 +11133,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="25" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="25" ht="122.25" customHeight="1">
       <c r="A25" s="6">
         <v>23</v>
       </c>
@@ -11153,23 +11160,23 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{66C9C7F0-1E22-41BE-BEA7-00559B4C3A05}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{3B7C13C9-5DC3-49CE-BC67-A59690A4F965}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="6.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="38.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="6.00390625" customWidth="1"/>
+    <col min="2" max="2" width="38.00390625" customWidth="1"/>
+    <col min="3" max="3" width="80.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>629</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -11180,7 +11187,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="3" ht="110.25" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -11191,7 +11198,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="4" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="110.25" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -11202,7 +11209,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="5" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="122.25" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -11213,7 +11220,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="6" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="6" ht="135" customHeight="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -11224,7 +11231,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="7" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="7" ht="122.25" customHeight="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -11235,7 +11242,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="8" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="8" ht="159.75" customHeight="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -11246,7 +11253,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="9" ht="135" customHeight="1" s="1" customFormat="1">
+    <row r="9" ht="135" customHeight="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -11257,7 +11264,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="10" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="10" ht="122.25" customHeight="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -11284,23 +11291,23 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{3CA6D0B1-5522-4532-8F29-79CCE31532DE}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{EEDCAB69-10C4-41D9-B7F6-D3B874DAD28A}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.399999999999999" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" style="1" width="6.00390625" customWidth="1"/>
-    <col min="2" max="2" style="1" width="38.00390625" customWidth="1"/>
-    <col min="3" max="3" style="1" width="80.00390625" customWidth="1"/>
+    <col min="1" max="1" width="6.00390625" customWidth="1"/>
+    <col min="2" max="2" width="38.00390625" customWidth="1"/>
+    <col min="3" max="3" width="80.00390625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="20.25" customHeight="1" s="1" customFormat="1">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -11311,7 +11318,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="3" ht="122.25" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -11322,7 +11329,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="4" ht="122.25" customHeight="1" s="1" customFormat="1">
+    <row r="4" ht="122.25" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -11333,7 +11340,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="5" ht="22.5" customHeight="1" s="1" customFormat="1">
+    <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -11344,7 +11351,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="6" ht="147.75" customHeight="1" s="1" customFormat="1">
+    <row r="6" ht="147.75" customHeight="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -11355,7 +11362,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="7" ht="47.25" customHeight="1" s="1" customFormat="1">
+    <row r="7" ht="47.25" customHeight="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -11366,7 +11373,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="8" ht="110.25" customHeight="1" s="1" customFormat="1">
+    <row r="8" ht="110.25" customHeight="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -11377,7 +11384,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="9" ht="159.75" customHeight="1" s="1" customFormat="1">
+    <row r="9" ht="159.75" customHeight="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
